--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -529,7 +529,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -911,6 +911,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -918,7 +919,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1452,6 +1453,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1459,7 +1461,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1888,6 +1890,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1895,7 +1898,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2387,6 +2390,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2394,7 +2398,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2643,6 +2647,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2650,7 +2655,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3237,6 +3242,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3244,7 +3250,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4015,6 +4021,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4022,7 +4029,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4335,6 +4342,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4342,7 +4350,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4739,6 +4747,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4746,7 +4755,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5090,6 +5099,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5097,7 +5107,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6035,6 +6045,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6042,7 +6053,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6215,6 +6226,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6222,7 +6234,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7172,6 +7184,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7179,7 +7192,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7564,6 +7577,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7571,7 +7585,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8518,6 +8532,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8525,7 +8540,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9197,5 +9212,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -853,7 +853,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6.24% -&gt; 6.01% on the AED risk-free path (du has no debt whose cost could define the</t>
+          <t>6.32% -&gt; 6.08% on the AED risk-free path (du has no debt whose cost could define the</t>
         </is>
       </c>
     </row>
@@ -2729,111 +2729,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>5.08%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>20.09028809929897</v>
+        <v>19.66933438309751</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>22.70200399121432</v>
+        <v>22.15174913365529</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>26.35028687677077</v>
+        <v>25.59094934303363</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>31.80947953617687</v>
+        <v>30.67626651149073</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>40.88093078422291</v>
+        <v>38.96850852166403</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>5.58%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>17.70882650142025</v>
+        <v>17.38248029009414</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>19.61381266941501</v>
+        <v>19.20400769626519</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>22.14815500546771</v>
+        <v>21.61270757502213</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>25.68826847930056</v>
+        <v>24.94969675636998</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>30.98549055762803</v>
+        <v>29.88377622565962</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>6.08%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>15.85515972490487</v>
+        <v>15.59424768185649</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>17.29553191126147</v>
+        <v>16.9778093008496</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>21.60109684626675</v>
+        <v>21.08026724450918</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>25.03440858808661</v>
+        <v>24.31633715735939</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>6.51%</t>
+          <t>6.58%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>14.37120518453367</v>
+        <v>14.15746739328381</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>15.49098364095381</v>
+        <v>15.23694854926923</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>16.88724745936135</v>
+        <v>16.57803794656374</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>18.67822143868329</v>
+        <v>18.29028721846222</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>21.06073829814544</v>
+        <v>20.55433959378778</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>7.01%</t>
+          <t>7.08%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>13.15628173121538</v>
+        <v>12.97770025312425</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>14.04629803516069</v>
+        <v>13.83817789141263</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>15.13119469679048</v>
+        <v>14.88394848792242</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>16.48390668230309</v>
+        <v>16.18310131865233</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>18.218951493052</v>
+        <v>17.84174327636619</v>
       </c>
     </row>
     <row r="12">
@@ -2847,138 +2847,138 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.32%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>5.74%</t>
+          <t>5.82%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>6.24%</t>
+          <t>6.32%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>6.74%</t>
+          <t>6.82%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>7.24%</t>
+          <t>7.32%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 5.01%</t>
+          <t>terminal 5.08%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>26.99024898628901</v>
+        <v>26.21186590655091</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>26.66777730641833</v>
+        <v>25.89899335245586</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>26.35028687677077</v>
+        <v>25.59094934303363</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>26.03768235944068</v>
+        <v>25.28764153760843</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>25.7298706020608</v>
+        <v>24.98897971072595</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 5.51%</t>
+          <t>terminal 5.58%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>22.68454287098371</v>
+        <v>22.13562242012934</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>22.41426634164783</v>
+        <v>21.87213658041468</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>22.14815500546771</v>
+        <v>21.61270757502213</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>21.88612926312696</v>
+        <v>21.35725793786072</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>21.62811133807164</v>
+        <v>21.10571197540687</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 6.01%</t>
+          <t>terminal 6.08%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>19.60547307585225</v>
+        <v>19.19660794179827</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>19.37252054004068</v>
+        <v>18.96872899903276</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>18.91729212807279</v>
+        <v>18.52340578337172</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>18.69488112350717</v>
+        <v>18.30582955046258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 6.51%</t>
+          <t>terminal 6.58%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>17.29397218329119</v>
+        <v>16.9769342449448</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>17.08903799568018</v>
+        <v>16.77594593445009</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>16.88724745936135</v>
+        <v>16.57803794656374</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>16.68854067526362</v>
+        <v>16.38315163596903</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>16.49285911301655</v>
+        <v>16.19122969638736</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 7.01%</t>
+          <t>terminal 7.08%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>15.49464229835749</v>
+        <v>15.24111786768624</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>15.31151713461568</v>
+        <v>15.06115727875821</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>15.13119469679048</v>
+        <v>14.88394848792242</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>14.95362165989702</v>
+        <v>14.70943918108711</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>14.77874591614142</v>
+        <v>14.53757823737439</v>
       </c>
     </row>
     <row r="20">
@@ -3009,23 +3009,23 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Beta (regression CI ends, then priors)  (0.38 / 0.47 / 0.57 / 0.65 / 0.80)</t>
+          <t>Beta (regression CI ends, then priors)  (0.35 / 0.49 / 0.62 / 0.65 / 0.80)</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>19.48137947908612</v>
+        <v>20.32335523048614</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>17.2964558290179</v>
+        <v>16.97182721463749</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>15.43856588369844</v>
+        <v>14.63874519231965</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>14.18617784829437</v>
+        <v>14.19258854611788</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>12.29906647699883</v>
+        <v>12.30464777997424</v>
       </c>
       <c r="H22" s="10">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -3039,19 +3039,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>20.51089199503732</v>
+        <v>20.08425161688863</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>17.82904430427011</v>
+        <v>17.45699457818922</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>16.67968100822702</v>
+        <v>16.33102727588947</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>15.49200560231583</v>
+        <v>15.16752773017973</v>
       </c>
       <c r="H23" s="10">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -3065,19 +3065,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>17.14659176130132</v>
+        <v>16.79007037820718</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>18.14487071702368</v>
+        <v>17.76721045267956</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>20.14142862846841</v>
+        <v>19.72149060162431</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>21.13970758419079</v>
+        <v>20.69863067609671</v>
       </c>
       <c r="H24" s="10">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -3091,19 +3091,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>18.19201125855779</v>
+        <v>17.81339064467879</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>18.66758046565191</v>
+        <v>18.27887058591536</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>19.61871887984017</v>
+        <v>19.20983046838851</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>20.0942880869343</v>
+        <v>19.67531040962509</v>
       </c>
       <c r="H25" s="10">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -3117,19 +3117,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>16.60110760867058</v>
+        <v>16.25397004432989</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>17.87212864070831</v>
+        <v>17.49916028574091</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>20.41417070478379</v>
+        <v>19.98954076856297</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>21.68519173682152</v>
+        <v>21.23473100997399</v>
       </c>
       <c r="H26" s="10">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>20.20687199725451</v>
+        <v>19.79009448877729</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>19.67501083500027</v>
+        <v>19.26722250796461</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>18.43400145640707</v>
+        <v>18.04718788606837</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>17.7248532400681</v>
+        <v>17.35002524498481</v>
       </c>
       <c r="H27" s="10">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -3169,19 +3169,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>19.357486821725</v>
+        <v>18.95677077543478</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>19.26065510581214</v>
+        <v>18.86080506331326</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>19.03471443534881</v>
+        <v>18.63688506836304</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>18.90560548079834</v>
+        <v>18.50893078553434</v>
       </c>
       <c r="H28" s="10">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -3195,19 +3195,19 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>18.3125403160204</v>
+        <v>17.93340585281933</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>18.77621646179244</v>
+        <v>18.38610446256195</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>19.3326278367189</v>
+        <v>18.9293427942531</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>19.51264328154805</v>
+        <v>19.10509637215317</v>
       </c>
       <c r="H29" s="10">
         <f>MAX(B29:F29)-MIN(B29:F29)</f>
@@ -3221,19 +3221,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>15.85515972490487</v>
+        <v>15.59424768185649</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>17.29553191126147</v>
+        <v>16.9778093008496</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>19.14314967274604</v>
+        <v>18.74435052715193</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>21.60109684626675</v>
+        <v>21.08026724450918</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>25.03440858808661</v>
+        <v>24.31633715735939</v>
       </c>
       <c r="H30" s="10">
         <f>MAX(B30:F30)-MIN(B30:F30)</f>
@@ -4428,14 +4428,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>10.96831911684814</v>
+        <v>10.8043265630865</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C63</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>29.5836887762623</v>
+        <v>28.73460090831387</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>0.45</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>10.96831911684814</v>
+        <v>10.8043265630865</v>
       </c>
     </row>
     <row r="7">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>29.5836887762623</v>
+        <v>28.73460090831387</v>
       </c>
     </row>
     <row r="8">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>16.29100563856143</v>
+        <v>15.94943075692926</v>
       </c>
     </row>
     <row r="20">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>9.880840632384245</v>
+        <v>9.870305228843574</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>7.824672505907397</v>
+        <v>7.816244183074859</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>11.59431407111495</v>
+        <v>11.58202276698417</v>
       </c>
     </row>
     <row r="25">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>19.32322520531152</v>
+        <v>18.92260719840512</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>10.18651185142768</v>
+        <v>10.05001098034791</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.53703290327117</v>
+        <v>21.99805621498489</v>
       </c>
     </row>
     <row r="26">
@@ -5057,13 +5057,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>19.03983619933884</v>
+        <v>18.64224021374001</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>12.64250308760287</v>
+        <v>12.40309632862426</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>21.32461654325951</v>
+        <v>20.87930903938881</v>
       </c>
     </row>
     <row r="27">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>18.08892923382408</v>
+        <v>17.73214262802726</v>
       </c>
     </row>
   </sheetData>
@@ -5776,11 +5776,11 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Beta (DU weekly vs DFM General Index, 5y)</t>
+          <t>Beta (DU weekly vs FTSE ADX General, 5y)</t>
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>0.472</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="53">
@@ -8211,7 +8211,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Beta (DU weekly vs its own index, the DFM General, 5 years)</t>
+          <t>Beta (DU weekly vs the FTSE ADX General, 5 years)</t>
         </is>
       </c>
       <c r="C38" s="39">

--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -34,10 +34,10 @@
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.00;(0.00);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.00x"/>
+    <numFmt numFmtId="166" formatCode="0.00x"/>
+    <numFmt numFmtId="167" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
   <fonts count="11">
@@ -139,33 +139,33 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -753,157 +753,244 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>The fiscal regime — the study's contested judgement. The 38% federal royalty + 9% corporate tax regime</t>
+          <t>The contested judgement — the required return. This is the one judgement that moves the answer more</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>(43.6% combined take) is legislated for 2024-2026 only. The base model carries it forward (Framing A);</t>
+          <t>than any other, so it is computed BOTH WAYS on the Fundamental Valuation sheet and never averaged.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>the Fundamental Valuation sheet also shows the DCF under a reversion to the pre-2024 construction</t>
+          <t>Framing 1 takes du's own measured beta and capitalises the terminal at the Gordon rate. Framing 2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>(Framing B, a 51-52% take). Both are shown; they are never averaged.</t>
+          <t>refuses the re-rating that implies and holds du's CURRENT trailing EV/EBITDA into perpetuity instead.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>The gap between them is the study, and it is published, not resolved. (The post-2026 fiscal regime</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>was the prior edition's contested judgement; it is no longer contested — du disclosed the 2027-2029</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>extension itself on 24 July 2026 on the same structure, with the AED 1.8bn combined floor retained.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr"/>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>A reversion after 2029 is still priced, as a named tail, on the same sheet.)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
-        </is>
-      </c>
+      <c r="A41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>financial statements read from investors.du.ae, and H1-2026 from the KPMG-reviewed interims — every</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>income-statement, balance-sheet and segment line is the filed figure. Segment revenue ties EXACTLY to</t>
+          <t>shown as ranges.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>consolidated revenue in every year (Note 38). du carries ZERO drawn borrowings in every year studied; the</t>
-        </is>
-      </c>
+      <c r="A44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>only debt-like item is IFRS-16 lease liabilities, and the bridge treats them as debt. Every input is</t>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
+          <t>financial statements read from investors.du.ae, and H1-2026 from the KPMG-reviewed interims — every</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr"/>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>income-statement, balance-sheet and segment line is the filed figure. Segment revenue ties EXACTLY to</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+          <t>consolidated revenue in every year (Note 38). du carries ZERO drawn borrowings in every year studied; the</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6.32% -&gt; 6.08% on the AED risk-free path (du has no debt whose cost could define the</t>
+          <t>only debt-like item is IFRS-16 lease liabilities, and the bridge treats them as debt. Every input is</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>glide); the terminal value is capitalised at the terminal rate and discounted at the year-5 cumulative</t>
+          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>factor. One date, one price of time: the bridge is dated 31-Dec-2025 and rolled to the 07-Aug-2026 anchor</t>
-        </is>
-      </c>
+      <c r="A51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>at the cost of equity, net of the AED 0.40 final dividend paid 28-Apr-2026.</t>
+          <t>Leases are debt, and charged once. du has no drawn borrowings; its only debt-like item is the IFRS-16</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr"/>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>lease liability. That liability is deducted in the enterprise-to-equity bridge and carries a debt</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Currency. AED million unless stated. Spot AED 12.30 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
+          <t>weight in the cost of capital, so NO lease charge belongs in the cash-flow waterfall as well —</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>perpetual renewal is already paid for in the terminal, where invested capital includes the</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+          <t>right-of-use asset and terminal reinvestment maintains it. The right-of-use book is held flat because</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>a new lease creates an asset and a liability together and is non-cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Discount convention, stated. Each explicit year is discounted at its own forward cost of capital,</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>at full-year END-of-period factors, gliding 6.41% -&gt; 6.17% on the AED risk-free path (du has no debt whose cost could</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>define the glide); the terminal value, a value dated at the end of year five, is discounted at the</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>year-five factor. A mid-year convention would raise the answer and is not adopted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>One date, one price of time: the bridge is dated 31-Dec-2025 and rolled to the 07-Aug-2026 anchor at</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>the cost of equity, net of the AED 0.66 of dividends whose EX-dates fall in that</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>window (the 0.40 final, paid 28-Apr-2026, and the 0.26 interim, ex 31-Jul-2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Currency. AED million unless stated. Spot AED 12.30 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -1010,13 +1097,13 @@
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="23" t="n">
         <v>9722.700000000001</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="23" t="n">
         <v>9838.448</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="23" t="n">
         <v>10288.767</v>
       </c>
       <c r="E5" s="31">
@@ -1046,13 +1133,13 @@
           <t xml:space="preserve">  of which depreciation charge (memo)</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>1544.182</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>1569.189</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <v>1557.989</v>
       </c>
       <c r="E6" s="31">
@@ -1082,33 +1169,33 @@
           <t>Right-of-use assets</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>1597.185</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>1657.217</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <v>1515.395</v>
       </c>
       <c r="E7" s="31">
-        <f>D7+Assumptions!$B$45-Assumptions!$B$45</f>
+        <f>$D$7</f>
         <v/>
       </c>
       <c r="F7" s="31">
-        <f>E7+Assumptions!$C$45-Assumptions!$C$45</f>
+        <f>$D$7</f>
         <v/>
       </c>
       <c r="G7" s="31">
-        <f>F7+Assumptions!$D$45-Assumptions!$D$45</f>
+        <f>$D$7</f>
         <v/>
       </c>
       <c r="H7" s="31">
-        <f>G7+Assumptions!$E$45-Assumptions!$E$45</f>
+        <f>$D$7</f>
         <v/>
       </c>
       <c r="I7" s="31">
-        <f>H7+Assumptions!$F$45-Assumptions!$F$45</f>
+        <f>$D$7</f>
         <v/>
       </c>
     </row>
@@ -1118,13 +1205,13 @@
           <t>Intangible assets (excl. goodwill)</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>1110.769</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>846.932</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>869.6</v>
       </c>
       <c r="E8" s="31">
@@ -1154,13 +1241,13 @@
           <t xml:space="preserve">  of which amortisation charge (memo)</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>209.053</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>209.896</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>245.881</v>
       </c>
       <c r="E9" s="31">
@@ -1195,10 +1282,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>413.22</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>413.22</v>
       </c>
       <c r="E10" s="31">
@@ -1228,13 +1315,13 @@
           <t>Net working capital (royalty accrual excluded)</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>-964.8510000000001</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>-1220.184</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <v>-1062.442</v>
       </c>
       <c r="E11" s="31">
@@ -1264,33 +1351,33 @@
           <t>Cash and term deposits</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <v>1936.622</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>2283.252</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>2249.719</v>
       </c>
       <c r="E12" s="31">
-        <f>D12+'Income Statement'!E18-'Income Statement'!E11+DCF!B12+DCF!B13+DCF!B14-'Income Statement'!E18*Assumptions!$C$65</f>
+        <f>D12+'Income Statement'!E18-'Income Statement'!E11+DCF!B12+DCF!B14-'Income Statement'!E18*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="F12" s="31">
-        <f>E12+'Income Statement'!F18-'Income Statement'!F11+DCF!C12+DCF!C13+DCF!C14-'Income Statement'!F18*Assumptions!$C$65</f>
+        <f>E12+'Income Statement'!F18-'Income Statement'!F11+DCF!C12+DCF!C14-'Income Statement'!F18*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="G12" s="31">
-        <f>F12+'Income Statement'!G18-'Income Statement'!G11+DCF!D12+DCF!D13+DCF!D14-'Income Statement'!G18*Assumptions!$C$65</f>
+        <f>F12+'Income Statement'!G18-'Income Statement'!G11+DCF!D12+DCF!D14-'Income Statement'!G18*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="H12" s="31">
-        <f>G12+'Income Statement'!H18-'Income Statement'!H11+DCF!E12+DCF!E13+DCF!E14-'Income Statement'!H18*Assumptions!$C$65</f>
+        <f>G12+'Income Statement'!H18-'Income Statement'!H11+DCF!E12+DCF!E14-'Income Statement'!H18*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="I12" s="31">
-        <f>H12+'Income Statement'!I18-'Income Statement'!I11+DCF!F12+DCF!F13+DCF!F14-'Income Statement'!I18*Assumptions!$C$65</f>
+        <f>H12+'Income Statement'!I18-'Income Statement'!I11+DCF!F12+DCF!F14-'Income Statement'!I18*Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -1300,13 +1387,13 @@
           <t>Lease liabilities (the only debt-like item)</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="23" t="n">
         <v>2104.959</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>1998.687</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>1938.819</v>
       </c>
       <c r="E13" s="31">
@@ -1582,10 +1669,10 @@
           <t>Federal royalty and income tax paid</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>-1928.939</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>-1883.442</v>
       </c>
     </row>
@@ -1595,10 +1682,10 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>4636.508</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>5229.823</v>
       </c>
     </row>
@@ -1608,10 +1695,10 @@
           <t>Purchase of PP&amp;E and intangibles</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>-1920.468</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>-2353.23</v>
       </c>
     </row>
@@ -1729,7 +1816,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Lease replacement</t>
+          <t>Memo — lease replacement, NOT deducted (leases are debt)</t>
         </is>
       </c>
       <c r="B12" s="31" t="inlineStr">
@@ -1816,23 +1903,23 @@
         </is>
       </c>
       <c r="D14" s="28">
-        <f>D9+D10+D11+D12+D13</f>
+        <f>D9+D10+D11+D13</f>
         <v/>
       </c>
       <c r="E14" s="28">
-        <f>E9+E10+E11+E12+E13</f>
+        <f>E9+E10+E11+E13</f>
         <v/>
       </c>
       <c r="F14" s="28">
-        <f>F9+F10+F11+F12+F13</f>
+        <f>F9+F10+F11+F13</f>
         <v/>
       </c>
       <c r="G14" s="28">
-        <f>G9+G10+G11+G12+G13</f>
+        <f>G9+G10+G11+G13</f>
         <v/>
       </c>
       <c r="H14" s="28">
-        <f>H9+H10+H11+H12+H13</f>
+        <f>H9+H10+H11+H13</f>
         <v/>
       </c>
       <c r="I14" s="15" t="n"/>
@@ -1843,10 +1930,10 @@
           <t>Dividends paid</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="23" t="n">
         <v>-1858.491</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>-2629.085</v>
       </c>
       <c r="D16" s="31">
@@ -2608,7 +2695,7 @@
           <t>Simulated paths</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -2729,111 +2816,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>5.17%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>19.66933438309751</v>
+        <v>19.06791132189714</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>22.15174913365529</v>
+        <v>21.37770179903905</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>25.59094934303363</v>
+        <v>24.54678331325201</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>30.67626651149073</v>
+        <v>29.16801637590067</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>38.96850852166403</v>
+        <v>36.54253626892263</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>17.38248029009414</v>
+        <v>16.9089976587036</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>19.20400769626519</v>
+        <v>18.6155317982148</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>21.61270757502213</v>
+        <v>20.85598439344367</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>24.94969675636998</v>
+        <v>23.9298500153909</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>29.88377622565962</v>
+        <v>28.41213486321618</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>6.17%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>15.59424768185649</v>
+        <v>15.21123251125888</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>16.9778093008496</v>
+        <v>16.51421550641088</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>21.08026724450918</v>
+        <v>20.34064834723247</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>24.31633715735939</v>
+        <v>23.3205014656016</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>6.58%</t>
+          <t>6.67%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>14.15746739328381</v>
+        <v>13.8409344488351</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>15.23694854926923</v>
+        <v>14.86168326427922</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>16.57803794656374</v>
+        <v>16.12420719306396</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>18.29028721846222</v>
+        <v>17.72721419544651</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>20.55433959378778</v>
+        <v>19.83160815367896</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>7.08%</t>
+          <t>7.17%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>12.97770025312425</v>
+        <v>12.71154180540853</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13.83817789141263</v>
+        <v>13.52783883937458</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>14.88394848792242</v>
+        <v>14.51633438136042</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>16.18310131865233</v>
+        <v>15.73890953549209</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>17.84174327636619</v>
+        <v>17.29113046957509</v>
       </c>
     </row>
     <row r="12">
@@ -2847,138 +2934,138 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>5.32%</t>
+          <t>5.41%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>5.82%</t>
+          <t>5.91%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>6.32%</t>
+          <t>6.41%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>6.82%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>7.32%</t>
+          <t>7.41%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 5.08%</t>
+          <t>terminal 5.17%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>26.21186590655091</v>
+        <v>25.1462633087418</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>25.89899335245586</v>
+        <v>24.84419724656098</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>25.59094934303363</v>
+        <v>24.54678331325201</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>25.28764153760843</v>
+        <v>24.25393267170437</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>24.98897971072595</v>
+        <v>23.96555851731982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 5.58%</t>
+          <t>terminal 5.67%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>22.13562242012934</v>
+        <v>21.3646021781526</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>21.87213658041468</v>
+        <v>21.10832472550778</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>21.61270757502213</v>
+        <v>20.85598439344367</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>21.35725793786072</v>
+        <v>20.60750611688699</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>21.10571197540687</v>
+        <v>20.36281654625054</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 6.08%</t>
+          <t>terminal 6.17%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>19.19660794179827</v>
+        <v>18.61111868087366</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>18.96872899903276</v>
+        <v>18.38817967730395</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>18.52340578337172</v>
+        <v>17.95248626582393</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>18.30582955046258</v>
+        <v>17.73960326570264</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 6.58%</t>
+          <t>terminal 6.67%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>16.9769342449448</v>
+        <v>16.51634027063411</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>16.77594593445009</v>
+        <v>16.31876346535764</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>16.57803794656374</v>
+        <v>16.12420719306396</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>16.38315163596903</v>
+        <v>15.93261404240899</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>16.19122969638736</v>
+        <v>15.74392791117709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 7.08%</t>
+          <t>terminal 7.17%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>15.24111786768624</v>
+        <v>14.86888784166854</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>15.06115727875821</v>
+        <v>14.69125655499216</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>14.88394848792242</v>
+        <v>14.51633438136042</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>14.70943918108711</v>
+        <v>14.34406990701374</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>14.53757823737439</v>
+        <v>14.17441288927764</v>
       </c>
     </row>
     <row r="20">
@@ -3013,19 +3100,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>20.32335523048614</v>
+        <v>21.54661639430977</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>16.97182721463749</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>14.63874519231965</v>
+        <v>15.78099116792509</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>14.19258854611788</v>
+        <v>15.32091216868629</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>12.30464777997424</v>
+        <v>13.36132449902587</v>
       </c>
       <c r="H22" s="10">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -3035,23 +3122,23 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Combined fiscal take (Framing B ~51.5%)  (40.0% / 43.6% / 47.0% / 50.0% / 53.1%)</t>
+          <t>Combined fiscal take (top of grid = the pre-2024 construction's FY2023 take)  (40.0% / 43.6% / 47.0% / 50.0% / 53.1%)</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>20.08425161688863</v>
+        <v>19.46457070713711</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>17.45699457818922</v>
+        <v>16.92356386654856</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>16.33102727588947</v>
+        <v>15.83456093486775</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>15.16752773017973</v>
+        <v>14.70925790546425</v>
       </c>
       <c r="H23" s="10">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -3061,23 +3148,23 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Blended ARPU multiplier  (0.92x / 0.96x / 1.00x / 1.04x / 1.08x)</t>
+          <t>Blended ARPU multiplier — applied to BOTH the mobile ARPU and the implied fixed revenue-per-subscriber paths  (0.92x / 0.96x / 1.00x / 1.04x / 1.08x)</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>16.79007037820718</v>
+        <v>16.26460079390747</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>17.76721045267956</v>
+        <v>17.21662900617221</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>19.72149060162431</v>
+        <v>19.12068543070169</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>20.69863067609671</v>
+        <v>20.07271364296644</v>
       </c>
       <c r="H24" s="10">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -3087,23 +3174,23 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Subscriber path shift ('000)  (-400 / -200 / +0 / +200 / +400)</t>
+          <t>Subscriber path shift ('000) — applied in full to the mobile base and at 8% of that to the fixed base  (-400 / -200 / +0 / +200 / +400)</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>17.81339064467879</v>
+        <v>17.26166853343523</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>18.27887058591536</v>
+        <v>17.71516287593608</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>19.20983046838851</v>
+        <v>18.62215156093781</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>19.67531040962509</v>
+        <v>19.07564590343867</v>
       </c>
       <c r="H25" s="10">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -3117,19 +3204,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>16.25397004432989</v>
+        <v>15.7396549927263</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>17.49916028574091</v>
+        <v>16.95415610558162</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>19.98954076856297</v>
+        <v>19.38315833129229</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>21.23473100997399</v>
+        <v>20.59765944414761</v>
       </c>
       <c r="H26" s="10">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -3143,19 +3230,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>19.79009448877729</v>
+        <v>19.19302743416895</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>19.26722250796461</v>
+        <v>18.68084232630295</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>18.04718788606837</v>
+        <v>17.48574374128228</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>17.35002524498481</v>
+        <v>16.80283026412761</v>
       </c>
       <c r="H27" s="10">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -3169,19 +3256,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>18.95677077543478</v>
+        <v>18.37879766603091</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>18.86080506331326</v>
+        <v>18.28386190608378</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.63688506836304</v>
+        <v>18.06234513287381</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>18.50893078553434</v>
+        <v>17.93576411961097</v>
       </c>
       <c r="H28" s="10">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -3191,23 +3278,23 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital  (18.0% / 22.0% / 26.7% / 30.0% / 34.0%)</t>
+          <t>Terminal return on invested capital  (18.0% / 22.0% / 26.5% / 30.0% / 34.0%)</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>17.93340585281933</v>
+        <v>17.4011105551553</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>18.38610446256195</v>
+        <v>17.83712906627904</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>18.9293427942531</v>
+        <v>18.36035127962752</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>19.10509637215317</v>
+        <v>18.52962905453439</v>
       </c>
       <c r="H29" s="10">
         <f>MAX(B29:F29)-MIN(B29:F29)</f>
@@ -3221,19 +3308,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>15.59424768185649</v>
+        <v>15.21123251125888</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>16.9778093008496</v>
+        <v>16.51421550641088</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>18.74435052715193</v>
+        <v>18.16865721843695</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>21.08026724450918</v>
+        <v>20.34064834723247</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>24.31633715735939</v>
+        <v>23.3205014656016</v>
       </c>
       <c r="H30" s="10">
         <f>MAX(B30:F30)-MIN(B30:F30)</f>
@@ -3904,15 +3991,15 @@
           <t>Mobile subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n">
         <v>8916</v>
       </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="23" t="n">
         <v>9704</v>
       </c>
       <c r="E21" s="18">
@@ -3942,15 +4029,15 @@
           <t>Fixed subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n">
         <v>682</v>
       </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="23" t="n">
         <v>735</v>
       </c>
       <c r="E22" s="18">
@@ -3985,10 +4072,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="24" t="n">
         <v>65.8</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="24" t="n">
         <v>63.3</v>
       </c>
       <c r="E23" s="42">
@@ -4015,7 +4102,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Mobile subscriber history: 8,916k (Q4-2024), 9,704k (Q4-2025) — the FY2024 column carries the Q4-2024 base and the ARPU column the company's quarterly prints (65.8 Q4-2024, 63.3 FY2025). Q2-2026 actual: 9,280k after the war quarter (−412k), the base the forecast recovers from.</t>
+          <t>Subscriber and ARPU history are the company's own year-end prints; FY2023 is not shown because the KPI series in the current disclosure pack starts at Q4-2024. The Q2-2026 actual mobile base is 9,280k after the war quarter (total base −412k on the quarter), which is the base the forecast recovers from.</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4196,7 @@
           <t>~4.8%</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>the other half of the duopoly; scale, international assets and a higher multiple</t>
         </is>
@@ -4136,7 +4223,7 @@
           <t>~5.2%</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>regional benchmark payer; the yield anchor for the cross-check</t>
         </is>
@@ -4163,7 +4250,7 @@
           <t>~2.9%</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>closest structural analogue — the #2 operator that closed the gap; the justified P/E</t>
         </is>
@@ -4190,7 +4277,7 @@
           <t>~4.6%</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>multi-market; softer growth, lower multiple</t>
         </is>
@@ -4217,7 +4304,7 @@
           <t>~6-7%</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>levered multi-market; the low end of the bracket</t>
         </is>
@@ -4244,7 +4331,7 @@
           <t>~6.7%</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>small-market incumbent; yield-heavy</t>
         </is>
@@ -4271,7 +4358,7 @@
           <t>3.4% / n/m</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>the developed-market bracket: slower growth, more leverage, lower returns</t>
         </is>
@@ -4428,14 +4515,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>10.8043265630865</v>
+        <v>10.54402485670467</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C63</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>28.73460090831387</v>
+        <v>27.58617162391559</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>0.45</v>
@@ -4546,7 +4633,7 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>MIN(B5:B8)</f>
+        <f>B5*E5+B6*E6+B7*E7+B8*E8</f>
         <v/>
       </c>
       <c r="C9" s="13">
@@ -4554,7 +4641,7 @@
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>MAX(D5:D8)</f>
+        <f>D5*E5+D6*E6+D7*E7+D8*E8</f>
         <v/>
       </c>
       <c r="E9" s="14">
@@ -4567,14 +4654,29 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Span across lenses (min/max — NOT weighted)</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <f>MIN(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="D10" s="10">
+        <f>MAX(D5:D8)</f>
+        <v/>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Alternative reading — the fiscal regime reverts (Framing B DCF)</t>
+          <t>Contested judgement, other way — no terminal re-rating (Framing 2)</t>
         </is>
       </c>
       <c r="C11" s="8">
-        <f>'Fundamental Valuation'!C19</f>
+        <f>'Fundamental Valuation'!C18</f>
         <v/>
       </c>
       <c r="G11" s="11">
@@ -4825,7 +4927,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>10.8043265630865</v>
+        <v>10.54402485670467</v>
       </c>
     </row>
     <row r="7">
@@ -4840,7 +4942,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>28.73460090831387</v>
+        <v>27.58617162391559</v>
       </c>
     </row>
     <row r="8">
@@ -4851,7 +4953,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>15.5x justified P/E on FY2026E earnings</t>
+          <t>12.9x justified P/E on FY2026E earnings</t>
         </is>
       </c>
       <c r="C8" s="8">
@@ -4867,7 +4969,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>15.5x normalised earnings per share</t>
+          <t>12.9x normalised earnings per share</t>
         </is>
       </c>
       <c r="C9" s="8">
@@ -4906,67 +5008,70 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>THE CONTESTED JUDGEMENT — THE POST-2026 FISCAL REGIME, BOTH WAYS</t>
+          <t>THE CONTESTED JUDGEMENT — THE REQUIRED RETURN, BOTH WAYS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Framing A (base): 38% royalty + 9% tax persist — combined take</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0.4357</v>
+          <t>Framing 1: du's own measured beta sets the cost of equity</t>
+        </is>
+      </c>
+      <c r="C15" s="8">
+        <f>DCF!C63</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Fair value under Framing A (the primary DCF)</t>
-        </is>
-      </c>
-      <c r="C16" s="8">
-        <f>DCF!C63</f>
-        <v/>
+          <t xml:space="preserve">  the terminal that implies — exit multiple on terminal EBITDA</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>9.951572188319338</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Framing B: reversion to the pre-2024 construction — year-1 take</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0.5150067266977971</v>
+          <t xml:space="preserve">  against du's OWN current trailing EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>7.555316462511931</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  15% of regulated revenue (69.0% share) + 30% of the regulated profit remainder</t>
-        </is>
+          <t>Framing 2: no terminal re-rating — du's current multiple held in perpetuity</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>14.40369208593501</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Fair value under Framing B (engine re-run of the same DCF)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>15.94943075692926</v>
+          <t>The judgement is worth (Framing 1 less Framing 2, per share)</t>
+        </is>
+      </c>
+      <c r="C19" s="10">
+        <f>C15-C18</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>The judgement is worth (A minus B, per share)</t>
-        </is>
-      </c>
-      <c r="C20" s="10">
-        <f>C16-C19</f>
-        <v/>
+          <t>Post-2029 fiscal tail: the pre-2024 royalty construction returns after the disclosed 2027-2029 extension lapses</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>15.21787551300283</v>
       </c>
     </row>
     <row r="22">
@@ -5015,13 +5120,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>9.870305228843574</v>
+        <v>9.547737257681046</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>7.816244183074859</v>
+        <v>7.506189806144837</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>11.58202276698417</v>
+        <v>11.24902680062789</v>
       </c>
     </row>
     <row r="25">
@@ -5036,13 +5141,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>18.92260719840512</v>
+        <v>18.01764358863624</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>10.05001098034791</v>
+        <v>9.532883848370837</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>21.99805621498489</v>
+        <v>20.90712024622747</v>
       </c>
     </row>
     <row r="26">
@@ -5057,13 +5162,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>18.64224021374001</v>
+        <v>17.73742567320945</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>12.40309632862426</v>
+        <v>11.75234569627446</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>20.87930903938881</v>
+        <v>19.86591675399459</v>
       </c>
     </row>
     <row r="27">
@@ -5088,13 +5193,13 @@
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>There is no liquid 10-year AED government point. The base model uses the Jan-2031 AED T-bond (4.48%); discounting instead at the peg-extrapolated 10-year proxy (4.69%) is an engine re-run worth the figure at right</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>17.73214262802726</v>
+        <v>17.21272776016761</v>
       </c>
     </row>
   </sheetData>
@@ -5205,7 +5310,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>4532.905989</v>
       </c>
     </row>
@@ -5269,19 +5374,19 @@
           <t>Mobile subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="23" t="n">
         <v>9450</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>9760</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>10010</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="23" t="n">
         <v>10240</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>10450</v>
       </c>
     </row>
@@ -5291,19 +5396,19 @@
           <t>Fixed subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="23" t="n">
         <v>760</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>790</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <v>815</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="23" t="n">
         <v>838</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>858</v>
       </c>
     </row>
@@ -5313,19 +5418,19 @@
           <t>Blended mobile ARPU (AED/month)</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="24" t="n">
         <v>63.4</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="24" t="n">
         <v>63.6</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="24" t="n">
         <v>63.8</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="24" t="n">
         <v>64</v>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="F15" s="24" t="n">
         <v>64.2</v>
       </c>
     </row>
@@ -5335,19 +5440,19 @@
           <t>Implied fixed revenue per subscriber (AED/month)</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="23" t="n">
         <v>537</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>545</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>553</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="23" t="n">
         <v>561</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="23" t="n">
         <v>569</v>
       </c>
     </row>
@@ -5517,8 +5622,8 @@
           <t>Staff cost, FY2026E level (AED mn)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n">
-        <v>985</v>
+      <c r="C27" s="23" t="n">
+        <v>1035.16</v>
       </c>
     </row>
     <row r="28">
@@ -5537,7 +5642,7 @@
           <t>Network &amp; maintenance, FY2025 base (AED mn, audited)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="23" t="n">
         <v>963.878</v>
       </c>
     </row>
@@ -5557,7 +5662,7 @@
           <t>Administrative expense, FY2025 base (AED mn, audited)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n">
+      <c r="C31" s="23" t="n">
         <v>189.654</v>
       </c>
     </row>
@@ -5577,7 +5682,7 @@
           <t>Other operating expense, FY2025 base (AED mn, audited)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="23" t="n">
         <v>133.192</v>
       </c>
     </row>
@@ -5627,7 +5732,7 @@
           <t>Other operating income (AED mn/yr)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="n">
+      <c r="C38" s="23" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5700,22 +5805,22 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Right-of-use depreciation = lease replacement capex (AED mn)</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="n">
+          <t>Right-of-use depreciation, matched by non-cash lease additions (AED mn)</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="n">
         <v>355</v>
       </c>
-      <c r="C45" s="22" t="n">
+      <c r="C45" s="23" t="n">
         <v>350</v>
       </c>
-      <c r="D45" s="22" t="n">
+      <c r="D45" s="23" t="n">
         <v>345</v>
       </c>
-      <c r="E45" s="22" t="n">
+      <c r="E45" s="23" t="n">
         <v>340</v>
       </c>
-      <c r="F45" s="22" t="n">
+      <c r="F45" s="23" t="n">
         <v>335</v>
       </c>
     </row>
@@ -5760,7 +5865,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>0.0042</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="51">
@@ -5770,7 +5875,7 @@
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>0.0487</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="52">
@@ -5779,7 +5884,7 @@
           <t>Beta (DU weekly vs FTSE ADX General, 5y)</t>
         </is>
       </c>
-      <c r="C52" s="24" t="n">
+      <c r="C52" s="25" t="n">
         <v>0.488</v>
       </c>
     </row>
@@ -5832,7 +5937,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>0.0487</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="57">
@@ -5885,7 +5990,7 @@
           <t>Lease liabilities at FY2025 (AED mn, audited — the only debt-like item)</t>
         </is>
       </c>
-      <c r="C62" s="22" t="n">
+      <c r="C62" s="23" t="n">
         <v>1938.819</v>
       </c>
     </row>
@@ -5895,7 +6000,7 @@
           <t>Cash and term deposits at FY2025 (AED mn, audited)</t>
         </is>
       </c>
-      <c r="C63" s="22" t="n">
+      <c r="C63" s="23" t="n">
         <v>2249.719</v>
       </c>
     </row>
@@ -5905,7 +6010,7 @@
           <t>Equity-accounted investees at carrying value (AED mn)</t>
         </is>
       </c>
-      <c r="C64" s="23" t="n">
+      <c r="C64" s="24" t="n">
         <v>0.511</v>
       </c>
     </row>
@@ -5942,11 +6047,11 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Final FY2025 dividend paid 28-Apr-2026 (AED/share)</t>
+          <t>Dividends gone ex between 31-Dec-2025 and the anchor (AED/share)</t>
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>0.4</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="69">
@@ -5955,7 +6060,7 @@
           <t>Days from the 31-Dec-2025 valuation date to the 07-Aug-2026 anchor</t>
         </is>
       </c>
-      <c r="C69" s="22" t="n">
+      <c r="C69" s="23" t="n">
         <v>219</v>
       </c>
     </row>
@@ -5979,8 +6084,8 @@
           <t>Justified price/earnings (GCC telecom peer median)</t>
         </is>
       </c>
-      <c r="C72" s="25" t="n">
-        <v>15.5</v>
+      <c r="C72" s="21" t="n">
+        <v>12.9</v>
       </c>
     </row>
     <row r="73">
@@ -5990,7 +6095,7 @@
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>0.052</v>
+        <v>0.0489</v>
       </c>
     </row>
     <row r="74">
@@ -6325,7 +6430,7 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="23" t="n">
         <v>7074.936</v>
       </c>
       <c r="C5" s="11">
@@ -6335,19 +6440,19 @@
       <c r="D5" s="9" t="n">
         <v>0.6082941244980873</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="23" t="n">
         <v>7208.76</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="23" t="n">
         <v>7330.536</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="23" t="n">
         <v>7567.956</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="23" t="n">
         <v>7776</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="23" t="n">
         <v>7969.788</v>
       </c>
     </row>
@@ -6357,7 +6462,7 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>4379.705</v>
       </c>
       <c r="C6" s="11">
@@ -6367,19 +6472,19 @@
       <c r="D6" s="9" t="n">
         <v>0.858015094623953</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="23" t="n">
         <v>4805.552</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="23" t="n">
         <v>5068.5</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="23" t="n">
         <v>5325.39</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="23" t="n">
         <v>5563.998</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="23" t="n">
         <v>5790.144</v>
       </c>
     </row>
@@ -6389,7 +6494,7 @@
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>2568.222</v>
       </c>
       <c r="C7" s="11">
@@ -6399,19 +6504,19 @@
       <c r="D7" s="9" t="n">
         <v>0.8642060538380248</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="23" t="n">
         <v>2547.676224</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="23" t="n">
         <v>2585.89136736</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="23" t="n">
         <v>2637.6091947072</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="23" t="n">
         <v>2690.361378601344</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="23" t="n">
         <v>2744.168606173371</v>
       </c>
     </row>
@@ -6421,7 +6526,7 @@
           <t>ICT and associated telecom services</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>1882.558</v>
       </c>
       <c r="C8" s="11">
@@ -6431,19 +6536,19 @@
       <c r="D8" s="9" t="n">
         <v>0.1939000020185301</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="23" t="n">
         <v>2031.280082</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="23" t="n">
         <v>2254.72089102</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="23" t="n">
         <v>2480.192980122</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="23" t="n">
         <v>2703.41034833298</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="23" t="n">
         <v>2919.683176199619</v>
       </c>
     </row>
@@ -7567,7 +7672,7 @@
         </is>
       </c>
       <c r="E35" s="10">
-        <f>((Assumptions!$C$74-0.04)/((DCF!C40+DCF!C50)/2+0.01-0.02))*C30*DCF!$C$62-Assumptions!$C$68</f>
+        <f>((Assumptions!$C$74-Assumptions!$C$59)/((DCF!C40+DCF!C50)/2+0.01-Assumptions!$C$59))*C30*DCF!$C$62-Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="F35" s="10">
@@ -7868,27 +7973,27 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Less lease replacement (at right-of-use depreciation)</t>
+          <t>Memo — lease replacement at right-of-use depreciation, NOT deducted (leases are debt)</t>
         </is>
       </c>
       <c r="B13" s="31">
-        <f>-Assumptions!$B$45</f>
+        <f>Assumptions!$B$45</f>
         <v/>
       </c>
       <c r="C13" s="31">
-        <f>-Assumptions!$C$45</f>
+        <f>Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="D13" s="31">
-        <f>-Assumptions!$D$45</f>
+        <f>Assumptions!$D$45</f>
         <v/>
       </c>
       <c r="E13" s="31">
-        <f>-Assumptions!$E$45</f>
+        <f>Assumptions!$E$45</f>
         <v/>
       </c>
       <c r="F13" s="31">
-        <f>-Assumptions!$F$45</f>
+        <f>Assumptions!$F$45</f>
         <v/>
       </c>
     </row>
@@ -7926,23 +8031,23 @@
         </is>
       </c>
       <c r="B15" s="28">
-        <f>B10+B11+B12+B13+B14</f>
+        <f>B10+B11+B12+B14</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>C10+C11+C12+C13+C14</f>
+        <f>C10+C11+C12+C14</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>D10+D11+D12+D13+D14</f>
+        <f>D10+D11+D12+D14</f>
         <v/>
       </c>
       <c r="E15" s="28">
-        <f>E10+E11+E12+E13+E14</f>
+        <f>E10+E11+E12+E14</f>
         <v/>
       </c>
       <c r="F15" s="28">
-        <f>F10+F11+F12+F13+F14</f>
+        <f>F10+F11+F12+F14</f>
         <v/>
       </c>
     </row>
@@ -8672,10 +8777,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>-4818.442</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <v>-5259.425</v>
       </c>
       <c r="E6" s="18">
@@ -8750,10 +8855,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>-3347.636</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>-3307.608</v>
       </c>
       <c r="E8" s="18">
@@ -8860,13 +8965,13 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>-2198.277</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>-2153.59</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <v>-2167.933</v>
       </c>
       <c r="E11" s="31">
@@ -8935,13 +9040,13 @@
           <t>Interest income</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="23" t="n">
         <v>61.327</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>82.214</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>74.672</v>
       </c>
       <c r="E13" s="31">
@@ -8971,13 +9076,13 @@
           <t>Interest expense (principally leases)</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="23" t="n">
         <v>-101.43</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>-89.77</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <v>-95.054</v>
       </c>
       <c r="E14" s="31">
@@ -9007,13 +9112,13 @@
           <t>Share of equity-accounted investments</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="23" t="n">
         <v>-2.72</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>-2.427</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="23" t="n">
         <v>-0.894</v>
       </c>
     </row>
@@ -9059,13 +9164,13 @@
           <t>Federal royalty and income tax</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="23" t="n">
         <v>-1890.65</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="23" t="n">
         <v>-1818.604</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="23" t="n">
         <v>-2244.037</v>
       </c>
       <c r="E17" s="31">

--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -31,14 +31,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.00;(0.00);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00x"/>
     <numFmt numFmtId="167" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -120,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,20 +150,23 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -531,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -736,232 +740,232 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>data-centre ramp respectively. Contribution margins are the audited Note 38 rates; the opex stack below</t>
+          <t>data-centre ramp respectively.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>them carries ONE escalator per cost class. Group EBITDA margin is an OUTPUT of all of this, not an input.</t>
-        </is>
-      </c>
+      <c r="A31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>How cost is built, and why no margin is an input. Direct cost is a COST PER UNIT, not a margin. Mobile</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>The contested judgement — the required return. This is the one judgement that moves the answer more</t>
+          <t>carries three separate per-subscriber lines - interconnect, commission, and devices - each with its own</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>than any other, so it is computed BOTH WAYS on the Fundamental Valuation sheet and never averaged.</t>
+          <t>escalator, because they are driven by physically different things: termination rates and messaging-app</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Framing 1 takes du's own measured beta and capitalises the terminal at the Gordon rate. Framing 2</t>
+          <t>substitution, the cost of winning a customer, and handset volume. Fixed carries a per-subscriber capacity</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>refuses the re-rating that implies and holds du's CURRENT trailing EV/EBITDA into perpetuity instead.</t>
+          <t>cost. Wholesale and ICT carry a cost rate on their own revenue because the company discloses no volume</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>The gap between them is the study, and it is published, not resolved. (The post-2026 fiscal regime</t>
+          <t>unit for either - that gap is flagged rather than filled. Every rate is anchored on the H1-2026 reviewed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>was the prior edition's contested judgement; it is no longer contested — du disclosed the 2027-2029</t>
+          <t>actual and held flat unless a named mechanism has a measured direction in the half-year pair. CONTRIBUTION</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>extension itself on 24 July 2026 on the same structure, with the AED 1.8bn combined floor retained.</t>
+          <t>MARGIN AND GROUP EBITDA MARGIN ARE THEREFORE OUTPUTS, computed on the Segments sheet, never typed in.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>A reversion after 2029 is still priced, as a named tail, on the same sheet.)</t>
-        </is>
-      </c>
+      <c r="A40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>The contested judgement — the required return. This is the one judgement that moves the answer more</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>than any other, so it is computed BOTH WAYS on the Fundamental Valuation sheet and never averaged.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>Framing 1 takes du's own measured beta and capitalises the terminal at the Gordon rate. Framing 2</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>refuses the re-rating that implies and holds du's CURRENT trailing EV/EBITDA into perpetuity instead.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
+          <t>The gap between them is the study, and it is published, not resolved. (The post-2026 fiscal regime</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>financial statements read from investors.du.ae, and H1-2026 from the KPMG-reviewed interims — every</t>
+          <t>was the prior edition's contested judgement; it is no longer contested — du disclosed the 2027-2029</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>income-statement, balance-sheet and segment line is the filed figure. Segment revenue ties EXACTLY to</t>
+          <t>extension itself on 24 July 2026 on the same structure, with the AED 1.8bn combined floor retained.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>consolidated revenue in every year (Note 38). du carries ZERO drawn borrowings in every year studied; the</t>
+          <t>A reversion after 2029 is still priced, as a named tail, on the same sheet.)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>only debt-like item is IFRS-16 lease liabilities, and the bridge treats them as debt. Every input is</t>
-        </is>
-      </c>
+      <c r="A49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr"/>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>shown as ranges.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Leases are debt, and charged once. du has no drawn borrowings; its only debt-like item is the IFRS-16</t>
-        </is>
-      </c>
+      <c r="A52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>lease liability. That liability is deducted in the enterprise-to-equity bridge and carries a debt</t>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>weight in the cost of capital, so NO lease charge belongs in the cash-flow waterfall as well —</t>
+          <t>financial statements read from investors.du.ae, and H1-2026 from the KPMG-reviewed interims — every</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>perpetual renewal is already paid for in the terminal, where invested capital includes the</t>
+          <t>income-statement, balance-sheet and segment line is the filed figure. Segment revenue ties EXACTLY to</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>right-of-use asset and terminal reinvestment maintains it. The right-of-use book is held flat because</t>
+          <t>consolidated revenue in every year (Note 38). du carries ZERO drawn borrowings in every year studied; the</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>a new lease creates an asset and a liability together and is non-cash.</t>
+          <t>only debt-like item is IFRS-16 lease liabilities, and the bridge treats them as debt. Every input is</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr"/>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Discount convention, stated. Each explicit year is discounted at its own forward cost of capital,</t>
-        </is>
-      </c>
+      <c r="A59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>at full-year END-of-period factors, gliding 6.41% -&gt; 6.17% on the AED risk-free path (du has no debt whose cost could</t>
+          <t>Leases are debt, and charged once. du has no drawn borrowings; its only debt-like item is the IFRS-16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>define the glide); the terminal value, a value dated at the end of year five, is discounted at the</t>
+          <t>lease liability. That liability is deducted in the enterprise-to-equity bridge and carries a debt</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>year-five factor. A mid-year convention would raise the answer and is not adopted.</t>
+          <t>weight in the cost of capital, so NO lease charge belongs in the cash-flow waterfall as well —</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>One date, one price of time: the bridge is dated 31-Dec-2025 and rolled to the 07-Aug-2026 anchor at</t>
+          <t>perpetual renewal is already paid for in the terminal, where invested capital includes the</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>the cost of equity, net of the AED 0.66 of dividends whose EX-dates fall in that</t>
+          <t>right-of-use asset and terminal reinvestment maintains it. The right-of-use book is held flat because</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>window (the 0.40 final, paid 28-Apr-2026, and the 0.26 interim, ex 31-Jul-2026).</t>
+          <t>a new lease creates an asset and a liability together and is non-cash.</t>
         </is>
       </c>
     </row>
@@ -971,26 +975,78 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Currency. AED million unless stated. Spot AED 12.30 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
+          <t>Discount convention, stated. Each explicit year is discounted at its own forward cost of capital,</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>at full-year END-of-period factors, gliding 6.41% -&gt; 6.17% on the AED risk-free path (du has no debt whose cost could</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+          <t>define the glide); the terminal value, a value dated at the end of year five, is discounted at the</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>year-five factor. A mid-year convention would raise the answer and is not adopted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>One date, one price of time: the bridge is dated 31-Dec-2025 and rolled to the 07-Aug-2026 anchor at</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>the cost of equity, net of the AED 0.66 of dividends whose EX-dates fall in that</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>window (the 0.40 final, paid 28-Apr-2026, and the 0.26 interim, ex 31-Jul-2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Currency. AED million unless stated. Spot AED 12.30 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -1107,23 +1163,23 @@
         <v>10288.767</v>
       </c>
       <c r="E5" s="31">
-        <f>D5-DCF!B12*Assumptions!$C$42-E6</f>
+        <f>D5-DCF!B12*Assumptions!$C$63-E6</f>
         <v/>
       </c>
       <c r="F5" s="31">
-        <f>E5-DCF!C12*Assumptions!$C$42-F6</f>
+        <f>E5-DCF!C12*Assumptions!$C$63-F6</f>
         <v/>
       </c>
       <c r="G5" s="31">
-        <f>F5-DCF!D12*Assumptions!$C$42-G6</f>
+        <f>F5-DCF!D12*Assumptions!$C$63-G6</f>
         <v/>
       </c>
       <c r="H5" s="31">
-        <f>G5-DCF!E12*Assumptions!$C$42-H6</f>
+        <f>G5-DCF!E12*Assumptions!$C$63-H6</f>
         <v/>
       </c>
       <c r="I5" s="31">
-        <f>H5-DCF!F12*Assumptions!$C$42-I6</f>
+        <f>H5-DCF!F12*Assumptions!$C$63-I6</f>
         <v/>
       </c>
     </row>
@@ -1143,23 +1199,23 @@
         <v>1557.989</v>
       </c>
       <c r="E6" s="31">
-        <f>Assumptions!$C$43*D5</f>
+        <f>Assumptions!$C$64*D5</f>
         <v/>
       </c>
       <c r="F6" s="31">
-        <f>Assumptions!$C$43*E5</f>
+        <f>Assumptions!$C$64*E5</f>
         <v/>
       </c>
       <c r="G6" s="31">
-        <f>Assumptions!$C$43*F5</f>
+        <f>Assumptions!$C$64*F5</f>
         <v/>
       </c>
       <c r="H6" s="31">
-        <f>Assumptions!$C$43*G5</f>
+        <f>Assumptions!$C$64*G5</f>
         <v/>
       </c>
       <c r="I6" s="31">
-        <f>Assumptions!$C$43*H5</f>
+        <f>Assumptions!$C$64*H5</f>
         <v/>
       </c>
     </row>
@@ -1215,23 +1271,23 @@
         <v>869.6</v>
       </c>
       <c r="E8" s="31">
-        <f>D8-DCF!B12*(1-Assumptions!$C$42)-E9</f>
+        <f>D8-DCF!B12*(1-Assumptions!$C$63)-E9</f>
         <v/>
       </c>
       <c r="F8" s="31">
-        <f>E8-DCF!C12*(1-Assumptions!$C$42)-F9</f>
+        <f>E8-DCF!C12*(1-Assumptions!$C$63)-F9</f>
         <v/>
       </c>
       <c r="G8" s="31">
-        <f>F8-DCF!D12*(1-Assumptions!$C$42)-G9</f>
+        <f>F8-DCF!D12*(1-Assumptions!$C$63)-G9</f>
         <v/>
       </c>
       <c r="H8" s="31">
-        <f>G8-DCF!E12*(1-Assumptions!$C$42)-H9</f>
+        <f>G8-DCF!E12*(1-Assumptions!$C$63)-H9</f>
         <v/>
       </c>
       <c r="I8" s="31">
-        <f>H8-DCF!F12*(1-Assumptions!$C$42)-I9</f>
+        <f>H8-DCF!F12*(1-Assumptions!$C$63)-I9</f>
         <v/>
       </c>
     </row>
@@ -1251,23 +1307,23 @@
         <v>245.881</v>
       </c>
       <c r="E9" s="31">
-        <f>Assumptions!$C$44*D8</f>
+        <f>Assumptions!$C$65*D8</f>
         <v/>
       </c>
       <c r="F9" s="31">
-        <f>Assumptions!$C$44*E8</f>
+        <f>Assumptions!$C$65*E8</f>
         <v/>
       </c>
       <c r="G9" s="31">
-        <f>Assumptions!$C$44*F8</f>
+        <f>Assumptions!$C$65*F8</f>
         <v/>
       </c>
       <c r="H9" s="31">
-        <f>Assumptions!$C$44*G8</f>
+        <f>Assumptions!$C$65*G8</f>
         <v/>
       </c>
       <c r="I9" s="31">
-        <f>Assumptions!$C$44*H8</f>
+        <f>Assumptions!$C$65*H8</f>
         <v/>
       </c>
     </row>
@@ -1325,23 +1381,23 @@
         <v>-1062.442</v>
       </c>
       <c r="E11" s="31">
-        <f>'Income Statement'!E5*Assumptions!$C$46</f>
+        <f>'Income Statement'!E5*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="F11" s="31">
-        <f>'Income Statement'!F5*Assumptions!$C$46</f>
+        <f>'Income Statement'!F5*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="G11" s="31">
-        <f>'Income Statement'!G5*Assumptions!$C$46</f>
+        <f>'Income Statement'!G5*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="H11" s="31">
-        <f>'Income Statement'!H5*Assumptions!$C$46</f>
+        <f>'Income Statement'!H5*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="I11" s="31">
-        <f>'Income Statement'!I5*Assumptions!$C$46</f>
+        <f>'Income Statement'!I5*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -1361,23 +1417,23 @@
         <v>2249.719</v>
       </c>
       <c r="E12" s="31">
-        <f>D12+'Income Statement'!E18-'Income Statement'!E11+DCF!B12+DCF!B14-'Income Statement'!E18*Assumptions!$C$65</f>
+        <f>D12+'Income Statement'!E18-'Income Statement'!E11+DCF!B12+DCF!B14-'Income Statement'!E18*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F12" s="31">
-        <f>E12+'Income Statement'!F18-'Income Statement'!F11+DCF!C12+DCF!C14-'Income Statement'!F18*Assumptions!$C$65</f>
+        <f>E12+'Income Statement'!F18-'Income Statement'!F11+DCF!C12+DCF!C14-'Income Statement'!F18*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="G12" s="31">
-        <f>F12+'Income Statement'!G18-'Income Statement'!G11+DCF!D12+DCF!D14-'Income Statement'!G18*Assumptions!$C$65</f>
+        <f>F12+'Income Statement'!G18-'Income Statement'!G11+DCF!D12+DCF!D14-'Income Statement'!G18*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="H12" s="31">
-        <f>G12+'Income Statement'!H18-'Income Statement'!H11+DCF!E12+DCF!E14-'Income Statement'!H18*Assumptions!$C$65</f>
+        <f>G12+'Income Statement'!H18-'Income Statement'!H11+DCF!E12+DCF!E14-'Income Statement'!H18*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="I12" s="31">
-        <f>H12+'Income Statement'!I18-'Income Statement'!I11+DCF!F12+DCF!F14-'Income Statement'!I18*Assumptions!$C$65</f>
+        <f>H12+'Income Statement'!I18-'Income Statement'!I11+DCF!F12+DCF!F14-'Income Statement'!I18*Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -1423,33 +1479,33 @@
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n">
+      <c r="B14" s="29" t="n">
         <v>9243.213</v>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="29" t="n">
         <v>9878.445</v>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="29" t="n">
         <v>10148.291</v>
       </c>
-      <c r="E14" s="28">
-        <f>D14+'Income Statement'!E18*(1-Assumptions!$C$65)</f>
-        <v/>
-      </c>
-      <c r="F14" s="28">
-        <f>E14+'Income Statement'!F18*(1-Assumptions!$C$65)</f>
-        <v/>
-      </c>
-      <c r="G14" s="28">
-        <f>F14+'Income Statement'!G18*(1-Assumptions!$C$65)</f>
-        <v/>
-      </c>
-      <c r="H14" s="28">
-        <f>G14+'Income Statement'!H18*(1-Assumptions!$C$65)</f>
-        <v/>
-      </c>
-      <c r="I14" s="28">
-        <f>H14+'Income Statement'!I18*(1-Assumptions!$C$65)</f>
+      <c r="E14" s="29">
+        <f>D14+'Income Statement'!E18*(1-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="F14" s="29">
+        <f>E14+'Income Statement'!F18*(1-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="G14" s="29">
+        <f>F14+'Income Statement'!G18*(1-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="H14" s="29">
+        <f>G14+'Income Statement'!H18*(1-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="I14" s="29">
+        <f>H14+'Income Statement'!I18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
     </row>
@@ -1498,35 +1554,35 @@
           <t>Lease liabilities / EBITDA</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="38">
         <f>B13/'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="38">
         <f>C13/'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="38">
         <f>D13/'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="38">
         <f>E13/'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="38">
         <f>F13/'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="38">
         <f>G13/'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="38">
         <f>H13/'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="38">
         <f>I13/'Income Statement'!I9</f>
         <v/>
       </c>
@@ -1892,33 +1948,33 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="29">
         <f>D9+D10+D11+D13</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="29">
         <f>E9+E10+E11+E13</f>
         <v/>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="29">
         <f>F9+F10+F11+F13</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="29">
         <f>G9+G10+G11+G13</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="29">
         <f>H9+H10+H11+H13</f>
         <v/>
       </c>
@@ -1937,23 +1993,23 @@
         <v>-2629.085</v>
       </c>
       <c r="D16" s="31">
-        <f>-'Income Statement'!E18*Assumptions!$C$65</f>
+        <f>-'Income Statement'!E18*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="E16" s="31">
-        <f>-'Income Statement'!F18*Assumptions!$C$65</f>
+        <f>-'Income Statement'!F18*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F16" s="31">
-        <f>-'Income Statement'!G18*Assumptions!$C$65</f>
+        <f>-'Income Statement'!G18*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="G16" s="31">
-        <f>-'Income Statement'!H18*Assumptions!$C$65</f>
+        <f>-'Income Statement'!H18*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="H16" s="31">
-        <f>-'Income Statement'!I18*Assumptions!$C$65</f>
+        <f>-'Income Statement'!I18*Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -2726,7 +2782,7 @@
           <t>Anchor date</t>
         </is>
       </c>
-      <c r="C18" s="41" t="inlineStr">
+      <c r="C18" s="44" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -2744,7 +2800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -2820,19 +2876,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>19.06791132189714</v>
+        <v>19.79941369811398</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>21.37770179903905</v>
+        <v>22.21134817207639</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>24.54678331325201</v>
+        <v>25.52077124203224</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>29.16801637590067</v>
+        <v>30.346897498859</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>36.54253626892263</v>
+        <v>38.04870082568256</v>
       </c>
     </row>
     <row r="7">
@@ -2842,19 +2898,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>16.9089976587036</v>
+        <v>17.55870311681214</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>18.6155317982148</v>
+        <v>19.34238216802864</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>20.85598439344367</v>
+        <v>21.68428419355597</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>23.9298500153909</v>
+        <v>24.89753706605635</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>28.41213486321618</v>
+        <v>29.58332185972701</v>
       </c>
     </row>
     <row r="8">
@@ -2864,19 +2920,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>15.21123251125888</v>
+        <v>15.79662376636993</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>16.51421550641088</v>
+        <v>17.15983565739926</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>20.34064834723247</v>
+        <v>21.16365166408015</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>23.3205014656016</v>
+        <v>24.28194674822564</v>
       </c>
     </row>
     <row r="9">
@@ -2886,19 +2942,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>13.8409344488351</v>
+        <v>14.37442603137347</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>14.86168326427922</v>
+        <v>15.44343464289715</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>16.12420719306396</v>
+        <v>16.76578009962793</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>17.72721419544651</v>
+        <v>18.44489059524078</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>19.83160815367896</v>
+        <v>20.649364466215</v>
       </c>
     </row>
     <row r="10">
@@ -2908,19 +2964,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>12.71154180540853</v>
+        <v>13.20226648770423</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13.52783883937458</v>
+        <v>14.05804986372445</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>14.51633438136042</v>
+        <v>15.09447965499236</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>15.73890953549209</v>
+        <v>16.37647279813237</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>17.29113046957509</v>
+        <v>18.00428385302159</v>
       </c>
     </row>
     <row r="12">
@@ -2965,19 +3021,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>25.1462633087418</v>
+        <v>26.14357352570003</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>24.84419724656098</v>
+        <v>25.82975570066811</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>24.54678331325201</v>
+        <v>25.52077124203224</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>24.25393267170437</v>
+        <v>25.21652784942216</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>23.96555851731982</v>
+        <v>24.916935334247</v>
       </c>
     </row>
     <row r="15">
@@ -2987,19 +3043,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>21.3646021781526</v>
+        <v>22.21263784305483</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>21.10832472550778</v>
+        <v>21.94641594959031</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>20.85598439344367</v>
+        <v>21.68428419355597</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>20.60750611688699</v>
+        <v>21.42616459016411</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>20.36281654625054</v>
+        <v>21.17198093686849</v>
       </c>
     </row>
     <row r="16">
@@ -3009,19 +3065,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>18.61111868087366</v>
+        <v>19.35048571765527</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>18.38817967730395</v>
+        <v>19.11891790217087</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>17.95248626582393</v>
+        <v>18.66636176730568</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>17.73960326570264</v>
+        <v>18.44523986519273</v>
       </c>
     </row>
     <row r="17">
@@ -3031,19 +3087,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>16.51634027063411</v>
+        <v>17.17305269319061</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>16.31876346535764</v>
+        <v>16.96784770384932</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>16.12420719306396</v>
+        <v>16.76578009962793</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>15.93261404240899</v>
+        <v>16.56679024596512</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>15.74392791117709</v>
+        <v>16.37081986815219</v>
       </c>
     </row>
     <row r="18">
@@ -3053,19 +3109,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>14.86888784166854</v>
+        <v>15.46061148513528</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>14.69125655499216</v>
+        <v>15.27613872850689</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>14.51633438136042</v>
+        <v>15.09447965499236</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>14.34406990701374</v>
+        <v>14.91558086413144</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>14.17441288927764</v>
+        <v>14.73939017182985</v>
       </c>
     </row>
     <row r="20">
@@ -3100,19 +3156,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>21.54661639430977</v>
+        <v>22.40198251354033</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>15.78099116792509</v>
+        <v>16.40920067045051</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>15.32091216868629</v>
+        <v>15.93101093635009</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>13.36132449902587</v>
+        <v>13.8943248227103</v>
       </c>
       <c r="H22" s="10">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -3126,19 +3182,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>19.46457070713711</v>
+        <v>20.23250466545218</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>16.92356386654856</v>
+        <v>17.60190552972687</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>15.83456093486775</v>
+        <v>16.4745059001303</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>14.70925790546425</v>
+        <v>15.30952628288052</v>
       </c>
       <c r="H23" s="10">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -3152,19 +3208,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>16.26460079390747</v>
+        <v>16.00460556694265</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>17.21662900617221</v>
+        <v>17.44775233658746</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>19.12068543070169</v>
+        <v>20.33404587587708</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>20.07271364296644</v>
+        <v>21.77719264552191</v>
       </c>
       <c r="H24" s="10">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -3178,19 +3234,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>17.26166853343523</v>
+        <v>17.95070477355046</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>17.71516287593608</v>
+        <v>18.42080193989137</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>18.62215156093781</v>
+        <v>19.36099627257317</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>19.07564590343867</v>
+        <v>19.83109343891408</v>
       </c>
       <c r="H25" s="10">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -3200,23 +3256,23 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Contribution margins, multiplicative  (0.94x / 0.97x / 1.00x / 1.03x / 1.06x)</t>
+          <t>Direct cost per unit, multiplicative  (0.94x / 0.97x / 1.00x / 1.03x / 1.06x)</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>15.7396549927263</v>
+        <v>20.07809120050769</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>16.95415610558162</v>
+        <v>19.48449515336998</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>19.38315833129229</v>
+        <v>18.29730305909456</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>20.59765944414761</v>
+        <v>17.70370701195685</v>
       </c>
       <c r="H26" s="10">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -3226,23 +3282,23 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Capex path multiplier  (0.850x / 0.925x / 1.000x / 1.100x / 1.200x)</t>
+          <t>Blended ARPU drift per year (mix exhaustion)  (-2.5% / -1.5% / +0.0% / +0.5% / +1.0%)</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>19.19302743416895</v>
+        <v>15.4693092551696</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>18.68084232630295</v>
+        <v>16.80692954187711</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>17.48574374128228</v>
+        <v>19.60665360020088</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>16.80283026412761</v>
+        <v>20.3331339912772</v>
       </c>
       <c r="H27" s="10">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -3252,23 +3308,23 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue  (-10.0% / -8.5% / -6.7% / -5.0% / -3.0%)</t>
+          <t>Capex path multiplier  (0.850x / 0.925x / 1.000x / 1.100x / 1.200x)</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>18.37879766603091</v>
+        <v>19.91526932196428</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>18.28386190608378</v>
+        <v>19.40308421409827</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.06234513287381</v>
+        <v>18.2079856290776</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>17.93576411961097</v>
+        <v>17.52507215192293</v>
       </c>
       <c r="H28" s="10">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -3278,23 +3334,23 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital  (18.0% / 22.0% / 26.5% / 30.0% / 34.0%)</t>
+          <t>Working capital / revenue  (-10.0% / -8.5% / -6.7% / -5.0% / -3.0%)</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>17.4011105551553</v>
+        <v>19.10103955382623</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>17.83712906627904</v>
+        <v>19.0061037938791</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>18.36035127962752</v>
+        <v>18.78458702066914</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>18.52962905453439</v>
+        <v>18.6580060074063</v>
       </c>
       <c r="H29" s="10">
         <f>MAX(B29:F29)-MIN(B29:F29)</f>
@@ -3304,26 +3360,52 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth (at base cost of capital)  (1.5% / 2.0% / 2.5% / 3.0% / 3.5%)</t>
+          <t>Terminal return on invested capital  (18.0% / 22.0% / 27.4% / 30.0% / 34.0%)</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>15.21123251125888</v>
+        <v>18.03758600609211</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>16.51421550641088</v>
+        <v>18.48919841482648</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>18.16865721843695</v>
+        <v>18.89089910623227</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>20.34064834723247</v>
+        <v>19.03113330530774</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>23.3205014656016</v>
+        <v>19.20646518163991</v>
       </c>
       <c r="H30" s="10">
         <f>MAX(B30:F30)-MIN(B30:F30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth (at base cost of capital)  (1.5% / 2.0% / 2.5% / 3.0% / 3.5%)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>15.79662376636993</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>17.15983565739926</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>18.89089910623227</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>21.16365166408015</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>24.28194674822564</v>
+      </c>
+      <c r="H31" s="10">
+        <f>MAX(B31:F31)-MIN(B31:F31)</f>
         <v/>
       </c>
     </row>
@@ -3906,35 +3988,35 @@
           <t>Lease liabilities / EBITDA</t>
         </is>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="38">
         <f>'Balance Sheet'!B16</f>
         <v/>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="38">
         <f>'Balance Sheet'!C16</f>
         <v/>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="38">
         <f>'Balance Sheet'!D16</f>
         <v/>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="38">
         <f>'Balance Sheet'!E16</f>
         <v/>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="38">
         <f>'Balance Sheet'!F16</f>
         <v/>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="38">
         <f>'Balance Sheet'!G16</f>
         <v/>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="38">
         <f>'Balance Sheet'!H16</f>
         <v/>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="38">
         <f>'Balance Sheet'!I16</f>
         <v/>
       </c>
@@ -4003,23 +4085,23 @@
         <v>9704</v>
       </c>
       <c r="E21" s="18">
-        <f>Assumptions!$B$13</f>
+        <f>Assumptions!$B$23</f>
         <v/>
       </c>
       <c r="F21" s="18">
-        <f>Assumptions!$C$13</f>
+        <f>Assumptions!$C$23</f>
         <v/>
       </c>
       <c r="G21" s="18">
-        <f>Assumptions!$D$13</f>
+        <f>Assumptions!$D$23</f>
         <v/>
       </c>
       <c r="H21" s="18">
-        <f>Assumptions!$E$13</f>
+        <f>Assumptions!$E$23</f>
         <v/>
       </c>
       <c r="I21" s="18">
-        <f>Assumptions!$F$13</f>
+        <f>Assumptions!$F$23</f>
         <v/>
       </c>
     </row>
@@ -4041,23 +4123,23 @@
         <v>735</v>
       </c>
       <c r="E22" s="18">
-        <f>Assumptions!$B$14</f>
+        <f>Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="F22" s="18">
-        <f>Assumptions!$C$14</f>
+        <f>Assumptions!$C$24</f>
         <v/>
       </c>
       <c r="G22" s="18">
-        <f>Assumptions!$D$14</f>
+        <f>Assumptions!$D$24</f>
         <v/>
       </c>
       <c r="H22" s="18">
-        <f>Assumptions!$E$14</f>
+        <f>Assumptions!$E$24</f>
         <v/>
       </c>
       <c r="I22" s="18">
-        <f>Assumptions!$F$14</f>
+        <f>Assumptions!$F$24</f>
         <v/>
       </c>
     </row>
@@ -4067,7 +4149,7 @@
           <t>Blended mobile ARPU (AED/month)</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4078,24 +4160,24 @@
       <c r="D23" s="24" t="n">
         <v>63.3</v>
       </c>
-      <c r="E23" s="42">
-        <f>Assumptions!$B$15</f>
-        <v/>
-      </c>
-      <c r="F23" s="42">
-        <f>Assumptions!$C$15</f>
-        <v/>
-      </c>
-      <c r="G23" s="42">
-        <f>Assumptions!$D$15</f>
-        <v/>
-      </c>
-      <c r="H23" s="42">
-        <f>Assumptions!$E$15</f>
-        <v/>
-      </c>
-      <c r="I23" s="42">
-        <f>Assumptions!$F$15</f>
+      <c r="E23" s="45">
+        <f>Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="F23" s="45">
+        <f>Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="G23" s="45">
+        <f>Assumptions!$D$25</f>
+        <v/>
+      </c>
+      <c r="H23" s="45">
+        <f>Assumptions!$E$25</f>
+        <v/>
+      </c>
+      <c r="I23" s="45">
+        <f>Assumptions!$F$25</f>
         <v/>
       </c>
     </row>
@@ -4186,12 +4268,12 @@
           <t>UAE (ADX)</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>~20.7x</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>~4.8%</t>
         </is>
@@ -4213,12 +4295,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>~18.9x</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr">
         <is>
           <t>~5.2%</t>
         </is>
@@ -4240,12 +4322,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>~15.5x</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D7" s="44" t="inlineStr">
         <is>
           <t>~2.9%</t>
         </is>
@@ -4267,12 +4349,12 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>~12.5x</t>
         </is>
       </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="D8" s="44" t="inlineStr">
         <is>
           <t>~4.6%</t>
         </is>
@@ -4294,12 +4376,12 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
         <is>
           <t>~9x</t>
         </is>
       </c>
-      <c r="D9" s="41" t="inlineStr">
+      <c r="D9" s="44" t="inlineStr">
         <is>
           <t>~6-7%</t>
         </is>
@@ -4321,12 +4403,12 @@
           <t>Oman</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>~11.4x</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>~6.7%</t>
         </is>
@@ -4348,12 +4430,12 @@
           <t>Developed markets</t>
         </is>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>n/m</t>
         </is>
       </c>
-      <c r="D11" s="41" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>3.4% / n/m</t>
         </is>
@@ -4382,7 +4464,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="36">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -4393,7 +4475,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="36">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -4415,7 +4497,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="36">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -4515,14 +4597,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>10.54402485670467</v>
+        <v>11.02686991091756</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C63</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>27.58617162391559</v>
+        <v>28.6533036884854</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>0.45</v>
@@ -4766,7 +4848,7 @@
         </is>
       </c>
       <c r="C19" s="18">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
@@ -4777,7 +4859,7 @@
         </is>
       </c>
       <c r="C20" s="18">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
     </row>
@@ -4927,7 +5009,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>10.54402485670467</v>
+        <v>11.02686991091756</v>
       </c>
     </row>
     <row r="7">
@@ -4942,7 +5024,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>27.58617162391559</v>
+        <v>28.6533036884854</v>
       </c>
     </row>
     <row r="8">
@@ -5030,7 +5112,7 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>9.951572188319338</v>
+        <v>10.08649012975652</v>
       </c>
     </row>
     <row r="17">
@@ -5050,7 +5132,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>14.40369208593501</v>
+        <v>14.81218441814286</v>
       </c>
     </row>
     <row r="19">
@@ -5071,7 +5153,7 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>15.21787551300283</v>
+        <v>16.11429287425042</v>
       </c>
     </row>
     <row r="22">
@@ -5120,13 +5202,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>9.547737257681046</v>
+        <v>9.881999525772653</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>7.506189806144837</v>
+        <v>7.773599620618121</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>11.24902680062789</v>
+        <v>11.63899944673476</v>
       </c>
     </row>
     <row r="25">
@@ -5141,13 +5223,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>18.01764358863624</v>
+        <v>18.57393404235861</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>9.532883848370837</v>
+        <v>9.836466254461905</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>20.90712024622747</v>
+        <v>21.54947017920073</v>
       </c>
     </row>
     <row r="26">
@@ -5162,13 +5244,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>17.73742567320945</v>
+        <v>18.45966756100478</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>11.75234569627446</v>
+        <v>12.19616318319305</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>19.86591675399459</v>
+        <v>20.67482766832535</v>
       </c>
     </row>
     <row r="27">
@@ -5199,7 +5281,7 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>17.21272776016761</v>
+        <v>17.89729092471108</v>
       </c>
     </row>
   </sheetData>
@@ -5214,7 +5296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5357,7 +5439,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Unit build — mobile and fixed (subscribers x ARPU)</t>
+          <t>H1-2026 reviewed segment actuals — the base the FY2026 build chains off</t>
         </is>
       </c>
       <c r="B12" s="15" t="n"/>
@@ -5371,609 +5453,531 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Mobile subscribers, end of year ('000)</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>9450</v>
+          <t>Mobile revenue, six months to 30-Jun-2026 (AED mn, reviewed)</t>
+        </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>9760</v>
-      </c>
-      <c r="D13" s="23" t="n">
-        <v>10010</v>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>10240</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>10450</v>
+        <v>3646.314</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Fixed subscribers, end of year ('000)</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>760</v>
+          <t>Fixed revenue, six months to 30-Jun-2026 (AED mn, reviewed)</t>
+        </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>790</v>
-      </c>
-      <c r="D14" s="23" t="n">
-        <v>815</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>838</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>858</v>
+        <v>2382.608</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Blended mobile ARPU (AED/month)</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="C15" s="24" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>64</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>64.2</v>
+          <t>Mobile subscribers at 30-Jun-2026 ('000, reviewed period end)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>9280</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Implied fixed revenue per subscriber (AED/month)</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="n">
-        <v>537</v>
+          <t>Fixed subscribers at 30-Jun-2026 ('000, reviewed period end)</t>
+        </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>545</v>
-      </c>
-      <c r="D16" s="23" t="n">
-        <v>553</v>
-      </c>
-      <c r="E16" s="23" t="n">
-        <v>561</v>
-      </c>
-      <c r="F16" s="23" t="n">
-        <v>569</v>
+        <v>744</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Wholesale revenue growth</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>0.02</v>
+          <t>Wholesale revenue FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>2568.222</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>ICT and associated telecom revenue growth</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.08</v>
+          <t>ICT revenue FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>1882.558</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Wholesale revenue, six months to 30-Jun-2026 (AED mn, reviewed)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="n">
+        <v>1257.566</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Segment contribution margins (audited FY2025 rates; ICT lifted on scale)</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Mobile — contribution margin</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>0.608</v>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ICT revenue, six months to 30-Jun-2026 (AED mn, reviewed)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>911.085</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Fixed — contribution margin</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>0.858</v>
-      </c>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Unit build — mobile and fixed (subscribers x ARPU)</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Wholesale — contribution margin</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>0.864</v>
+          <t>Mobile subscribers, end of year ('000)</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>9450</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>9760</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>10010</v>
+      </c>
+      <c r="E23" s="23" t="n">
+        <v>10240</v>
+      </c>
+      <c r="F23" s="23" t="n">
+        <v>10450</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>ICT — contribution margin</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>0.215</v>
+          <t>Fixed subscribers, end of year ('000)</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>760</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>790</v>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>815</v>
+      </c>
+      <c r="E24" s="23" t="n">
+        <v>838</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Blended mobile ARPU (AED/month)</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D25" s="24" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>64</v>
+      </c>
+      <c r="F25" s="24" t="n">
+        <v>64.2</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Operating expense stack — one escalator per cost class</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="15" t="n"/>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Implied fixed revenue per subscriber (AED/month)</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>537</v>
+      </c>
+      <c r="C26" s="23" t="n">
+        <v>545</v>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>553</v>
+      </c>
+      <c r="E26" s="23" t="n">
+        <v>561</v>
+      </c>
+      <c r="F26" s="23" t="n">
+        <v>569</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Staff cost, FY2026E level (AED mn)</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="n">
-        <v>1035.16</v>
+          <t>Wholesale revenue growth</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Staff escalator (UAE wage inflation)</t>
-        </is>
+          <t>ICT and associated telecom revenue growth</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>0.079</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Network &amp; maintenance, FY2025 base (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="n">
-        <v>963.878</v>
+        <v>0.11</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Network escalator (network scale)</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Direct-cost stack — cost per unit, one escalator per driver class. CONTRIBUTION MARGIN IS NOT AN INPUT HERE: it is computed on the Segments sheet as what is left after each cost line is grown on its own physical driver.</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Administrative expense, FY2025 base (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="n">
-        <v>189.654</v>
+          <t>Mobile interconnect cost, H1-2026 actual (AED/subscriber/month)</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>16.81380811911785</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Administrative escalator (CPI)</t>
+          <t>Mobile interconnect escalator (termination rates, OTT substitution)</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>0.02</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Other operating expense, FY2025 base (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>133.192</v>
+          <t>Mobile commission cost, H1-2026 actual (AED/subscriber/month)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>6.306854895350471</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Other-expense escalator (CPI)</t>
+          <t>Mobile commission escalator (acquisition/retention cost)</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Marketing / revenue</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>0.018</v>
+          <t>Mobile devices and direct services, H1-2026 actual (AED/subscriber/month)</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="n">
+        <v>0.9565423514538555</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Telecom licence and related fees / revenue (regulatory revenue share)</t>
+          <t>Mobile devices escalator (held flat — lumpy, no trend read into it)</t>
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Expected credit losses / revenue</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="n">
-        <v>0.0145</v>
+          <t>Fixed capacity and direct cost, H1-2026 actual (AED/subscriber/month)</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>68.35316655397791</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Other operating income (AED mn/yr)</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="n">
-        <v>15</v>
+          <t>Fixed capacity escalator (held flat against an observed decline)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Wholesale direct cost / wholesale revenue (H1-2026 rate, held flat)</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>0.1558</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Capital intensity and working capital</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
-      <c r="H40" s="15" t="n"/>
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>ICT direct cost / ICT revenue (H1-2026 rate, held flat)</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>0.7848000000000001</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>0.13</v>
+          <t>Mobile direct cost, six months to 30-Jun-2026 (AED mn, reviewed)</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>1371.245</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Tangible share of capex (audited FY2025)</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>0.866</v>
+          <t>Fixed direct cost, six months to 30-Jun-2026 (AED mn, reviewed)</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="n">
+        <v>303.283</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>PP&amp;E depreciation rate on opening balance (audited FY2025)</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>0.1583</v>
+          <t>Wholesale direct cost, six months to 30-Jun-2026 (AED mn, reviewed)</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="n">
+        <v>195.926</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Intangibles amortisation rate on opening balance (audited FY2025)</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>0.289</v>
+          <t>ICT direct cost, six months to 30-Jun-2026 (AED mn, reviewed)</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="n">
+        <v>714.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Right-of-use depreciation, matched by non-cash lease additions (AED mn)</t>
-        </is>
-      </c>
-      <c r="B45" s="23" t="n">
-        <v>355</v>
-      </c>
-      <c r="C45" s="23" t="n">
-        <v>350</v>
-      </c>
-      <c r="D45" s="23" t="n">
-        <v>345</v>
-      </c>
-      <c r="E45" s="23" t="n">
-        <v>340</v>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Net working capital / revenue (audited FY2025 component days)</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>-0.0667974774135183</v>
-      </c>
+          <t>Blended ARPU drift (mix-exhaustion sensitivity; zero in the base case)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Operating expense stack — one escalator per cost class</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
+      <c r="H47" s="15" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>Cost of capital</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="n"/>
-      <c r="C48" s="15" t="n"/>
-      <c r="D48" s="15" t="n"/>
-      <c r="E48" s="15" t="n"/>
-      <c r="F48" s="15" t="n"/>
-      <c r="G48" s="15" t="n"/>
-      <c r="H48" s="15" t="n"/>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Staff cost, FY2026E level (AED mn)</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="n">
+        <v>1035.16</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Risk-free rate — Jan-2031 AED T-bond (longest liquid AED tenor)</t>
+          <t>Staff escalator (UAE wage inflation)</t>
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>0.0448</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>UAE sovereign default spread (netted out; Aa2 rating basis)</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="n">
-        <v>0.0004</v>
+          <t>Network &amp; maintenance, FY2025 base (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="n">
+        <v>963.878</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium (UAE total, rating basis)</t>
+          <t>Network escalator (network scale)</t>
         </is>
       </c>
       <c r="C51" s="9" t="n">
-        <v>0.0429</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Beta (DU weekly vs FTSE ADX General, 5y)</t>
-        </is>
-      </c>
-      <c r="C52" s="25" t="n">
-        <v>0.488</v>
+          <t>Administrative expense, FY2025 base (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="n">
+        <v>189.654</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Marginal cost of debt (AED sovereign + GCC telecom spread)</t>
+          <t>Administrative escalator (CPI)</t>
         </is>
       </c>
       <c r="C53" s="9" t="n">
-        <v>0.051</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>AED risk-free path (defines the glide)</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="n">
-        <v>0.0448</v>
-      </c>
-      <c r="C54" s="9" t="n">
-        <v>0.0444</v>
-      </c>
-      <c r="D54" s="9" t="n">
-        <v>0.0439</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>0.0435</v>
-      </c>
-      <c r="F54" s="9" t="n">
-        <v>0.043</v>
+          <t>Other operating expense, FY2025 base (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="n">
+        <v>133.192</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t>Other-expense escalator (CPI)</t>
         </is>
       </c>
       <c r="C55" s="9" t="n">
-        <v>0.043</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Marketing / revenue</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>0.0429</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Telecom licence and related fees / revenue (regulatory revenue share)</t>
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>0.049</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
+          <t>Expected credit losses / revenue</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>0.05</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="n">
-        <v>0.025</v>
+          <t>Other operating income (AED mn/yr)</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>Balance-sheet and bridge anchors</t>
+          <t>Capital intensity and working capital</t>
         </is>
       </c>
       <c r="B61" s="15" t="n"/>
@@ -5987,164 +5991,398 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities at FY2025 (AED mn, audited — the only debt-like item)</t>
-        </is>
-      </c>
-      <c r="C62" s="23" t="n">
-        <v>1938.819</v>
+          <t>Capital expenditure / revenue</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Cash and term deposits at FY2025 (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C63" s="23" t="n">
-        <v>2249.719</v>
+          <t>Tangible share of capex (audited FY2025)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>0.866</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Equity-accounted investees at carrying value (AED mn)</t>
-        </is>
-      </c>
-      <c r="C64" s="24" t="n">
-        <v>0.511</v>
+          <t>PP&amp;E depreciation rate on opening balance (audited FY2025)</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>0.1583</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio (FY2024 actual 98%, FY2025 ~100%)</t>
+          <t>Intangibles amortisation rate on opening balance (audited FY2025)</t>
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>0.98</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Yield on cash and term deposits (audited FY2025 effective)</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="n">
-        <v>0.033</v>
+          <t>Right-of-use depreciation, matched by non-cash lease additions (AED mn)</t>
+        </is>
+      </c>
+      <c r="B66" s="23" t="n">
+        <v>355</v>
+      </c>
+      <c r="C66" s="23" t="n">
+        <v>350</v>
+      </c>
+      <c r="D66" s="23" t="n">
+        <v>345</v>
+      </c>
+      <c r="E66" s="23" t="n">
+        <v>340</v>
+      </c>
+      <c r="F66" s="23" t="n">
+        <v>335</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Lease interest rate (audited FY2025 effective)</t>
+          <t>Net working capital / revenue (audited FY2025 component days)</t>
         </is>
       </c>
       <c r="C67" s="9" t="n">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Dividends gone ex between 31-Dec-2025 and the anchor (AED/share)</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>0.66</v>
+        <v>-0.0667974774135183</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Days from the 31-Dec-2025 valuation date to the 07-Aug-2026 anchor</t>
-        </is>
-      </c>
-      <c r="C69" s="23" t="n">
-        <v>219</v>
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>Cost of capital</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="15" t="n"/>
+      <c r="D69" s="15" t="n"/>
+      <c r="E69" s="15" t="n"/>
+      <c r="F69" s="15" t="n"/>
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="15" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Risk-free rate — Jan-2031 AED T-bond (longest liquid AED tenor)</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>0.0448</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="n"/>
-      <c r="C71" s="15" t="n"/>
-      <c r="D71" s="15" t="n"/>
-      <c r="E71" s="15" t="n"/>
-      <c r="F71" s="15" t="n"/>
-      <c r="G71" s="15" t="n"/>
-      <c r="H71" s="15" t="n"/>
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>UAE sovereign default spread (netted out; Aa2 rating basis)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>0.0004</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings (GCC telecom peer median)</t>
-        </is>
-      </c>
-      <c r="C72" s="21" t="n">
-        <v>12.9</v>
+          <t>Equity risk premium (UAE total, rating basis)</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>0.0429</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>Peer benchmark dividend yield</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="n">
-        <v>0.0489</v>
+          <t>Beta (DU weekly vs FTSE ADX General, 5y)</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="n">
+        <v>0.488</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
+          <t>Marginal cost of debt (AED sovereign + GCC telecom spread)</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>0.27</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
+          <t>AED risk-free path (defines the glide)</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>0.0448</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>0.45</v>
+        <v>0.0444</v>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>0.043</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
+          <t>Terminal risk-free rate</t>
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>0.25</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
+          <t>Terminal equity risk premium</t>
         </is>
       </c>
       <c r="C77" s="9" t="n">
-        <v>0.2</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
+          <t>Terminal cost of debt</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Terminal debt weight</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>Balance-sheet and bridge anchors</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="n"/>
+      <c r="C82" s="15" t="n"/>
+      <c r="D82" s="15" t="n"/>
+      <c r="E82" s="15" t="n"/>
+      <c r="F82" s="15" t="n"/>
+      <c r="G82" s="15" t="n"/>
+      <c r="H82" s="15" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Lease liabilities at FY2025 (AED mn, audited — the only debt-like item)</t>
+        </is>
+      </c>
+      <c r="C83" s="23" t="n">
+        <v>1938.819</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Cash and term deposits at FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C84" s="23" t="n">
+        <v>2249.719</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Equity-accounted investees at carrying value (AED mn)</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="n">
+        <v>0.511</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Forecast dividend payout ratio (FY2024 actual 98%, FY2025 ~100%)</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Yield on cash and term deposits (audited FY2025 effective)</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Lease interest rate (audited FY2025 effective)</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Dividends gone ex between 31-Dec-2025 and the anchor (AED/share)</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Days from the 31-Dec-2025 valuation date to the 07-Aug-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C90" s="23" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="n"/>
+      <c r="C92" s="15" t="n"/>
+      <c r="D92" s="15" t="n"/>
+      <c r="E92" s="15" t="n"/>
+      <c r="F92" s="15" t="n"/>
+      <c r="G92" s="15" t="n"/>
+      <c r="H92" s="15" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Justified price/earnings (GCC telecom peer median)</t>
+        </is>
+      </c>
+      <c r="C93" s="21" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Peer benchmark dividend yield</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n">
+        <v>0.0489</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
           <t>Weight — book</t>
         </is>
       </c>
-      <c r="C78" s="9" t="n">
+      <c r="C99" s="9" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -6241,11 +6479,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6257,7 +6495,7 @@
         </is>
       </c>
       <c r="C8" s="18">
-        <f>-Assumptions!$C$62</f>
+        <f>-Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="D8" s="10">
@@ -6272,7 +6510,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="D9" s="10">
@@ -6287,7 +6525,7 @@
         </is>
       </c>
       <c r="C10" s="18">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="D10" s="10">
@@ -6302,11 +6540,11 @@
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>C7+C8+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>C11/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6341,7 +6579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6440,20 +6678,25 @@
       <c r="D5" s="9" t="n">
         <v>0.6082941244980873</v>
       </c>
-      <c r="E5" s="23" t="n">
-        <v>7208.76</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>7330.536</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>7567.956</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>7776</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <v>7969.788</v>
+      <c r="E5" s="31">
+        <f>Assumptions!$C$13+(Assumptions!$C$15+Assumptions!$B$23)/2*Assumptions!$B$25*6/1000</f>
+        <v/>
+      </c>
+      <c r="F5" s="31">
+        <f>(Assumptions!$B$23+Assumptions!$C$23)/2*Assumptions!$C$25*(1+Assumptions!$C$45)^1*12/1000</f>
+        <v/>
+      </c>
+      <c r="G5" s="31">
+        <f>(Assumptions!$C$23+Assumptions!$D$23)/2*Assumptions!$D$25*(1+Assumptions!$C$45)^2*12/1000</f>
+        <v/>
+      </c>
+      <c r="H5" s="31">
+        <f>(Assumptions!$D$23+Assumptions!$E$23)/2*Assumptions!$E$25*(1+Assumptions!$C$45)^3*12/1000</f>
+        <v/>
+      </c>
+      <c r="I5" s="31">
+        <f>(Assumptions!$E$23+Assumptions!$F$23)/2*Assumptions!$F$25*(1+Assumptions!$C$45)^4*12/1000</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -6472,20 +6715,25 @@
       <c r="D6" s="9" t="n">
         <v>0.858015094623953</v>
       </c>
-      <c r="E6" s="23" t="n">
-        <v>4805.552</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <v>5068.5</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>5325.39</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <v>5563.998</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <v>5790.144</v>
+      <c r="E6" s="31">
+        <f>Assumptions!$C$14+(Assumptions!$C$16+Assumptions!$B$24)/2*Assumptions!$B$26*6/1000</f>
+        <v/>
+      </c>
+      <c r="F6" s="31">
+        <f>(Assumptions!$B$24+Assumptions!$C$24)/2*Assumptions!$C$26*(1+Assumptions!$C$45)^1*12/1000</f>
+        <v/>
+      </c>
+      <c r="G6" s="31">
+        <f>(Assumptions!$C$24+Assumptions!$D$24)/2*Assumptions!$D$26*(1+Assumptions!$C$45)^2*12/1000</f>
+        <v/>
+      </c>
+      <c r="H6" s="31">
+        <f>(Assumptions!$D$24+Assumptions!$E$24)/2*Assumptions!$E$26*(1+Assumptions!$C$45)^3*12/1000</f>
+        <v/>
+      </c>
+      <c r="I6" s="31">
+        <f>(Assumptions!$E$24+Assumptions!$F$24)/2*Assumptions!$F$26*(1+Assumptions!$C$45)^4*12/1000</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -6504,20 +6752,25 @@
       <c r="D7" s="9" t="n">
         <v>0.8642060538380248</v>
       </c>
-      <c r="E7" s="23" t="n">
-        <v>2547.676224</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>2585.89136736</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>2637.6091947072</v>
-      </c>
-      <c r="H7" s="23" t="n">
-        <v>2690.361378601344</v>
-      </c>
-      <c r="I7" s="23" t="n">
-        <v>2744.168606173371</v>
+      <c r="E7" s="31">
+        <f>Assumptions!$C$17*(1+Assumptions!$B$27)</f>
+        <v/>
+      </c>
+      <c r="F7" s="31">
+        <f>E7*(1+Assumptions!$C$27)</f>
+        <v/>
+      </c>
+      <c r="G7" s="31">
+        <f>F7*(1+Assumptions!$D$27)</f>
+        <v/>
+      </c>
+      <c r="H7" s="31">
+        <f>G7*(1+Assumptions!$E$27)</f>
+        <v/>
+      </c>
+      <c r="I7" s="31">
+        <f>H7*(1+Assumptions!$F$27)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -6536,20 +6789,25 @@
       <c r="D8" s="9" t="n">
         <v>0.1939000020185301</v>
       </c>
-      <c r="E8" s="23" t="n">
-        <v>2031.280082</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>2254.72089102</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>2480.192980122</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <v>2703.41034833298</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <v>2919.683176199619</v>
+      <c r="E8" s="31">
+        <f>Assumptions!$C$18*(1+Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="F8" s="31">
+        <f>E8*(1+Assumptions!$C$28)</f>
+        <v/>
+      </c>
+      <c r="G8" s="31">
+        <f>F8*(1+Assumptions!$D$28)</f>
+        <v/>
+      </c>
+      <c r="H8" s="31">
+        <f>G8*(1+Assumptions!$E$28)</f>
+        <v/>
+      </c>
+      <c r="I8" s="31">
+        <f>H8*(1+Assumptions!$F$28)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -6558,7 +6816,7 @@
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
@@ -6567,23 +6825,23 @@
         <v/>
       </c>
       <c r="D9" s="15" t="n"/>
-      <c r="E9" s="30">
+      <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="32">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="32">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="32">
         <f>SUM(I5:I8)</f>
         <v/>
       </c>
@@ -6591,7 +6849,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Contribution — revenue x the margin path</t>
+          <t>Direct cost per unit — each line grown on its own physical driver</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -6623,665 +6881,1220 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>E5*Assumptions!$B$21</f>
-        <v/>
-      </c>
-      <c r="C12" s="31">
-        <f>F5*Assumptions!$C$21</f>
-        <v/>
-      </c>
-      <c r="D12" s="31">
-        <f>G5*Assumptions!$D$21</f>
-        <v/>
-      </c>
-      <c r="E12" s="31">
-        <f>H5*Assumptions!$E$21</f>
-        <v/>
-      </c>
-      <c r="F12" s="31">
-        <f>I5*Assumptions!$F$21</f>
+          <t>Mobile interconnect (AED per subscriber per month)</t>
+        </is>
+      </c>
+      <c r="B12" s="33">
+        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^0</f>
+        <v/>
+      </c>
+      <c r="C12" s="33">
+        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^1</f>
+        <v/>
+      </c>
+      <c r="D12" s="33">
+        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^2</f>
+        <v/>
+      </c>
+      <c r="E12" s="33">
+        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^3</f>
+        <v/>
+      </c>
+      <c r="F12" s="33">
+        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^4</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="B13" s="31">
-        <f>E6*Assumptions!$B$22</f>
-        <v/>
-      </c>
-      <c r="C13" s="31">
-        <f>F6*Assumptions!$C$22</f>
-        <v/>
-      </c>
-      <c r="D13" s="31">
-        <f>G6*Assumptions!$D$22</f>
-        <v/>
-      </c>
-      <c r="E13" s="31">
-        <f>H6*Assumptions!$E$22</f>
-        <v/>
-      </c>
-      <c r="F13" s="31">
-        <f>I6*Assumptions!$F$22</f>
+          <t>Mobile commission (AED per subscriber per month)</t>
+        </is>
+      </c>
+      <c r="B13" s="33">
+        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^0</f>
+        <v/>
+      </c>
+      <c r="C13" s="33">
+        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^1</f>
+        <v/>
+      </c>
+      <c r="D13" s="33">
+        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^2</f>
+        <v/>
+      </c>
+      <c r="E13" s="33">
+        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^3</f>
+        <v/>
+      </c>
+      <c r="F13" s="33">
+        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^4</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Wholesale</t>
-        </is>
-      </c>
-      <c r="B14" s="31">
-        <f>E7*Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="C14" s="31">
-        <f>F7*Assumptions!$C$23</f>
-        <v/>
-      </c>
-      <c r="D14" s="31">
-        <f>G7*Assumptions!$D$23</f>
-        <v/>
-      </c>
-      <c r="E14" s="31">
-        <f>H7*Assumptions!$E$23</f>
-        <v/>
-      </c>
-      <c r="F14" s="31">
-        <f>I7*Assumptions!$F$23</f>
+          <t>Mobile devices and direct services (AED per subscriber per month)</t>
+        </is>
+      </c>
+      <c r="B14" s="33">
+        <f>Assumptions!$C$35*(1+Assumptions!$C$36)^0</f>
+        <v/>
+      </c>
+      <c r="C14" s="33">
+        <f>Assumptions!$C$35*(1+Assumptions!$C$36)^1</f>
+        <v/>
+      </c>
+      <c r="D14" s="33">
+        <f>Assumptions!$C$35*(1+Assumptions!$C$36)^2</f>
+        <v/>
+      </c>
+      <c r="E14" s="33">
+        <f>Assumptions!$C$35*(1+Assumptions!$C$36)^3</f>
+        <v/>
+      </c>
+      <c r="F14" s="33">
+        <f>Assumptions!$C$35*(1+Assumptions!$C$36)^4</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>ICT and associated telecom services</t>
-        </is>
-      </c>
-      <c r="B15" s="31">
-        <f>E8*Assumptions!$B$24</f>
-        <v/>
-      </c>
-      <c r="C15" s="31">
-        <f>F8*Assumptions!$C$24</f>
-        <v/>
-      </c>
-      <c r="D15" s="31">
-        <f>G8*Assumptions!$D$24</f>
-        <v/>
-      </c>
-      <c r="E15" s="31">
-        <f>H8*Assumptions!$E$24</f>
-        <v/>
-      </c>
-      <c r="F15" s="31">
-        <f>I8*Assumptions!$F$24</f>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Mobile — total direct cost per subscriber per month</t>
+        </is>
+      </c>
+      <c r="B15" s="34">
+        <f>B12+B13+B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="34">
+        <f>C12+C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="34">
+        <f>D12+D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="34">
+        <f>E12+E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="34">
+        <f>F12+F13+F14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Total contribution</t>
-        </is>
-      </c>
-      <c r="B16" s="30">
-        <f>SUM(B12:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="30">
-        <f>SUM(C12:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="30">
-        <f>SUM(D12:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="30">
-        <f>SUM(E12:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="30">
-        <f>SUM(F12:F15)</f>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Fixed capacity and direct cost (AED per subscriber per month)</t>
+        </is>
+      </c>
+      <c r="B16" s="33">
+        <f>Assumptions!$C$37*(1+Assumptions!$C$38)^0</f>
+        <v/>
+      </c>
+      <c r="C16" s="33">
+        <f>Assumptions!$C$37*(1+Assumptions!$C$38)^1</f>
+        <v/>
+      </c>
+      <c r="D16" s="33">
+        <f>Assumptions!$C$37*(1+Assumptions!$C$38)^2</f>
+        <v/>
+      </c>
+      <c r="E16" s="33">
+        <f>Assumptions!$C$37*(1+Assumptions!$C$38)^3</f>
+        <v/>
+      </c>
+      <c r="F16" s="33">
+        <f>Assumptions!$C$37*(1+Assumptions!$C$38)^4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Wholesale direct cost / wholesale revenue (no disclosed unit — flagged)</t>
+        </is>
+      </c>
+      <c r="B17" s="11">
+        <f>Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="C17" s="11">
+        <f>Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="D17" s="11">
+        <f>Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="E17" s="11">
+        <f>Assumptions!$C$39</f>
+        <v/>
+      </c>
+      <c r="F17" s="11">
+        <f>Assumptions!$C$39</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Operating expense stack — one escalator per cost class</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ICT direct cost / ICT revenue (no disclosed unit — flagged)</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
+        <f>Assumptions!$C$40</f>
+        <v/>
+      </c>
+      <c r="C18" s="11">
+        <f>Assumptions!$C$40</f>
+        <v/>
+      </c>
+      <c r="D18" s="11">
+        <f>Assumptions!$C$40</f>
+        <v/>
+      </c>
+      <c r="E18" s="11">
+        <f>Assumptions!$C$40</f>
+        <v/>
+      </c>
+      <c r="F18" s="11">
+        <f>Assumptions!$C$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Direct cost (AED mn) — volume x cost per unit</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Staff (wage escalator)</t>
-        </is>
-      </c>
-      <c r="B19" s="31">
-        <f>Assumptions!$C$27*(1+Assumptions!$C$28)^0</f>
-        <v/>
-      </c>
-      <c r="C19" s="31">
-        <f>Assumptions!$C$27*(1+Assumptions!$C$28)^1</f>
-        <v/>
-      </c>
-      <c r="D19" s="31">
-        <f>Assumptions!$C$27*(1+Assumptions!$C$28)^2</f>
-        <v/>
-      </c>
-      <c r="E19" s="31">
-        <f>Assumptions!$C$27*(1+Assumptions!$C$28)^3</f>
-        <v/>
-      </c>
-      <c r="F19" s="31">
-        <f>Assumptions!$C$27*(1+Assumptions!$C$28)^4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Network &amp; maintenance (network-scale escalator)</t>
-        </is>
-      </c>
-      <c r="B20" s="31">
-        <f>Assumptions!$C$29*(1+Assumptions!$C$30)^1</f>
-        <v/>
-      </c>
-      <c r="C20" s="31">
-        <f>Assumptions!$C$29*(1+Assumptions!$C$30)^2</f>
-        <v/>
-      </c>
-      <c r="D20" s="31">
-        <f>Assumptions!$C$29*(1+Assumptions!$C$30)^3</f>
-        <v/>
-      </c>
-      <c r="E20" s="31">
-        <f>Assumptions!$C$29*(1+Assumptions!$C$30)^4</f>
-        <v/>
-      </c>
-      <c r="F20" s="31">
-        <f>Assumptions!$C$29*(1+Assumptions!$C$30)^5</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Marketing (% of revenue)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="B21" s="31">
-        <f>E9*Assumptions!$C$35</f>
+        <f>Assumptions!$C$41+(Assumptions!$C$15+Assumptions!$B$23)/2*B15*6/1000</f>
         <v/>
       </c>
       <c r="C21" s="31">
-        <f>F9*Assumptions!$C$35</f>
+        <f>(Assumptions!$B$23+Assumptions!$C$23)/2*C15*12/1000</f>
         <v/>
       </c>
       <c r="D21" s="31">
-        <f>G9*Assumptions!$C$35</f>
+        <f>(Assumptions!$C$23+Assumptions!$D$23)/2*D15*12/1000</f>
         <v/>
       </c>
       <c r="E21" s="31">
-        <f>H9*Assumptions!$C$35</f>
+        <f>(Assumptions!$D$23+Assumptions!$E$23)/2*E15*12/1000</f>
         <v/>
       </c>
       <c r="F21" s="31">
-        <f>I9*Assumptions!$C$35</f>
+        <f>(Assumptions!$E$23+Assumptions!$F$23)/2*F15*12/1000</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Telecom licence and related fees (% of revenue)</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="B22" s="31">
-        <f>E9*Assumptions!$C$36</f>
+        <f>Assumptions!$C$42+(Assumptions!$C$16+Assumptions!$B$24)/2*B16*6/1000</f>
         <v/>
       </c>
       <c r="C22" s="31">
-        <f>F9*Assumptions!$C$36</f>
+        <f>(Assumptions!$B$24+Assumptions!$C$24)/2*C16*12/1000</f>
         <v/>
       </c>
       <c r="D22" s="31">
-        <f>G9*Assumptions!$C$36</f>
+        <f>(Assumptions!$C$24+Assumptions!$D$24)/2*D16*12/1000</f>
         <v/>
       </c>
       <c r="E22" s="31">
-        <f>H9*Assumptions!$C$36</f>
+        <f>(Assumptions!$D$24+Assumptions!$E$24)/2*E16*12/1000</f>
         <v/>
       </c>
       <c r="F22" s="31">
-        <f>I9*Assumptions!$C$36</f>
+        <f>(Assumptions!$E$24+Assumptions!$F$24)/2*F16*12/1000</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Administrative (CPI escalator)</t>
+          <t>Wholesale</t>
         </is>
       </c>
       <c r="B23" s="31">
-        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^1</f>
+        <f>Assumptions!$C$43+(E7-Assumptions!$C$19)*B17</f>
         <v/>
       </c>
       <c r="C23" s="31">
-        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^2</f>
+        <f>F7*C17</f>
         <v/>
       </c>
       <c r="D23" s="31">
-        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^3</f>
+        <f>G7*D17</f>
         <v/>
       </c>
       <c r="E23" s="31">
-        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^4</f>
+        <f>H7*E17</f>
         <v/>
       </c>
       <c r="F23" s="31">
-        <f>Assumptions!$C$31*(1+Assumptions!$C$32)^5</f>
+        <f>I7*F17</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Other operating expense (CPI escalator)</t>
+          <t>ICT and associated telecom services</t>
         </is>
       </c>
       <c r="B24" s="31">
-        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^1</f>
+        <f>Assumptions!$C$44+(E8-Assumptions!$C$20)*B18</f>
         <v/>
       </c>
       <c r="C24" s="31">
-        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^2</f>
+        <f>F8*C18</f>
         <v/>
       </c>
       <c r="D24" s="31">
-        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^3</f>
+        <f>G8*D18</f>
         <v/>
       </c>
       <c r="E24" s="31">
-        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^4</f>
+        <f>H8*E18</f>
         <v/>
       </c>
       <c r="F24" s="31">
-        <f>Assumptions!$C$33*(1+Assumptions!$C$34)^5</f>
+        <f>I8*F18</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Expected credit losses (% of revenue)</t>
-        </is>
-      </c>
-      <c r="B25" s="31">
-        <f>E9*Assumptions!$C$37</f>
-        <v/>
-      </c>
-      <c r="C25" s="31">
-        <f>F9*Assumptions!$C$37</f>
-        <v/>
-      </c>
-      <c r="D25" s="31">
-        <f>G9*Assumptions!$C$37</f>
-        <v/>
-      </c>
-      <c r="E25" s="31">
-        <f>H9*Assumptions!$C$37</f>
-        <v/>
-      </c>
-      <c r="F25" s="31">
-        <f>I9*Assumptions!$C$37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Less other operating income</t>
-        </is>
-      </c>
-      <c r="B26" s="31">
-        <f>-Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="C26" s="31">
-        <f>-Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="D26" s="31">
-        <f>-Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="E26" s="31">
-        <f>-Assumptions!$C$38</f>
-        <v/>
-      </c>
-      <c r="F26" s="31">
-        <f>-Assumptions!$C$38</f>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Total direct cost</t>
+        </is>
+      </c>
+      <c r="B25" s="32">
+        <f>SUM(B21:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="32">
+        <f>SUM(C21:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="32">
+        <f>SUM(D21:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="32">
+        <f>SUM(E21:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="32">
+        <f>SUM(F21:F24)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Total operating expenses before D&amp;A</t>
-        </is>
-      </c>
-      <c r="B27" s="30">
-        <f>SUM(B19:B26)</f>
-        <v/>
-      </c>
-      <c r="C27" s="30">
-        <f>SUM(C19:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="30">
-        <f>SUM(D19:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="30">
-        <f>SUM(E19:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="30">
-        <f>SUM(F19:F26)</f>
-        <v/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Contribution = revenue less direct cost — AN OUTPUT, NOT AN INPUT</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Group EBITDA (contribution less the opex stack)</t>
-        </is>
-      </c>
-      <c r="B28" s="30">
-        <f>B16-B27</f>
-        <v/>
-      </c>
-      <c r="C28" s="30">
-        <f>C16-C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="30">
-        <f>D16-D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="30">
-        <f>E16-E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="30">
-        <f>F16-F27</f>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="B28" s="31">
+        <f>E5-B21</f>
+        <v/>
+      </c>
+      <c r="C28" s="31">
+        <f>F5-C21</f>
+        <v/>
+      </c>
+      <c r="D28" s="31">
+        <f>G5-D21</f>
+        <v/>
+      </c>
+      <c r="E28" s="31">
+        <f>H5-E21</f>
+        <v/>
+      </c>
+      <c r="F28" s="31">
+        <f>I5-F21</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Group EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B29" s="11">
-        <f>B28/E$9</f>
-        <v/>
-      </c>
-      <c r="C29" s="11">
-        <f>C28/F$9</f>
-        <v/>
-      </c>
-      <c r="D29" s="11">
-        <f>D28/G$9</f>
-        <v/>
-      </c>
-      <c r="E29" s="11">
-        <f>E28/H$9</f>
-        <v/>
-      </c>
-      <c r="F29" s="11">
-        <f>F28/I$9</f>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="B29" s="31">
+        <f>E6-B22</f>
+        <v/>
+      </c>
+      <c r="C29" s="31">
+        <f>F6-C22</f>
+        <v/>
+      </c>
+      <c r="D29" s="31">
+        <f>G6-D22</f>
+        <v/>
+      </c>
+      <c r="E29" s="31">
+        <f>H6-E22</f>
+        <v/>
+      </c>
+      <c r="F29" s="31">
+        <f>I6-F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="B30" s="31">
+        <f>E7-B23</f>
+        <v/>
+      </c>
+      <c r="C30" s="31">
+        <f>F7-C23</f>
+        <v/>
+      </c>
+      <c r="D30" s="31">
+        <f>G7-D23</f>
+        <v/>
+      </c>
+      <c r="E30" s="31">
+        <f>H7-E23</f>
+        <v/>
+      </c>
+      <c r="F30" s="31">
+        <f>I7-F23</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>The unit build behind Mobile and Fixed (triangulation shown, not asserted)</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>ICT and associated telecom services</t>
+        </is>
+      </c>
+      <c r="B31" s="31">
+        <f>E8-B24</f>
+        <v/>
+      </c>
+      <c r="C31" s="31">
+        <f>F8-C24</f>
+        <v/>
+      </c>
+      <c r="D31" s="31">
+        <f>G8-D24</f>
+        <v/>
+      </c>
+      <c r="E31" s="31">
+        <f>H8-E24</f>
+        <v/>
+      </c>
+      <c r="F31" s="31">
+        <f>I8-F24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Total contribution</t>
+        </is>
+      </c>
+      <c r="B32" s="32">
+        <f>SUM(B28:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="32">
+        <f>SUM(C28:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="32">
+        <f>SUM(D28:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="32">
+        <f>SUM(E28:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="32">
+        <f>SUM(F28:F31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Contribution margin — computed, never assumed</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Mobile subscribers, end of year ('000)</t>
-        </is>
-      </c>
-      <c r="B32" s="31">
-        <f>Assumptions!$B$13</f>
-        <v/>
-      </c>
-      <c r="C32" s="31">
-        <f>Assumptions!$C$13</f>
-        <v/>
-      </c>
-      <c r="D32" s="31">
-        <f>Assumptions!$D$13</f>
-        <v/>
-      </c>
-      <c r="E32" s="31">
-        <f>Assumptions!$E$13</f>
-        <v/>
-      </c>
-      <c r="F32" s="31">
-        <f>Assumptions!$F$13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Average mobile base ('000) — (prior end + end)/2</t>
-        </is>
-      </c>
-      <c r="B33" s="31">
-        <f>(9280+Assumptions!$B$13)/2</f>
-        <v/>
-      </c>
-      <c r="C33" s="31">
-        <f>(Assumptions!$B$13+Assumptions!$C$13)/2</f>
-        <v/>
-      </c>
-      <c r="D33" s="31">
-        <f>(Assumptions!$C$13+Assumptions!$D$13)/2</f>
-        <v/>
-      </c>
-      <c r="E33" s="31">
-        <f>(Assumptions!$D$13+Assumptions!$E$13)/2</f>
-        <v/>
-      </c>
-      <c r="F33" s="31">
-        <f>(Assumptions!$E$13+Assumptions!$F$13)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Blended mobile ARPU (AED/month)</t>
-        </is>
-      </c>
-      <c r="B34" s="32">
-        <f>Assumptions!$B$15</f>
-        <v/>
-      </c>
-      <c r="C34" s="32">
-        <f>Assumptions!$C$15</f>
-        <v/>
-      </c>
-      <c r="D34" s="32">
-        <f>Assumptions!$D$15</f>
-        <v/>
-      </c>
-      <c r="E34" s="32">
-        <f>Assumptions!$E$15</f>
-        <v/>
-      </c>
-      <c r="F34" s="32">
-        <f>Assumptions!$F$15</f>
-        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Unit-implied mobile revenue — average base x ARPU x 12 (FY2026 is H1 actual + unit-built H2, so the check applies from FY2027)</t>
-        </is>
-      </c>
-      <c r="B35" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="31">
-        <f>C33*C34*12/1000</f>
-        <v/>
-      </c>
-      <c r="D35" s="31">
-        <f>D33*D34*12/1000</f>
-        <v/>
-      </c>
-      <c r="E35" s="31">
-        <f>E33*E34*12/1000</f>
-        <v/>
-      </c>
-      <c r="F35" s="31">
-        <f>F33*F34*12/1000</f>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="B35" s="11">
+        <f>B28/E5</f>
+        <v/>
+      </c>
+      <c r="C35" s="11">
+        <f>C28/F5</f>
+        <v/>
+      </c>
+      <c r="D35" s="11">
+        <f>D28/G5</f>
+        <v/>
+      </c>
+      <c r="E35" s="11">
+        <f>E28/H5</f>
+        <v/>
+      </c>
+      <c r="F35" s="11">
+        <f>F28/I5</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Pasted mobile segment revenue (the build output above)</t>
-        </is>
-      </c>
-      <c r="B36" s="18">
-        <f>E5</f>
-        <v/>
-      </c>
-      <c r="C36" s="18">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="D36" s="18">
-        <f>G5</f>
-        <v/>
-      </c>
-      <c r="E36" s="18">
-        <f>H5</f>
-        <v/>
-      </c>
-      <c r="F36" s="18">
-        <f>I5</f>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="B36" s="11">
+        <f>B29/E6</f>
+        <v/>
+      </c>
+      <c r="C36" s="11">
+        <f>C29/F6</f>
+        <v/>
+      </c>
+      <c r="D36" s="11">
+        <f>D29/G6</f>
+        <v/>
+      </c>
+      <c r="E36" s="11">
+        <f>E29/H6</f>
+        <v/>
+      </c>
+      <c r="F36" s="11">
+        <f>F29/I6</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="B37" s="11">
+        <f>B30/E7</f>
+        <v/>
+      </c>
+      <c r="C37" s="11">
+        <f>C30/F7</f>
+        <v/>
+      </c>
+      <c r="D37" s="11">
+        <f>D30/G7</f>
+        <v/>
+      </c>
+      <c r="E37" s="11">
+        <f>E30/H7</f>
+        <v/>
+      </c>
+      <c r="F37" s="11">
+        <f>F30/I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>ICT and associated telecom services</t>
+        </is>
+      </c>
+      <c r="B38" s="11">
+        <f>B31/E8</f>
+        <v/>
+      </c>
+      <c r="C38" s="11">
+        <f>C31/F8</f>
+        <v/>
+      </c>
+      <c r="D38" s="11">
+        <f>D31/G8</f>
+        <v/>
+      </c>
+      <c r="E38" s="11">
+        <f>E31/H8</f>
+        <v/>
+      </c>
+      <c r="F38" s="11">
+        <f>F31/I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Group gross margin</t>
+        </is>
+      </c>
+      <c r="B39" s="14">
+        <f>B32/E9</f>
+        <v/>
+      </c>
+      <c r="C39" s="14">
+        <f>C32/F9</f>
+        <v/>
+      </c>
+      <c r="D39" s="14">
+        <f>D32/G9</f>
+        <v/>
+      </c>
+      <c r="E39" s="14">
+        <f>E32/H9</f>
+        <v/>
+      </c>
+      <c r="F39" s="14">
+        <f>F32/I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Operating expense stack — one escalator per cost class</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Staff (wage escalator)</t>
+        </is>
+      </c>
+      <c r="B42" s="31">
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^0</f>
+        <v/>
+      </c>
+      <c r="C42" s="31">
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^1</f>
+        <v/>
+      </c>
+      <c r="D42" s="31">
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^2</f>
+        <v/>
+      </c>
+      <c r="E42" s="31">
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^3</f>
+        <v/>
+      </c>
+      <c r="F42" s="31">
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Network &amp; maintenance (network-scale escalator)</t>
+        </is>
+      </c>
+      <c r="B43" s="31">
+        <f>Assumptions!$C$50*(1+Assumptions!$C$51)^1</f>
+        <v/>
+      </c>
+      <c r="C43" s="31">
+        <f>Assumptions!$C$50*(1+Assumptions!$C$51)^2</f>
+        <v/>
+      </c>
+      <c r="D43" s="31">
+        <f>Assumptions!$C$50*(1+Assumptions!$C$51)^3</f>
+        <v/>
+      </c>
+      <c r="E43" s="31">
+        <f>Assumptions!$C$50*(1+Assumptions!$C$51)^4</f>
+        <v/>
+      </c>
+      <c r="F43" s="31">
+        <f>Assumptions!$C$50*(1+Assumptions!$C$51)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Marketing (% of revenue)</t>
+        </is>
+      </c>
+      <c r="B44" s="31">
+        <f>E9*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="C44" s="31">
+        <f>F9*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="D44" s="31">
+        <f>G9*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="E44" s="31">
+        <f>H9*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="F44" s="31">
+        <f>I9*Assumptions!$C$56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Telecom licence and related fees (% of revenue)</t>
+        </is>
+      </c>
+      <c r="B45" s="31">
+        <f>E9*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="C45" s="31">
+        <f>F9*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="D45" s="31">
+        <f>G9*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="E45" s="31">
+        <f>H9*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="F45" s="31">
+        <f>I9*Assumptions!$C$57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Administrative (CPI escalator)</t>
+        </is>
+      </c>
+      <c r="B46" s="31">
+        <f>Assumptions!$C$52*(1+Assumptions!$C$53)^1</f>
+        <v/>
+      </c>
+      <c r="C46" s="31">
+        <f>Assumptions!$C$52*(1+Assumptions!$C$53)^2</f>
+        <v/>
+      </c>
+      <c r="D46" s="31">
+        <f>Assumptions!$C$52*(1+Assumptions!$C$53)^3</f>
+        <v/>
+      </c>
+      <c r="E46" s="31">
+        <f>Assumptions!$C$52*(1+Assumptions!$C$53)^4</f>
+        <v/>
+      </c>
+      <c r="F46" s="31">
+        <f>Assumptions!$C$52*(1+Assumptions!$C$53)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Other operating expense (CPI escalator)</t>
+        </is>
+      </c>
+      <c r="B47" s="31">
+        <f>Assumptions!$C$54*(1+Assumptions!$C$55)^1</f>
+        <v/>
+      </c>
+      <c r="C47" s="31">
+        <f>Assumptions!$C$54*(1+Assumptions!$C$55)^2</f>
+        <v/>
+      </c>
+      <c r="D47" s="31">
+        <f>Assumptions!$C$54*(1+Assumptions!$C$55)^3</f>
+        <v/>
+      </c>
+      <c r="E47" s="31">
+        <f>Assumptions!$C$54*(1+Assumptions!$C$55)^4</f>
+        <v/>
+      </c>
+      <c r="F47" s="31">
+        <f>Assumptions!$C$54*(1+Assumptions!$C$55)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Expected credit losses (% of revenue)</t>
+        </is>
+      </c>
+      <c r="B48" s="31">
+        <f>E9*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="C48" s="31">
+        <f>F9*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="D48" s="31">
+        <f>G9*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="E48" s="31">
+        <f>H9*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="F48" s="31">
+        <f>I9*Assumptions!$C$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Less other operating income</t>
+        </is>
+      </c>
+      <c r="B49" s="31">
+        <f>-Assumptions!$C$59</f>
+        <v/>
+      </c>
+      <c r="C49" s="31">
+        <f>-Assumptions!$C$59</f>
+        <v/>
+      </c>
+      <c r="D49" s="31">
+        <f>-Assumptions!$C$59</f>
+        <v/>
+      </c>
+      <c r="E49" s="31">
+        <f>-Assumptions!$C$59</f>
+        <v/>
+      </c>
+      <c r="F49" s="31">
+        <f>-Assumptions!$C$59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Total operating expenses before D&amp;A</t>
+        </is>
+      </c>
+      <c r="B50" s="32">
+        <f>SUM(B42:B49)</f>
+        <v/>
+      </c>
+      <c r="C50" s="32">
+        <f>SUM(C42:C49)</f>
+        <v/>
+      </c>
+      <c r="D50" s="32">
+        <f>SUM(D42:D49)</f>
+        <v/>
+      </c>
+      <c r="E50" s="32">
+        <f>SUM(E42:E49)</f>
+        <v/>
+      </c>
+      <c r="F50" s="32">
+        <f>SUM(F42:F49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Group EBITDA (contribution less the opex stack)</t>
+        </is>
+      </c>
+      <c r="B51" s="32">
+        <f>B32-B50</f>
+        <v/>
+      </c>
+      <c r="C51" s="32">
+        <f>C32-C50</f>
+        <v/>
+      </c>
+      <c r="D51" s="32">
+        <f>D32-D50</f>
+        <v/>
+      </c>
+      <c r="E51" s="32">
+        <f>E32-E50</f>
+        <v/>
+      </c>
+      <c r="F51" s="32">
+        <f>F32-F50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Group EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B52" s="11">
+        <f>B51/E$9</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>C51/F$9</f>
+        <v/>
+      </c>
+      <c r="D52" s="11">
+        <f>D51/G$9</f>
+        <v/>
+      </c>
+      <c r="E52" s="11">
+        <f>E51/H$9</f>
+        <v/>
+      </c>
+      <c r="F52" s="11">
+        <f>F51/I$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>The unit build behind Mobile and Fixed (triangulation shown, not asserted)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Mobile subscribers, end of year ('000)</t>
+        </is>
+      </c>
+      <c r="B55" s="31">
+        <f>Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="C55" s="31">
+        <f>Assumptions!$C$23</f>
+        <v/>
+      </c>
+      <c r="D55" s="31">
+        <f>Assumptions!$D$23</f>
+        <v/>
+      </c>
+      <c r="E55" s="31">
+        <f>Assumptions!$E$23</f>
+        <v/>
+      </c>
+      <c r="F55" s="31">
+        <f>Assumptions!$F$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Average mobile base ('000) — (prior end + end)/2</t>
+        </is>
+      </c>
+      <c r="B56" s="31">
+        <f>(9280+Assumptions!$B$23)/2</f>
+        <v/>
+      </c>
+      <c r="C56" s="31">
+        <f>(Assumptions!$B$23+Assumptions!$C$23)/2</f>
+        <v/>
+      </c>
+      <c r="D56" s="31">
+        <f>(Assumptions!$C$23+Assumptions!$D$23)/2</f>
+        <v/>
+      </c>
+      <c r="E56" s="31">
+        <f>(Assumptions!$D$23+Assumptions!$E$23)/2</f>
+        <v/>
+      </c>
+      <c r="F56" s="31">
+        <f>(Assumptions!$E$23+Assumptions!$F$23)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Blended mobile ARPU (AED/month)</t>
+        </is>
+      </c>
+      <c r="B57" s="35">
+        <f>Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="C57" s="35">
+        <f>Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="D57" s="35">
+        <f>Assumptions!$D$25</f>
+        <v/>
+      </c>
+      <c r="E57" s="35">
+        <f>Assumptions!$E$25</f>
+        <v/>
+      </c>
+      <c r="F57" s="35">
+        <f>Assumptions!$F$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Unit-implied mobile revenue — average base x ARPU x 12 (FY2026 is H1 actual + unit-built H2, so the check applies from FY2027)</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C58" s="31">
+        <f>C56*C57*12/1000</f>
+        <v/>
+      </c>
+      <c r="D58" s="31">
+        <f>D56*D57*12/1000</f>
+        <v/>
+      </c>
+      <c r="E58" s="31">
+        <f>E56*E57*12/1000</f>
+        <v/>
+      </c>
+      <c r="F58" s="31">
+        <f>F56*F57*12/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Pasted mobile segment revenue (the build output above)</t>
+        </is>
+      </c>
+      <c r="B59" s="18">
+        <f>E5</f>
+        <v/>
+      </c>
+      <c r="C59" s="18">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="D59" s="18">
+        <f>G5</f>
+        <v/>
+      </c>
+      <c r="E59" s="18">
+        <f>H5</f>
+        <v/>
+      </c>
+      <c r="F59" s="18">
+        <f>I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
           <t>Check — unit-implied less pasted</t>
         </is>
       </c>
-      <c r="B37" s="31" t="inlineStr">
+      <c r="B60" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C37" s="32">
-        <f>C35-C36</f>
-        <v/>
-      </c>
-      <c r="D37" s="32">
-        <f>D35-D36</f>
-        <v/>
-      </c>
-      <c r="E37" s="32">
-        <f>E35-E36</f>
-        <v/>
-      </c>
-      <c r="F37" s="32">
-        <f>F35-F36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="C60" s="35">
+        <f>C58-C59</f>
+        <v/>
+      </c>
+      <c r="D60" s="35">
+        <f>D58-D59</f>
+        <v/>
+      </c>
+      <c r="E60" s="35">
+        <f>E58-E59</f>
+        <v/>
+      </c>
+      <c r="F60" s="35">
+        <f>F58-F59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>FY2025 reconciliation: average base 9,310k x ARPU 63.3 x 12 = 7,072 vs the audited mobile segment 7,075 (−0.04%). Wholesale and ICT have no disclosed unit KPIs — segment-level growth is the finest sourced level, and that gap is flagged.</t>
         </is>
@@ -7351,8 +8164,8 @@
           <t>Justified price / earnings (GCC peer median)</t>
         </is>
       </c>
-      <c r="C6" s="33">
-        <f>Assumptions!$C$72</f>
+      <c r="C6" s="36">
+        <f>Assumptions!$C$93</f>
         <v/>
       </c>
     </row>
@@ -7373,7 +8186,7 @@
           <t>Anchor accretion factor</t>
         </is>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="37">
         <f>DCF!C62</f>
         <v/>
       </c>
@@ -7385,7 +8198,7 @@
         </is>
       </c>
       <c r="C9" s="8">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -7399,7 +8212,7 @@
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>C7*C8-C9</f>
         <v/>
       </c>
@@ -7425,7 +8238,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="36">
         <f>Assumptions!$C$5/'Income Statement'!D19</f>
         <v/>
       </c>
@@ -7436,8 +8249,8 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C14" s="33">
-        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$62-Assumptions!$C$63)/'Income Statement'!D9</f>
+      <c r="C14" s="36">
+        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$83-Assumptions!$C$84)/'Income Statement'!D9</f>
         <v/>
       </c>
     </row>
@@ -7459,7 +8272,7 @@
         </is>
       </c>
       <c r="C16" s="11">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
     </row>
@@ -7570,8 +8383,8 @@
         </is>
       </c>
       <c r="B27" s="15" t="n"/>
-      <c r="C27" s="29">
-        <f>C26*Assumptions!$C$72*DCF!$C$62-Assumptions!$C$68</f>
+      <c r="C27" s="30">
+        <f>C26*Assumptions!$C$93*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -7580,11 +8393,11 @@
         </is>
       </c>
       <c r="E27" s="10">
-        <f>C26*12*DCF!$C$62-Assumptions!$C$68</f>
+        <f>C26*12*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="F27" s="10">
-        <f>C26*18.5*DCF!$C$62-Assumptions!$C$68</f>
+        <f>C26*18.5*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -7618,7 +8431,7 @@
         </is>
       </c>
       <c r="C31" s="11">
-        <f>Assumptions!$C$74</f>
+        <f>Assumptions!$C$95</f>
         <v/>
       </c>
     </row>
@@ -7650,8 +8463,8 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C34" s="35">
-        <f>(C31-Assumptions!$C$59)/(C33-Assumptions!$C$59)</f>
+      <c r="C34" s="38">
+        <f>(C31-Assumptions!$C$80)/(C33-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -7662,8 +8475,8 @@
         </is>
       </c>
       <c r="B35" s="15" t="n"/>
-      <c r="C35" s="29">
-        <f>C30*C34*DCF!$C$62-Assumptions!$C$68</f>
+      <c r="C35" s="30">
+        <f>C30*C34*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -7672,11 +8485,11 @@
         </is>
       </c>
       <c r="E35" s="10">
-        <f>((Assumptions!$C$74-Assumptions!$C$59)/((DCF!C40+DCF!C50)/2+0.01-Assumptions!$C$59))*C30*DCF!$C$62-Assumptions!$C$68</f>
+        <f>((Assumptions!$C$95-Assumptions!$C$80)/((DCF!C40+DCF!C50)/2+0.01-Assumptions!$C$80))*C30*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="F35" s="10">
-        <f>((Assumptions!$C$74+0.02-Assumptions!$C$59)/(DCF!C50-Assumptions!$C$59))*C30*DCF!$C$62-Assumptions!$C$68</f>
+        <f>((Assumptions!$C$95+0.02-Assumptions!$C$80)/(DCF!C50-Assumptions!$C$80))*C30*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -7788,23 +8601,23 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>Segments!B28</f>
+        <f>Segments!B51</f>
         <v/>
       </c>
       <c r="C6" s="18">
-        <f>Segments!C28</f>
+        <f>Segments!C51</f>
         <v/>
       </c>
       <c r="D6" s="18">
-        <f>Segments!D28</f>
+        <f>Segments!D51</f>
         <v/>
       </c>
       <c r="E6" s="18">
-        <f>Segments!E28</f>
+        <f>Segments!E51</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>Segments!F28</f>
+        <f>Segments!F51</f>
         <v/>
       </c>
     </row>
@@ -7868,23 +8681,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="29">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -7950,23 +8763,23 @@
         </is>
       </c>
       <c r="B12" s="31">
-        <f>-B5*Assumptions!$B$41</f>
+        <f>-B5*Assumptions!$B$62</f>
         <v/>
       </c>
       <c r="C12" s="31">
-        <f>-C5*Assumptions!$C$41</f>
+        <f>-C5*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="D12" s="31">
-        <f>-D5*Assumptions!$D$41</f>
+        <f>-D5*Assumptions!$D$62</f>
         <v/>
       </c>
       <c r="E12" s="31">
-        <f>-E5*Assumptions!$E$41</f>
+        <f>-E5*Assumptions!$E$62</f>
         <v/>
       </c>
       <c r="F12" s="31">
-        <f>-F5*Assumptions!$F$41</f>
+        <f>-F5*Assumptions!$F$62</f>
         <v/>
       </c>
     </row>
@@ -7977,23 +8790,23 @@
         </is>
       </c>
       <c r="B13" s="31">
-        <f>Assumptions!$B$45</f>
+        <f>Assumptions!$B$66</f>
         <v/>
       </c>
       <c r="C13" s="31">
-        <f>Assumptions!$C$45</f>
+        <f>Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="D13" s="31">
-        <f>Assumptions!$D$45</f>
+        <f>Assumptions!$D$66</f>
         <v/>
       </c>
       <c r="E13" s="31">
-        <f>Assumptions!$E$45</f>
+        <f>Assumptions!$E$66</f>
         <v/>
       </c>
       <c r="F13" s="31">
-        <f>Assumptions!$F$45</f>
+        <f>Assumptions!$F$66</f>
         <v/>
       </c>
     </row>
@@ -8004,23 +8817,23 @@
         </is>
       </c>
       <c r="B14" s="31">
-        <f>-(B5*Assumptions!$C$46-'Balance Sheet'!D11)</f>
+        <f>-(B5*Assumptions!$C$67-'Balance Sheet'!D11)</f>
         <v/>
       </c>
       <c r="C14" s="31">
-        <f>-(C5-B5)*Assumptions!$C$46</f>
+        <f>-(C5-B5)*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>-(D5-C5)*Assumptions!$C$46</f>
+        <f>-(D5-C5)*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="E14" s="31">
-        <f>-(E5-D5)*Assumptions!$C$46</f>
+        <f>-(E5-D5)*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="F14" s="31">
-        <f>-(F5-E5)*Assumptions!$C$46</f>
+        <f>-(F5-E5)*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -8030,23 +8843,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="29">
         <f>B10+B11+B12+B14</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>C10+C11+C12+C14</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="29">
         <f>D10+D11+D12+D14</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>E10+E11+E12+E14</f>
         <v/>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>F10+F11+F12+F14</f>
         <v/>
       </c>
@@ -8057,23 +8870,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="39">
         <f>$C$47-($C$47-$C$54)*B58</f>
         <v/>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="39">
         <f>$C$47-($C$47-$C$54)*C58</f>
         <v/>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="39">
         <f>$C$47-($C$47-$C$54)*D58</f>
         <v/>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="39">
         <f>$C$47-($C$47-$C$54)*E58</f>
         <v/>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="39">
         <f>$C$47-($C$47-$C$54)*F58</f>
         <v/>
       </c>
@@ -8084,23 +8897,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="40">
         <f>1/(1+B16)</f>
         <v/>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="40">
         <f>B17/(1+C16)</f>
         <v/>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="40">
         <f>C17/(1+D16)</f>
         <v/>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="40">
         <f>D17/(1+E16)</f>
         <v/>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="40">
         <f>E17/(1+F16)</f>
         <v/>
       </c>
@@ -8111,23 +8924,23 @@
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="29">
         <f>B15*B17</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>C15*C17</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>D15*D17</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f>E15*E17</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f>F15*F17</f>
         <v/>
       </c>
@@ -8179,7 +8992,7 @@
         </is>
       </c>
       <c r="C24" s="16">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -8267,7 +9080,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="n"/>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <f>C31/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -8286,8 +9099,8 @@
           <t>Risk-free rate — Jan-2031 AED T-bond (longest liquid AED tenor)</t>
         </is>
       </c>
-      <c r="C35" s="38">
-        <f>Assumptions!$C$49</f>
+      <c r="C35" s="41">
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -8297,8 +9110,8 @@
           <t>Less UAE sovereign default spread (removed to avoid double-counting)</t>
         </is>
       </c>
-      <c r="C36" s="38">
-        <f>Assumptions!$C$50</f>
+      <c r="C36" s="41">
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -8308,7 +9121,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C37" s="36">
+      <c r="C37" s="39">
         <f>C35-C36</f>
         <v/>
       </c>
@@ -8319,8 +9132,8 @@
           <t>Beta (DU weekly vs the FTSE ADX General, 5 years)</t>
         </is>
       </c>
-      <c r="C38" s="39">
-        <f>Assumptions!$C$52</f>
+      <c r="C38" s="42">
+        <f>Assumptions!$C$73</f>
         <v/>
       </c>
     </row>
@@ -8330,8 +9143,8 @@
           <t>Equity risk premium (UAE total, rating basis)</t>
         </is>
       </c>
-      <c r="C39" s="38">
-        <f>Assumptions!$C$51</f>
+      <c r="C39" s="41">
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
     </row>
@@ -8341,7 +9154,7 @@
           <t>Cost of equity, explicit window</t>
         </is>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="39">
         <f>C37+C38*C39</f>
         <v/>
       </c>
@@ -8352,8 +9165,8 @@
           <t>Marginal cost of debt (AED sovereign + GCC telecom spread)</t>
         </is>
       </c>
-      <c r="C41" s="38">
-        <f>Assumptions!$C$53</f>
+      <c r="C41" s="41">
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -8363,7 +9176,7 @@
           <t>Cost of debt after tax (interest shields both fiscal legs)</t>
         </is>
       </c>
-      <c r="C42" s="36">
+      <c r="C42" s="39">
         <f>C41*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -8386,7 +9199,7 @@
         </is>
       </c>
       <c r="C44" s="18">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
@@ -8396,7 +9209,7 @@
           <t>Debt weight (leases / (leases + market capitalisation))</t>
         </is>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="39">
         <f>C44/(C44+C43)</f>
         <v/>
       </c>
@@ -8407,7 +9220,7 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C46" s="36">
+      <c r="C46" s="39">
         <f>1-C45</f>
         <v/>
       </c>
@@ -8419,7 +9232,7 @@
         </is>
       </c>
       <c r="B47" s="15" t="n"/>
-      <c r="C47" s="40">
+      <c r="C47" s="43">
         <f>C46*C40+C45*C42</f>
         <v/>
       </c>
@@ -8431,8 +9244,8 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C48" s="38">
-        <f>Assumptions!$C$55</f>
+      <c r="C48" s="41">
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
     </row>
@@ -8442,7 +9255,7 @@
           <t>Terminal risk-free net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C49" s="36">
+      <c r="C49" s="39">
         <f>C48-C36</f>
         <v/>
       </c>
@@ -8453,8 +9266,8 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C50" s="36">
-        <f>C49+C38*Assumptions!$C$56</f>
+      <c r="C50" s="39">
+        <f>C49+C38*Assumptions!$C$77</f>
         <v/>
       </c>
     </row>
@@ -8464,8 +9277,8 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C51" s="38">
-        <f>Assumptions!$C$57</f>
+      <c r="C51" s="41">
+        <f>Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
@@ -8475,7 +9288,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C52" s="36">
+      <c r="C52" s="39">
         <f>C51*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -8486,8 +9299,8 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C53" s="38">
-        <f>Assumptions!$C$58</f>
+      <c r="C53" s="41">
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
     </row>
@@ -8498,7 +9311,7 @@
         </is>
       </c>
       <c r="B54" s="15" t="n"/>
-      <c r="C54" s="40">
+      <c r="C54" s="43">
         <f>(1-C53)*C50+C53*C52</f>
         <v/>
       </c>
@@ -8542,24 +9355,24 @@
           <t>AED risk-free path</t>
         </is>
       </c>
-      <c r="B57" s="38">
-        <f>Assumptions!$B$54</f>
-        <v/>
-      </c>
-      <c r="C57" s="38">
-        <f>Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="D57" s="38">
-        <f>Assumptions!$D$54</f>
-        <v/>
-      </c>
-      <c r="E57" s="38">
-        <f>Assumptions!$E$54</f>
-        <v/>
-      </c>
-      <c r="F57" s="38">
-        <f>Assumptions!$F$54</f>
+      <c r="B57" s="41">
+        <f>Assumptions!$B$75</f>
+        <v/>
+      </c>
+      <c r="C57" s="41">
+        <f>Assumptions!$C$75</f>
+        <v/>
+      </c>
+      <c r="D57" s="41">
+        <f>Assumptions!$D$75</f>
+        <v/>
+      </c>
+      <c r="E57" s="41">
+        <f>Assumptions!$E$75</f>
+        <v/>
+      </c>
+      <c r="F57" s="41">
+        <f>Assumptions!$F$75</f>
         <v/>
       </c>
     </row>
@@ -8569,23 +9382,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B58" s="36">
+      <c r="B58" s="39">
         <f>($B$57-B57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="C58" s="36">
+      <c r="C58" s="39">
         <f>($B$57-C57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="D58" s="36">
+      <c r="D58" s="39">
         <f>($B$57-D57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="E58" s="36">
+      <c r="E58" s="39">
         <f>($B$57-E57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="F58" s="36">
+      <c r="F58" s="39">
         <f>($B$57-F57)/($B$57-$F$57)</f>
         <v/>
       </c>
@@ -8610,8 +9423,8 @@
           <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
         </is>
       </c>
-      <c r="C62" s="37">
-        <f>(1+C40)^(Assumptions!$C$69/365)</f>
+      <c r="C62" s="40">
+        <f>(1+C40)^(Assumptions!$C$90/365)</f>
         <v/>
       </c>
     </row>
@@ -8622,8 +9435,8 @@
         </is>
       </c>
       <c r="B63" s="15" t="n"/>
-      <c r="C63" s="29">
-        <f>C32*C62-Assumptions!$C$68</f>
+      <c r="C63" s="30">
+        <f>C32*C62-Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="D63" s="15" t="n"/>
@@ -8736,32 +9549,32 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="29" t="n">
         <v>13636.34</v>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="29" t="n">
         <v>14635.917</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="29" t="n">
         <v>15905.421</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="29">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="29">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -8784,23 +9597,23 @@
         <v>-5259.425</v>
       </c>
       <c r="E6" s="18">
-        <f>-(DCF!B5-Segments!B16)</f>
+        <f>-(DCF!B5-Segments!B32)</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>-(DCF!C5-Segments!C16)</f>
+        <f>-(DCF!C5-Segments!C32)</f>
         <v/>
       </c>
       <c r="G6" s="18">
-        <f>-(DCF!D5-Segments!D16)</f>
+        <f>-(DCF!D5-Segments!D32)</f>
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>-(DCF!E5-Segments!E16)</f>
+        <f>-(DCF!E5-Segments!E32)</f>
         <v/>
       </c>
       <c r="I6" s="18">
-        <f>-(DCF!F5-Segments!F16)</f>
+        <f>-(DCF!F5-Segments!F32)</f>
         <v/>
       </c>
     </row>
@@ -8862,23 +9675,23 @@
         <v>-3307.608</v>
       </c>
       <c r="E8" s="18">
-        <f>-Segments!B27</f>
+        <f>-Segments!B50</f>
         <v/>
       </c>
       <c r="F8" s="18">
-        <f>-Segments!C27</f>
+        <f>-Segments!C50</f>
         <v/>
       </c>
       <c r="G8" s="18">
-        <f>-Segments!D27</f>
+        <f>-Segments!D50</f>
         <v/>
       </c>
       <c r="H8" s="18">
-        <f>-Segments!E27</f>
+        <f>-Segments!E50</f>
         <v/>
       </c>
       <c r="I8" s="18">
-        <f>-Segments!F27</f>
+        <f>-Segments!F50</f>
         <v/>
       </c>
     </row>
@@ -8888,34 +9701,34 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="29" t="n">
         <v>5799.601</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="29">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="29">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -8975,23 +9788,23 @@
         <v>-2167.933</v>
       </c>
       <c r="E11" s="31">
-        <f>-('Balance Sheet'!E6+'Balance Sheet'!E9+Assumptions!$B$45)</f>
+        <f>-('Balance Sheet'!E6+'Balance Sheet'!E9+Assumptions!$B$66)</f>
         <v/>
       </c>
       <c r="F11" s="31">
-        <f>-('Balance Sheet'!F6+'Balance Sheet'!F9+Assumptions!$C$45)</f>
+        <f>-('Balance Sheet'!F6+'Balance Sheet'!F9+Assumptions!$C$66)</f>
         <v/>
       </c>
       <c r="G11" s="31">
-        <f>-('Balance Sheet'!G6+'Balance Sheet'!G9+Assumptions!$D$45)</f>
+        <f>-('Balance Sheet'!G6+'Balance Sheet'!G9+Assumptions!$D$66)</f>
         <v/>
       </c>
       <c r="H11" s="31">
-        <f>-('Balance Sheet'!H6+'Balance Sheet'!H9+Assumptions!$E$45)</f>
+        <f>-('Balance Sheet'!H6+'Balance Sheet'!H9+Assumptions!$E$66)</f>
         <v/>
       </c>
       <c r="I11" s="31">
-        <f>-('Balance Sheet'!I6+'Balance Sheet'!I9+Assumptions!$F$45)</f>
+        <f>-('Balance Sheet'!I6+'Balance Sheet'!I9+Assumptions!$F$66)</f>
         <v/>
       </c>
     </row>
@@ -9001,35 +9814,35 @@
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="29">
         <f>B9+B11</f>
         <v/>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>C9+C11</f>
         <v/>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <f>D9+D11</f>
         <v/>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>E9+E11</f>
         <v/>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <f>F9+F11</f>
         <v/>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="29">
         <f>G9+G11</f>
         <v/>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="29">
         <f>H9+H11</f>
         <v/>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="29">
         <f>I9+I11</f>
         <v/>
       </c>
@@ -9050,23 +9863,23 @@
         <v>74.672</v>
       </c>
       <c r="E13" s="31">
-        <f>Assumptions!$C$66*MAX('Balance Sheet'!D12,0)</f>
+        <f>Assumptions!$C$87*MAX('Balance Sheet'!D12,0)</f>
         <v/>
       </c>
       <c r="F13" s="31">
-        <f>Assumptions!$C$66*MAX('Balance Sheet'!E12,0)</f>
+        <f>Assumptions!$C$87*MAX('Balance Sheet'!E12,0)</f>
         <v/>
       </c>
       <c r="G13" s="31">
-        <f>Assumptions!$C$66*MAX('Balance Sheet'!F12,0)</f>
+        <f>Assumptions!$C$87*MAX('Balance Sheet'!F12,0)</f>
         <v/>
       </c>
       <c r="H13" s="31">
-        <f>Assumptions!$C$66*MAX('Balance Sheet'!G12,0)</f>
+        <f>Assumptions!$C$87*MAX('Balance Sheet'!G12,0)</f>
         <v/>
       </c>
       <c r="I13" s="31">
-        <f>Assumptions!$C$66*MAX('Balance Sheet'!H12,0)</f>
+        <f>Assumptions!$C$87*MAX('Balance Sheet'!H12,0)</f>
         <v/>
       </c>
     </row>
@@ -9086,23 +9899,23 @@
         <v>-95.054</v>
       </c>
       <c r="E14" s="31">
-        <f>-Assumptions!$C$67*'Balance Sheet'!E13</f>
+        <f>-Assumptions!$C$88*'Balance Sheet'!E13</f>
         <v/>
       </c>
       <c r="F14" s="31">
-        <f>-Assumptions!$C$67*'Balance Sheet'!F13</f>
+        <f>-Assumptions!$C$88*'Balance Sheet'!F13</f>
         <v/>
       </c>
       <c r="G14" s="31">
-        <f>-Assumptions!$C$67*'Balance Sheet'!G13</f>
+        <f>-Assumptions!$C$88*'Balance Sheet'!G13</f>
         <v/>
       </c>
       <c r="H14" s="31">
-        <f>-Assumptions!$C$67*'Balance Sheet'!H13</f>
+        <f>-Assumptions!$C$88*'Balance Sheet'!H13</f>
         <v/>
       </c>
       <c r="I14" s="31">
-        <f>-Assumptions!$C$67*'Balance Sheet'!I13</f>
+        <f>-Assumptions!$C$88*'Balance Sheet'!I13</f>
         <v/>
       </c>
     </row>
@@ -9128,32 +9941,32 @@
           <t>Profit before federal royalty and income tax</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
+      <c r="B16" s="29" t="n">
         <v>3558.501</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="29" t="n">
         <v>4306.151</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="29" t="n">
         <v>5149.122</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F12+F13+F14</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G12+G13+G14</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>H12+H13+H14</f>
         <v/>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>I12+I13+I14</f>
         <v/>
       </c>
@@ -9200,35 +10013,35 @@
           <t>Net profit</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="29">
         <f>B16+B17</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f>E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <f>G16+G17</f>
         <v/>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="29">
         <f>H16+H17</f>
         <v/>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="29">
         <f>I16+I17</f>
         <v/>
       </c>
@@ -9288,23 +10101,23 @@
         <v>0.64</v>
       </c>
       <c r="E20" s="10">
-        <f>E19*Assumptions!$C$65</f>
+        <f>E19*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F20" s="10">
-        <f>F19*Assumptions!$C$65</f>
+        <f>F19*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="G20" s="10">
-        <f>G19*Assumptions!$C$65</f>
+        <f>G19*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="H20" s="10">
-        <f>H19*Assumptions!$C$65</f>
+        <f>H19*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="I20" s="10">
-        <f>I19*Assumptions!$C$65</f>
+        <f>I19*Assumptions!$C$86</f>
         <v/>
       </c>
     </row>

--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -5202,13 +5202,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>9.881999525772653</v>
+        <v>11.53634760090742</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>7.773599620618121</v>
+        <v>9.557590446229586</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>11.63899944673476</v>
+        <v>13.18531189647228</v>
       </c>
     </row>
     <row r="25">

--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,23 +131,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1162,23 +1163,23 @@
       <c r="D5" s="23" t="n">
         <v>10288.767</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>D5-DCF!B12*Assumptions!$C$63-E6</f>
         <v/>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <f>E5-DCF!C12*Assumptions!$C$63-F6</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="32">
         <f>F5-DCF!D12*Assumptions!$C$63-G6</f>
         <v/>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <f>G5-DCF!E12*Assumptions!$C$63-H6</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="32">
         <f>H5-DCF!F12*Assumptions!$C$63-I6</f>
         <v/>
       </c>
@@ -1198,23 +1199,23 @@
       <c r="D6" s="23" t="n">
         <v>1557.989</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>Assumptions!$C$64*D5</f>
         <v/>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>Assumptions!$C$64*E5</f>
         <v/>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="32">
         <f>Assumptions!$C$64*F5</f>
         <v/>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <f>Assumptions!$C$64*G5</f>
         <v/>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="32">
         <f>Assumptions!$C$64*H5</f>
         <v/>
       </c>
@@ -1234,23 +1235,23 @@
       <c r="D7" s="23" t="n">
         <v>1515.395</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
@@ -1270,23 +1271,23 @@
       <c r="D8" s="23" t="n">
         <v>869.6</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>D8-DCF!B12*(1-Assumptions!$C$63)-E9</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>E8-DCF!C12*(1-Assumptions!$C$63)-F9</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>F8-DCF!D12*(1-Assumptions!$C$63)-G9</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>G8-DCF!E12*(1-Assumptions!$C$63)-H9</f>
         <v/>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="32">
         <f>H8-DCF!F12*(1-Assumptions!$C$63)-I9</f>
         <v/>
       </c>
@@ -1306,23 +1307,23 @@
       <c r="D9" s="23" t="n">
         <v>245.881</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>Assumptions!$C$65*D8</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>Assumptions!$C$65*E8</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="32">
         <f>Assumptions!$C$65*F8</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <f>Assumptions!$C$65*G8</f>
         <v/>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="32">
         <f>Assumptions!$C$65*H8</f>
         <v/>
       </c>
@@ -1333,7 +1334,7 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1344,23 +1345,23 @@
       <c r="D10" s="23" t="n">
         <v>413.22</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
@@ -1380,23 +1381,23 @@
       <c r="D11" s="23" t="n">
         <v>-1062.442</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>'Income Statement'!E5*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>'Income Statement'!F5*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="32">
         <f>'Income Statement'!G5*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>'Income Statement'!H5*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="32">
         <f>'Income Statement'!I5*Assumptions!$C$67</f>
         <v/>
       </c>
@@ -1416,23 +1417,23 @@
       <c r="D12" s="23" t="n">
         <v>2249.719</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>D12+'Income Statement'!E18-'Income Statement'!E11+DCF!B12+DCF!B14-'Income Statement'!E18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>E12+'Income Statement'!F18-'Income Statement'!F11+DCF!C12+DCF!C14-'Income Statement'!F18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="32">
         <f>F12+'Income Statement'!G18-'Income Statement'!G11+DCF!D12+DCF!D14-'Income Statement'!G18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="32">
         <f>G12+'Income Statement'!H18-'Income Statement'!H11+DCF!E12+DCF!E14-'Income Statement'!H18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="32">
         <f>H12+'Income Statement'!I18-'Income Statement'!I11+DCF!F12+DCF!F14-'Income Statement'!I18*Assumptions!$C$86</f>
         <v/>
       </c>
@@ -1452,59 +1453,59 @@
       <c r="D13" s="23" t="n">
         <v>1938.819</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="30" t="n">
         <v>9243.213</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="30" t="n">
         <v>9878.445</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="30" t="n">
         <v>10148.291</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>D14+'Income Statement'!E18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>E14+'Income Statement'!F18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <f>F14+'Income Statement'!G18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <f>G14+'Income Statement'!H18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="30">
         <f>H14+'Income Statement'!I18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
@@ -1515,35 +1516,35 @@
           <t>Net cash after lease liabilities</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <f>B12-B13</f>
         <v/>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>D12-D13</f>
         <v/>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>E12-E13</f>
         <v/>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>F12-F13</f>
         <v/>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>G12-G13</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="32">
         <f>H12-H13</f>
         <v/>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="32">
         <f>I12-I13</f>
         <v/>
       </c>
@@ -1554,35 +1555,35 @@
           <t>Lease liabilities / EBITDA</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="39">
         <f>B13/'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <f>C13/'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="39">
         <f>D13/'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="39">
         <f>E13/'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="39">
         <f>F13/'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G16" s="38">
+      <c r="G16" s="39">
         <f>G13/'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="39">
         <f>H13/'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I16" s="38">
+      <c r="I16" s="39">
         <f>I13/'Income Statement'!I9</f>
         <v/>
       </c>
@@ -1690,31 +1691,31 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="19">
         <f>'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="19">
         <f>'Income Statement'!I9</f>
         <v/>
       </c>
@@ -1764,33 +1765,33 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>DCF!B10</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>DCF!C10</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>DCF!D10</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="19">
         <f>DCF!E10</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="19">
         <f>DCF!F10</f>
         <v/>
       </c>
@@ -1801,33 +1802,33 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>DCF!B11</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>DCF!C11</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>DCF!D11</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <f>DCF!E11</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="19">
         <f>DCF!F11</f>
         <v/>
       </c>
@@ -1838,33 +1839,33 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f>DCF!B12</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>DCF!C12</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <f>DCF!D12</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="19">
         <f>DCF!E12</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="19">
         <f>DCF!F12</f>
         <v/>
       </c>
@@ -1875,33 +1876,33 @@
           <t>Memo — lease replacement, NOT deducted (leases are debt)</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f>DCF!B13</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>DCF!C13</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <f>DCF!D13</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <f>DCF!E13</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="19">
         <f>DCF!F13</f>
         <v/>
       </c>
@@ -1912,73 +1913,73 @@
           <t>Change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>-('Balance Sheet'!D11-'Balance Sheet'!C11)</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>DCF!B14</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>DCF!C14</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>DCF!D14</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="19">
         <f>DCF!E14</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="19">
         <f>DCF!F14</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>D9+D10+D11+D13</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>E9+E10+E11+E13</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>F9+F10+F11+F13</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <f>G9+G10+G11+G13</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <f>H9+H10+H11+H13</f>
         <v/>
       </c>
-      <c r="I14" s="15" t="n"/>
+      <c r="I14" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1992,23 +1993,23 @@
       <c r="C16" s="23" t="n">
         <v>-2629.085</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>-'Income Statement'!E18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>-'Income Statement'!F18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>-'Income Statement'!G18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>-'Income Statement'!H18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>-'Income Statement'!I18*Assumptions!$C$86</f>
         <v/>
       </c>
@@ -2019,7 +2020,7 @@
           <t>Cash conversion — operating cash flow as a share of EBITDA, FY2025</t>
         </is>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="9">
         <f>C7/C5</f>
         <v/>
       </c>
@@ -2132,35 +2133,35 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="19">
         <f>'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="19">
         <f>'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="19">
         <f>'Income Statement'!I5</f>
         <v/>
       </c>
@@ -2171,36 +2172,36 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="9">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="9">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9">
         <f>I5/H5-1</f>
         <v/>
       </c>
@@ -2211,35 +2212,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="19">
         <f>'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="19">
         <f>'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="19">
         <f>'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="19">
         <f>'Income Statement'!I9</f>
         <v/>
       </c>
@@ -2250,35 +2251,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <f>I7/I5</f>
         <v/>
       </c>
@@ -2289,35 +2290,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>'Income Statement'!B12</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>'Income Statement'!C12</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>'Income Statement'!D12</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>'Income Statement'!E12</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>'Income Statement'!F12</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="19">
         <f>'Income Statement'!G12</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="19">
         <f>'Income Statement'!H12</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="19">
         <f>'Income Statement'!I12</f>
         <v/>
       </c>
@@ -2328,35 +2329,35 @@
           <t>Net profit</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>'Income Statement'!B18</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>'Income Statement'!C18</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>'Income Statement'!D18</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>'Income Statement'!E18</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>'Income Statement'!F18</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <f>'Income Statement'!G18</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="19">
         <f>'Income Statement'!H18</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="19">
         <f>'Income Statement'!I18</f>
         <v/>
       </c>
@@ -2367,38 +2368,38 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>'Cash Flow'!D14</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <f>'Cash Flow'!E14</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="19">
         <f>'Cash Flow'!F14</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="19">
         <f>'Cash Flow'!G14</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="19">
         <f>'Cash Flow'!H14</f>
         <v/>
       </c>
@@ -2409,35 +2410,35 @@
           <t>Net cash after lease liabilities</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <f>'Balance Sheet'!B15</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <f>'Balance Sheet'!C15</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f>'Balance Sheet'!D15</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>'Balance Sheet'!E15</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <f>'Balance Sheet'!F15</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <f>'Balance Sheet'!G15</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="19">
         <f>'Balance Sheet'!H15</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="19">
         <f>'Balance Sheet'!I15</f>
         <v/>
       </c>
@@ -2448,36 +2449,36 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <f>'Balance Sheet'!C5+'Balance Sheet'!C7+'Balance Sheet'!C8+'Balance Sheet'!C10+'Balance Sheet'!C11</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>'Balance Sheet'!D5+'Balance Sheet'!D7+'Balance Sheet'!D8+'Balance Sheet'!D10+'Balance Sheet'!D11</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>'Balance Sheet'!E5+'Balance Sheet'!E7+'Balance Sheet'!E8+'Balance Sheet'!E10+'Balance Sheet'!E11</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>'Balance Sheet'!F5+'Balance Sheet'!F7+'Balance Sheet'!F8+'Balance Sheet'!F10+'Balance Sheet'!F11</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="19">
         <f>'Balance Sheet'!G5+'Balance Sheet'!G7+'Balance Sheet'!G8+'Balance Sheet'!G10+'Balance Sheet'!G11</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="19">
         <f>'Balance Sheet'!H5+'Balance Sheet'!H7+'Balance Sheet'!H8+'Balance Sheet'!H10+'Balance Sheet'!H11</f>
         <v/>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="19">
         <f>'Balance Sheet'!I5+'Balance Sheet'!I7+'Balance Sheet'!I8+'Balance Sheet'!I10+'Balance Sheet'!I11</f>
         <v/>
       </c>
@@ -2488,38 +2489,38 @@
           <t>Return on invested capital (average capital)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="17">
         <f>DCF!B10/((D13+E13)/2)</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="17">
         <f>DCF!C10/((E13+F13)/2)</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>DCF!D10/((F13+G13)/2)</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="17">
         <f>DCF!E10/((G13+H13)/2)</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="17">
         <f>DCF!F10/((H13+I13)/2)</f>
         <v/>
       </c>
@@ -2635,7 +2636,7 @@
       <c r="F5" s="7" t="n">
         <v>13.87837142039896</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="24" t="n">
         <v>0.49186</v>
       </c>
     </row>
@@ -2660,7 +2661,7 @@
       <c r="F6" s="7" t="n">
         <v>15.32471824257266</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="24" t="n">
         <v>0.48962</v>
       </c>
     </row>
@@ -2687,10 +2688,10 @@
           <t>Finishes 10% or more above spot</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="24" t="n">
         <v>0.09089999999999999</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="24" t="n">
         <v>0.21854</v>
       </c>
     </row>
@@ -2700,10 +2701,10 @@
           <t>Finishes 10% or more below spot</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="24" t="n">
         <v>0.07883999999999999</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="24" t="n">
         <v>0.21026</v>
       </c>
     </row>
@@ -2713,10 +2714,10 @@
           <t>Touches 10% above spot at any point</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="24" t="n">
         <v>0.1523</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="24" t="n">
         <v>0.40526</v>
       </c>
     </row>
@@ -2726,10 +2727,10 @@
           <t>Touches 10% below spot at any point</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="24" t="n">
         <v>0.128</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="24" t="n">
         <v>0.37854</v>
       </c>
     </row>
@@ -2761,7 +2762,7 @@
           <t>Annualised volatility (3-month anchor)</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="24" t="n">
         <v>0.2808947610903803</v>
       </c>
     </row>
@@ -2772,7 +2773,7 @@
         </is>
       </c>
       <c r="C17" s="8">
-        <f>Summary!C14</f>
+        <f>Summary!C15</f>
         <v/>
       </c>
     </row>
@@ -2782,7 +2783,7 @@
           <t>Anchor date</t>
         </is>
       </c>
-      <c r="C18" s="44" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -2835,7 +2836,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Terminal cost of capital (rows) x terminal growth (columns)</t>
         </is>
@@ -2980,7 +2981,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Explicit-window cost of capital (columns) x terminal cost of capital (rows)</t>
         </is>
@@ -3125,7 +3126,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Single-driver sensitivities — five engine re-runs per row; the parameter grid for each row is shown beside its name</t>
         </is>
@@ -3170,7 +3171,7 @@
       <c r="F22" s="7" t="n">
         <v>13.8943248227103</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
         <v/>
       </c>
@@ -3196,7 +3197,7 @@
       <c r="F23" s="7" t="n">
         <v>15.30952628288052</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
         <v/>
       </c>
@@ -3222,7 +3223,7 @@
       <c r="F24" s="7" t="n">
         <v>21.77719264552191</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
         <v/>
       </c>
@@ -3248,7 +3249,7 @@
       <c r="F25" s="7" t="n">
         <v>19.83109343891408</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
         <v/>
       </c>
@@ -3274,7 +3275,7 @@
       <c r="F26" s="7" t="n">
         <v>17.70370701195685</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
         <v/>
       </c>
@@ -3300,7 +3301,7 @@
       <c r="F27" s="7" t="n">
         <v>20.3331339912772</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
         <v/>
       </c>
@@ -3326,7 +3327,7 @@
       <c r="F28" s="7" t="n">
         <v>17.52507215192293</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
         <v/>
       </c>
@@ -3352,7 +3353,7 @@
       <c r="F29" s="7" t="n">
         <v>18.6580060074063</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="16">
         <f>MAX(B29:F29)-MIN(B29:F29)</f>
         <v/>
       </c>
@@ -3378,7 +3379,7 @@
       <c r="F30" s="7" t="n">
         <v>19.20646518163991</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="16">
         <f>MAX(B30:F30)-MIN(B30:F30)</f>
         <v/>
       </c>
@@ -3404,7 +3405,7 @@
       <c r="F31" s="7" t="n">
         <v>24.28194674822564</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="16">
         <f>MAX(B31:F31)-MIN(B31:F31)</f>
         <v/>
       </c>
@@ -3510,35 +3511,35 @@
           <t>Earnings per share (AED)</t>
         </is>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="16">
         <f>'Income Statement'!B19</f>
         <v/>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="16">
         <f>'Income Statement'!C19</f>
         <v/>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="16">
         <f>'Income Statement'!D19</f>
         <v/>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="16">
         <f>'Income Statement'!E19</f>
         <v/>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="16">
         <f>'Income Statement'!F19</f>
         <v/>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="16">
         <f>'Income Statement'!G19</f>
         <v/>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="16">
         <f>'Income Statement'!H19</f>
         <v/>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="16">
         <f>'Income Statement'!I19</f>
         <v/>
       </c>
@@ -3549,35 +3550,35 @@
           <t>Dividend per share (AED)</t>
         </is>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="16">
         <f>'Income Statement'!B20</f>
         <v/>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="16">
         <f>'Income Statement'!C20</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="16">
         <f>'Income Statement'!D20</f>
         <v/>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="16">
         <f>'Income Statement'!E20</f>
         <v/>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="16">
         <f>'Income Statement'!F20</f>
         <v/>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="16">
         <f>'Income Statement'!G20</f>
         <v/>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="16">
         <f>'Income Statement'!H20</f>
         <v/>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="16">
         <f>'Income Statement'!I20</f>
         <v/>
       </c>
@@ -3588,35 +3589,35 @@
           <t>Payout ratio</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <f>'Income Statement'!B20/'Income Statement'!B19</f>
         <v/>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <f>'Income Statement'!C20/'Income Statement'!C19</f>
         <v/>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <f>'Income Statement'!D20/'Income Statement'!D19</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <f>'Income Statement'!E20/'Income Statement'!E19</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <f>'Income Statement'!F20/'Income Statement'!F19</f>
         <v/>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="9">
         <f>'Income Statement'!G20/'Income Statement'!G19</f>
         <v/>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="9">
         <f>'Income Statement'!H20/'Income Statement'!H19</f>
         <v/>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="9">
         <f>'Income Statement'!I20/'Income Statement'!I19</f>
         <v/>
       </c>
@@ -3627,35 +3628,35 @@
           <t>Dividend yield at the anchor spot</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <f>'Income Statement'!B20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>'Income Statement'!C20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <f>'Income Statement'!D20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>'Income Statement'!E20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>'Income Statement'!F20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <f>'Income Statement'!G20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <f>'Income Statement'!H20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <f>'Income Statement'!I20/Assumptions!$C$5</f>
         <v/>
       </c>
@@ -3666,35 +3667,35 @@
           <t>Book value per share (AED)</t>
         </is>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="16">
         <f>'Balance Sheet'!B14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="16">
         <f>'Balance Sheet'!C14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="16">
         <f>'Balance Sheet'!D14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="16">
         <f>'Balance Sheet'!E14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="16">
         <f>'Balance Sheet'!F14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="16">
         <f>'Balance Sheet'!G14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="16">
         <f>'Balance Sheet'!H14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="16">
         <f>'Balance Sheet'!I14/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -3705,38 +3706,38 @@
           <t>Free cash flow to the firm per share (AED)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="16">
         <f>'Summary Financials'!E11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="16">
         <f>'Summary Financials'!F11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="16">
         <f>'Summary Financials'!G11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="16">
         <f>'Summary Financials'!H11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="16">
         <f>'Summary Financials'!I11/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -3747,35 +3748,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <f>'Summary Financials'!B8</f>
         <v/>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <f>'Summary Financials'!C8</f>
         <v/>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <f>'Summary Financials'!D8</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <f>'Summary Financials'!E8</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="9">
         <f>'Summary Financials'!F8</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="9">
         <f>'Summary Financials'!G8</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="9">
         <f>'Summary Financials'!H8</f>
         <v/>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="9">
         <f>'Summary Financials'!I8</f>
         <v/>
       </c>
@@ -3786,35 +3787,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <f>'Income Statement'!B12/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="9">
         <f>'Income Statement'!C12/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="9">
         <f>'Income Statement'!D12/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <f>'Income Statement'!E12/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="9">
         <f>'Income Statement'!F12/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="9">
         <f>'Income Statement'!G12/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="9">
         <f>'Income Statement'!H12/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="9">
         <f>'Income Statement'!I12/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3825,35 +3826,35 @@
           <t>Net margin</t>
         </is>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="9">
         <f>'Income Statement'!B18/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="9">
         <f>'Income Statement'!C18/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="9">
         <f>'Income Statement'!D18/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <f>'Income Statement'!E18/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="9">
         <f>'Income Statement'!F18/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="9">
         <f>'Income Statement'!G18/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="9">
         <f>'Income Statement'!H18/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <f>'Income Statement'!I18/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3864,36 +3865,36 @@
           <t>Return on equity</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="9">
         <f>'Income Statement'!C18/(('Balance Sheet'!B14+'Balance Sheet'!C14)/2)</f>
         <v/>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="9">
         <f>'Income Statement'!D18/(('Balance Sheet'!C14+'Balance Sheet'!D14)/2)</f>
         <v/>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <f>'Income Statement'!E18/(('Balance Sheet'!D14+'Balance Sheet'!E14)/2)</f>
         <v/>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="9">
         <f>'Income Statement'!F18/(('Balance Sheet'!E14+'Balance Sheet'!F14)/2)</f>
         <v/>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="9">
         <f>'Income Statement'!G18/(('Balance Sheet'!F14+'Balance Sheet'!G14)/2)</f>
         <v/>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="9">
         <f>'Income Statement'!H18/(('Balance Sheet'!G14+'Balance Sheet'!H14)/2)</f>
         <v/>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <f>'Income Statement'!I18/(('Balance Sheet'!H14+'Balance Sheet'!I14)/2)</f>
         <v/>
       </c>
@@ -3904,38 +3905,38 @@
           <t>Return on invested capital</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="9">
         <f>'Summary Financials'!E14</f>
         <v/>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="9">
         <f>'Summary Financials'!F14</f>
         <v/>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="9">
         <f>'Summary Financials'!G14</f>
         <v/>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="9">
         <f>'Summary Financials'!H14</f>
         <v/>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="9">
         <f>'Summary Financials'!I14</f>
         <v/>
       </c>
@@ -3946,38 +3947,38 @@
           <t>Capital expenditure / revenue (capital intensity)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <f>-'Cash Flow'!D11/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="9">
         <f>-'Cash Flow'!E11/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="9">
         <f>-'Cash Flow'!F11/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="9">
         <f>-'Cash Flow'!G11/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="9">
         <f>-'Cash Flow'!H11/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3988,35 +3989,35 @@
           <t>Lease liabilities / EBITDA</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="39">
         <f>'Balance Sheet'!B16</f>
         <v/>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="39">
         <f>'Balance Sheet'!C16</f>
         <v/>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="39">
         <f>'Balance Sheet'!D16</f>
         <v/>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="39">
         <f>'Balance Sheet'!E16</f>
         <v/>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="39">
         <f>'Balance Sheet'!F16</f>
         <v/>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="39">
         <f>'Balance Sheet'!G16</f>
         <v/>
       </c>
-      <c r="H17" s="38">
+      <c r="H17" s="39">
         <f>'Balance Sheet'!H16</f>
         <v/>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="39">
         <f>'Balance Sheet'!I16</f>
         <v/>
       </c>
@@ -4027,41 +4028,41 @@
           <t>Working capital / revenue</t>
         </is>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <f>'Balance Sheet'!B11/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="9">
         <f>'Balance Sheet'!C11/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="9">
         <f>'Balance Sheet'!D11/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="9">
         <f>'Balance Sheet'!E11/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="9">
         <f>'Balance Sheet'!F11/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="9">
         <f>'Balance Sheet'!G11/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="9">
         <f>'Balance Sheet'!H11/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="9">
         <f>'Balance Sheet'!I11/'Income Statement'!I5</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Operating KPIs (company-disclosed history, house forecast)</t>
         </is>
@@ -4073,7 +4074,7 @@
           <t>Mobile subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4084,23 +4085,23 @@
       <c r="D21" s="23" t="n">
         <v>9704</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="19">
         <f>Assumptions!$B$23</f>
         <v/>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="19">
         <f>Assumptions!$C$23</f>
         <v/>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="19">
         <f>Assumptions!$D$23</f>
         <v/>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="19">
         <f>Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="19">
         <f>Assumptions!$F$23</f>
         <v/>
       </c>
@@ -4111,7 +4112,7 @@
           <t>Fixed subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4122,23 +4123,23 @@
       <c r="D22" s="23" t="n">
         <v>735</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="19">
         <f>Assumptions!$B$24</f>
         <v/>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="19">
         <f>Assumptions!$C$24</f>
         <v/>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="19">
         <f>Assumptions!$D$24</f>
         <v/>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="19">
         <f>Assumptions!$E$24</f>
         <v/>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="19">
         <f>Assumptions!$F$24</f>
         <v/>
       </c>
@@ -4149,34 +4150,34 @@
           <t>Blended mobile ARPU (AED/month)</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="24" t="n">
+      <c r="C23" s="25" t="n">
         <v>65.8</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="25" t="n">
         <v>63.3</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="46">
         <f>Assumptions!$B$25</f>
         <v/>
       </c>
-      <c r="F23" s="45">
+      <c r="F23" s="46">
         <f>Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="G23" s="45">
+      <c r="G23" s="46">
         <f>Assumptions!$D$25</f>
         <v/>
       </c>
-      <c r="H23" s="45">
+      <c r="H23" s="46">
         <f>Assumptions!$E$25</f>
         <v/>
       </c>
-      <c r="I23" s="45">
+      <c r="I23" s="46">
         <f>Assumptions!$F$25</f>
         <v/>
       </c>
@@ -4268,12 +4269,12 @@
           <t>UAE (ADX)</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="45" t="inlineStr">
         <is>
           <t>~20.7x</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="45" t="inlineStr">
         <is>
           <t>~4.8%</t>
         </is>
@@ -4295,12 +4296,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>~18.9x</t>
         </is>
       </c>
-      <c r="D6" s="44" t="inlineStr">
+      <c r="D6" s="45" t="inlineStr">
         <is>
           <t>~5.2%</t>
         </is>
@@ -4322,12 +4323,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="45" t="inlineStr">
         <is>
           <t>~15.5x</t>
         </is>
       </c>
-      <c r="D7" s="44" t="inlineStr">
+      <c r="D7" s="45" t="inlineStr">
         <is>
           <t>~2.9%</t>
         </is>
@@ -4349,12 +4350,12 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>~12.5x</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>~4.6%</t>
         </is>
@@ -4376,12 +4377,12 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C9" s="45" t="inlineStr">
         <is>
           <t>~9x</t>
         </is>
       </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="D9" s="45" t="inlineStr">
         <is>
           <t>~6-7%</t>
         </is>
@@ -4403,12 +4404,12 @@
           <t>Oman</t>
         </is>
       </c>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>~11.4x</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>~6.7%</t>
         </is>
@@ -4430,12 +4431,12 @@
           <t>Developed markets</t>
         </is>
       </c>
-      <c r="C11" s="44" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
         <is>
           <t>n/m</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D11" s="45" t="inlineStr">
         <is>
           <t>3.4% / n/m</t>
         </is>
@@ -4464,7 +4465,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="37">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -4475,7 +4476,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="37">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -4486,7 +4487,7 @@
           <t>Trailing dividend yield (FY2025 DPS / spot)</t>
         </is>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="17">
         <f>'Income Statement'!D20/Assumptions!$C$5</f>
         <v/>
       </c>
@@ -4497,7 +4498,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B17" s="36">
+      <c r="B17" s="37">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -4521,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4606,15 +4607,13 @@
       <c r="D5" s="7" t="n">
         <v>28.6533036884854</v>
       </c>
-      <c r="E5" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F5" s="10">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>C5/$C$14-1</f>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the class primary</t>
+        </is>
+      </c>
+      <c r="G5" s="9">
+        <f>C5/$C$15-1</f>
         <v/>
       </c>
     </row>
@@ -4636,15 +4635,13 @@
         <f>'Relative &amp; Normalized'!D12</f>
         <v/>
       </c>
-      <c r="E6" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F6" s="10">
-        <f>C6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
-        <f>C6/$C$14-1</f>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="G6" s="9">
+        <f>C6/$C$15-1</f>
         <v/>
       </c>
     </row>
@@ -4666,15 +4663,13 @@
         <f>'Relative &amp; Normalized'!F27</f>
         <v/>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F7" s="10">
-        <f>C7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
-        <f>C7/$C$14-1</f>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED — not a lens this class publishes</t>
+        </is>
+      </c>
+      <c r="G7" s="9">
+        <f>C7/$C$15-1</f>
         <v/>
       </c>
     </row>
@@ -4696,235 +4691,254 @@
         <f>'Relative &amp; Normalized'!F35</f>
         <v/>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F8" s="10">
-        <f>C8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
-        <f>C8/$C$14-1</f>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>a disclosed floor, never weighted</t>
+        </is>
+      </c>
+      <c r="G8" s="9">
+        <f>C8/$C$15-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B9" s="13">
-        <f>B5*E5+B6*E6+B7*E7+B8*E8</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>SUM(F5:F8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>D5*E5+D6*E6+D7*E7+D8*E8</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>SUM(E5:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="15" t="n"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the cash-flow lens, not an average</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>the class primary</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n"/>
       <c r="G9" s="14">
-        <f>C9/$C$14-1</f>
+        <f>C9/$C$15-1</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Span across lenses (min/max — NOT weighted)</t>
-        </is>
-      </c>
-      <c r="B10" s="10">
-        <f>MIN(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="D10" s="10">
-        <f>MAX(D5:D8)</f>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>NOT AVERAGED — the retired blend, published unused</t>
+        </is>
+      </c>
+      <c r="C10" s="16">
+        <f>C5*0.45+C6*0.25+C7*0.2+C8*0.1</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>retired 02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="G10" s="9">
+        <f>C10/$C$15-1</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Contested judgement, other way — no terminal re-rating (Framing 2)</t>
-        </is>
-      </c>
-      <c r="C11" s="8">
-        <f>'Fundamental Valuation'!C18</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>C11/$C$14-1</f>
+          <t>Span across the lenses (min/max) — a spread between METHODS, not a range around the answer</t>
+        </is>
+      </c>
+      <c r="B11" s="16">
+        <f>MIN(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f>MAX(D5:D8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Terminal value share of DCF enterprise value</t>
-        </is>
-      </c>
-      <c r="C12" s="16">
-        <f>DCF!C29</f>
+          <t>Contested judgement, other way — no terminal re-rating (Framing 2)</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
+        <f>'Fundamental Valuation'!C18</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>C12/$C$15-1</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>Terminal value share of DCF enterprise value</t>
+        </is>
+      </c>
+      <c r="C13" s="17">
+        <f>DCF!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>Expert panel median</t>
         </is>
       </c>
-      <c r="C13" s="8">
+      <c r="C14" s="8">
         <f>'Fundamental Valuation'!C27</f>
         <v/>
       </c>
-      <c r="G13" s="11">
-        <f>C13/$C$14-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="G14" s="9">
+        <f>C14/$C$15-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Market price (anchor)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="17" t="n">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="18" t="n">
         <v>12.3</v>
       </c>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Key figure</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="C17" s="18">
-        <f>Assumptions!$C$6</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Market capitalisation (AED mn)</t>
-        </is>
-      </c>
-      <c r="C18" s="18">
-        <f>$C$14*C17</f>
+          <t>Shares outstanding (mn)</t>
+        </is>
+      </c>
+      <c r="C18" s="19">
+        <f>Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities, FY2025 (AED mn) — the only debt-like item</t>
-        </is>
-      </c>
-      <c r="C19" s="18">
-        <f>Assumptions!$C$83</f>
+          <t>Market capitalisation (AED mn)</t>
+        </is>
+      </c>
+      <c r="C19" s="19">
+        <f>$C$15*C18</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Cash and term deposits, FY2025 (AED mn)</t>
-        </is>
-      </c>
-      <c r="C20" s="18">
-        <f>Assumptions!$C$84</f>
+          <t>Lease liabilities, FY2025 (AED mn) — the only debt-like item</t>
+        </is>
+      </c>
+      <c r="C20" s="19">
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>FY2025 revenue (AED mn)</t>
-        </is>
-      </c>
-      <c r="C21" s="18">
-        <f>'Income Statement'!D5</f>
+          <t>Cash and term deposits, FY2025 (AED mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="19">
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>FY2025 EBITDA (AED mn)</t>
-        </is>
-      </c>
-      <c r="C22" s="18">
-        <f>'Income Statement'!D9</f>
+          <t>FY2025 revenue (AED mn)</t>
+        </is>
+      </c>
+      <c r="C22" s="19">
+        <f>'Income Statement'!D5</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net profit (AED mn)</t>
-        </is>
-      </c>
-      <c r="C23" s="18">
-        <f>'Income Statement'!D18</f>
+          <t>FY2025 EBITDA (AED mn)</t>
+        </is>
+      </c>
+      <c r="C23" s="19">
+        <f>'Income Statement'!D9</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — explicit window</t>
-        </is>
-      </c>
-      <c r="C24" s="16">
-        <f>DCF!C47</f>
+          <t>FY2025 net profit (AED mn)</t>
+        </is>
+      </c>
+      <c r="C24" s="19">
+        <f>'Income Statement'!D18</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — terminal</t>
-        </is>
-      </c>
-      <c r="C25" s="16">
-        <f>DCF!C54</f>
+          <t>Cost of capital — explicit window</t>
+        </is>
+      </c>
+      <c r="C25" s="17">
+        <f>DCF!C47</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t>Cost of capital — terminal</t>
+        </is>
+      </c>
+      <c r="C26" s="17">
+        <f>DCF!C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C26" s="16">
+      <c r="C27" s="17">
         <f>DCF!C24</f>
         <v/>
       </c>
@@ -5076,19 +5090,19 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Weighted central</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="19">
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="20">
         <f>Summary!C9</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>THE CONTESTED JUDGEMENT — THE REQUIRED RETURN, BOTH WAYS</t>
         </is>
@@ -5141,7 +5155,7 @@
           <t>The judgement is worth (Framing 1 less Framing 2, per share)</t>
         </is>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="16">
         <f>C15-C18</f>
         <v/>
       </c>
@@ -5157,7 +5171,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>EXPERT PANEL</t>
         </is>
@@ -5254,18 +5268,18 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Panel median</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="13">
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="11">
         <f>MEDIAN(C24:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5296,7 +5310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5363,18 +5377,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Anchors</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5402,7 +5416,7 @@
           <t>Combined federal royalty + income tax rate (Framing A, audited FY2025)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="24" t="n">
         <v>0.4357</v>
       </c>
     </row>
@@ -5412,7 +5426,7 @@
           <t>Regulated revenue share (Framing B base, audited FY2023)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="24" t="n">
         <v>0.6899999999999999</v>
       </c>
     </row>
@@ -5422,7 +5436,7 @@
           <t>Framing B — royalty rate on regulated revenue</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="24" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5432,23 +5446,23 @@
           <t>Framing B — royalty rate on regulated profit</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="24" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>H1-2026 reviewed segment actuals — the base the FY2026 build chains off</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5531,18 +5545,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Unit build — mobile and fixed (subscribers x ARPU)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5594,19 +5608,19 @@
           <t>Blended mobile ARPU (AED/month)</t>
         </is>
       </c>
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="25" t="n">
         <v>63.4</v>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="25" t="n">
         <v>63.6</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="25" t="n">
         <v>63.8</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="25" t="n">
         <v>64</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="25" t="n">
         <v>64.2</v>
       </c>
     </row>
@@ -5638,19 +5652,19 @@
           <t>Wholesale revenue growth</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="24" t="n">
         <v>-0.008</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="24" t="n">
         <v>0.015</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="24" t="n">
         <v>0.02</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="24" t="n">
         <v>0.02</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="24" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -5660,35 +5674,35 @@
           <t>ICT and associated telecom revenue growth</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="24" t="n">
         <v>0.079</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="24" t="n">
         <v>0.11</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="24" t="n">
         <v>0.09</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="24" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Direct-cost stack — cost per unit, one escalator per driver class. CONTRIBUTION MARGIN IS NOT AN INPUT HERE: it is computed on the Segments sheet as what is left after each cost line is grown on its own physical driver.</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5696,7 +5710,7 @@
           <t>Mobile interconnect cost, H1-2026 actual (AED/subscriber/month)</t>
         </is>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="26" t="n">
         <v>16.81380811911785</v>
       </c>
     </row>
@@ -5706,7 +5720,7 @@
           <t>Mobile interconnect escalator (termination rates, OTT substitution)</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="24" t="n">
         <v>-0.015</v>
       </c>
     </row>
@@ -5716,7 +5730,7 @@
           <t>Mobile commission cost, H1-2026 actual (AED/subscriber/month)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="n">
+      <c r="C33" s="26" t="n">
         <v>6.306854895350471</v>
       </c>
     </row>
@@ -5726,7 +5740,7 @@
           <t>Mobile commission escalator (acquisition/retention cost)</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="24" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -5736,7 +5750,7 @@
           <t>Mobile devices and direct services, H1-2026 actual (AED/subscriber/month)</t>
         </is>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C35" s="26" t="n">
         <v>0.9565423514538555</v>
       </c>
     </row>
@@ -5746,7 +5760,7 @@
           <t>Mobile devices escalator (held flat — lumpy, no trend read into it)</t>
         </is>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5756,7 +5770,7 @@
           <t>Fixed capacity and direct cost, H1-2026 actual (AED/subscriber/month)</t>
         </is>
       </c>
-      <c r="C37" s="25" t="n">
+      <c r="C37" s="26" t="n">
         <v>68.35316655397791</v>
       </c>
     </row>
@@ -5766,7 +5780,7 @@
           <t>Fixed capacity escalator (held flat against an observed decline)</t>
         </is>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5776,7 +5790,7 @@
           <t>Wholesale direct cost / wholesale revenue (H1-2026 rate, held flat)</t>
         </is>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="24" t="n">
         <v>0.1558</v>
       </c>
     </row>
@@ -5786,7 +5800,7 @@
           <t>ICT direct cost / ICT revenue (H1-2026 rate, held flat)</t>
         </is>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="24" t="n">
         <v>0.7848000000000001</v>
       </c>
     </row>
@@ -5836,23 +5850,23 @@
           <t>Blended ARPU drift (mix-exhaustion sensitivity; zero in the base case)</t>
         </is>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Operating expense stack — one escalator per cost class</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="15" t="n"/>
-      <c r="D47" s="15" t="n"/>
-      <c r="E47" s="15" t="n"/>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
-      <c r="H47" s="15" t="n"/>
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="13" t="n"/>
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -5870,7 +5884,7 @@
           <t>Staff escalator (UAE wage inflation)</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" s="24" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -5890,7 +5904,7 @@
           <t>Network escalator (network scale)</t>
         </is>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="24" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -5910,7 +5924,7 @@
           <t>Administrative escalator (CPI)</t>
         </is>
       </c>
-      <c r="C53" s="9" t="n">
+      <c r="C53" s="24" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -5930,7 +5944,7 @@
           <t>Other-expense escalator (CPI)</t>
         </is>
       </c>
-      <c r="C55" s="9" t="n">
+      <c r="C55" s="24" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -5940,7 +5954,7 @@
           <t>Marketing / revenue</t>
         </is>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="C56" s="24" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -5950,7 +5964,7 @@
           <t>Telecom licence and related fees / revenue (regulatory revenue share)</t>
         </is>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C57" s="24" t="n">
         <v>0.027</v>
       </c>
     </row>
@@ -5960,7 +5974,7 @@
           <t>Expected credit losses / revenue</t>
         </is>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C58" s="24" t="n">
         <v>0.0145</v>
       </c>
     </row>
@@ -5975,18 +5989,18 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>Capital intensity and working capital</t>
         </is>
       </c>
-      <c r="B61" s="15" t="n"/>
-      <c r="C61" s="15" t="n"/>
-      <c r="D61" s="15" t="n"/>
-      <c r="E61" s="15" t="n"/>
-      <c r="F61" s="15" t="n"/>
-      <c r="G61" s="15" t="n"/>
-      <c r="H61" s="15" t="n"/>
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="13" t="n"/>
+      <c r="E61" s="13" t="n"/>
+      <c r="F61" s="13" t="n"/>
+      <c r="G61" s="13" t="n"/>
+      <c r="H61" s="13" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -5994,19 +6008,19 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="B62" s="9" t="n">
+      <c r="B62" s="24" t="n">
         <v>0.155</v>
       </c>
-      <c r="C62" s="9" t="n">
+      <c r="C62" s="24" t="n">
         <v>0.15</v>
       </c>
-      <c r="D62" s="9" t="n">
+      <c r="D62" s="24" t="n">
         <v>0.145</v>
       </c>
-      <c r="E62" s="9" t="n">
+      <c r="E62" s="24" t="n">
         <v>0.135</v>
       </c>
-      <c r="F62" s="9" t="n">
+      <c r="F62" s="24" t="n">
         <v>0.13</v>
       </c>
     </row>
@@ -6016,7 +6030,7 @@
           <t>Tangible share of capex (audited FY2025)</t>
         </is>
       </c>
-      <c r="C63" s="9" t="n">
+      <c r="C63" s="24" t="n">
         <v>0.866</v>
       </c>
     </row>
@@ -6026,7 +6040,7 @@
           <t>PP&amp;E depreciation rate on opening balance (audited FY2025)</t>
         </is>
       </c>
-      <c r="C64" s="9" t="n">
+      <c r="C64" s="24" t="n">
         <v>0.1583</v>
       </c>
     </row>
@@ -6036,7 +6050,7 @@
           <t>Intangibles amortisation rate on opening balance (audited FY2025)</t>
         </is>
       </c>
-      <c r="C65" s="9" t="n">
+      <c r="C65" s="24" t="n">
         <v>0.289</v>
       </c>
     </row>
@@ -6068,23 +6082,23 @@
           <t>Net working capital / revenue (audited FY2025 component days)</t>
         </is>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="C67" s="24" t="n">
         <v>-0.0667974774135183</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>Cost of capital</t>
         </is>
       </c>
-      <c r="B69" s="15" t="n"/>
-      <c r="C69" s="15" t="n"/>
-      <c r="D69" s="15" t="n"/>
-      <c r="E69" s="15" t="n"/>
-      <c r="F69" s="15" t="n"/>
-      <c r="G69" s="15" t="n"/>
-      <c r="H69" s="15" t="n"/>
+      <c r="B69" s="13" t="n"/>
+      <c r="C69" s="13" t="n"/>
+      <c r="D69" s="13" t="n"/>
+      <c r="E69" s="13" t="n"/>
+      <c r="F69" s="13" t="n"/>
+      <c r="G69" s="13" t="n"/>
+      <c r="H69" s="13" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -6092,7 +6106,7 @@
           <t>Risk-free rate — Jan-2031 AED T-bond (longest liquid AED tenor)</t>
         </is>
       </c>
-      <c r="C70" s="9" t="n">
+      <c r="C70" s="24" t="n">
         <v>0.0448</v>
       </c>
     </row>
@@ -6102,7 +6116,7 @@
           <t>UAE sovereign default spread (netted out; Aa2 rating basis)</t>
         </is>
       </c>
-      <c r="C71" s="9" t="n">
+      <c r="C71" s="24" t="n">
         <v>0.0004</v>
       </c>
     </row>
@@ -6112,7 +6126,7 @@
           <t>Equity risk premium (UAE total, rating basis)</t>
         </is>
       </c>
-      <c r="C72" s="9" t="n">
+      <c r="C72" s="24" t="n">
         <v>0.0429</v>
       </c>
     </row>
@@ -6122,7 +6136,7 @@
           <t>Beta (DU weekly vs FTSE ADX General, 5y)</t>
         </is>
       </c>
-      <c r="C73" s="26" t="n">
+      <c r="C73" s="27" t="n">
         <v>0.488</v>
       </c>
     </row>
@@ -6132,7 +6146,7 @@
           <t>Marginal cost of debt (AED sovereign + GCC telecom spread)</t>
         </is>
       </c>
-      <c r="C74" s="9" t="n">
+      <c r="C74" s="24" t="n">
         <v>0.051</v>
       </c>
     </row>
@@ -6142,19 +6156,19 @@
           <t>AED risk-free path (defines the glide)</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n">
+      <c r="B75" s="24" t="n">
         <v>0.0448</v>
       </c>
-      <c r="C75" s="9" t="n">
+      <c r="C75" s="24" t="n">
         <v>0.0444</v>
       </c>
-      <c r="D75" s="9" t="n">
+      <c r="D75" s="24" t="n">
         <v>0.0439</v>
       </c>
-      <c r="E75" s="9" t="n">
+      <c r="E75" s="24" t="n">
         <v>0.0435</v>
       </c>
-      <c r="F75" s="9" t="n">
+      <c r="F75" s="24" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -6164,7 +6178,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C76" s="9" t="n">
+      <c r="C76" s="24" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -6174,7 +6188,7 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C77" s="9" t="n">
+      <c r="C77" s="24" t="n">
         <v>0.0429</v>
       </c>
     </row>
@@ -6184,7 +6198,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C78" s="9" t="n">
+      <c r="C78" s="24" t="n">
         <v>0.049</v>
       </c>
     </row>
@@ -6194,7 +6208,7 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C79" s="9" t="n">
+      <c r="C79" s="24" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -6204,23 +6218,23 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C80" s="9" t="n">
+      <c r="C80" s="24" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>Balance-sheet and bridge anchors</t>
         </is>
       </c>
-      <c r="B82" s="15" t="n"/>
-      <c r="C82" s="15" t="n"/>
-      <c r="D82" s="15" t="n"/>
-      <c r="E82" s="15" t="n"/>
-      <c r="F82" s="15" t="n"/>
-      <c r="G82" s="15" t="n"/>
-      <c r="H82" s="15" t="n"/>
+      <c r="B82" s="13" t="n"/>
+      <c r="C82" s="13" t="n"/>
+      <c r="D82" s="13" t="n"/>
+      <c r="E82" s="13" t="n"/>
+      <c r="F82" s="13" t="n"/>
+      <c r="G82" s="13" t="n"/>
+      <c r="H82" s="13" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -6248,7 +6262,7 @@
           <t>Equity-accounted investees at carrying value (AED mn)</t>
         </is>
       </c>
-      <c r="C85" s="24" t="n">
+      <c r="C85" s="25" t="n">
         <v>0.511</v>
       </c>
     </row>
@@ -6258,7 +6272,7 @@
           <t>Forecast dividend payout ratio (FY2024 actual 98%, FY2025 ~100%)</t>
         </is>
       </c>
-      <c r="C86" s="9" t="n">
+      <c r="C86" s="24" t="n">
         <v>0.98</v>
       </c>
     </row>
@@ -6268,7 +6282,7 @@
           <t>Yield on cash and term deposits (audited FY2025 effective)</t>
         </is>
       </c>
-      <c r="C87" s="9" t="n">
+      <c r="C87" s="24" t="n">
         <v>0.033</v>
       </c>
     </row>
@@ -6278,7 +6292,7 @@
           <t>Lease interest rate (audited FY2025 effective)</t>
         </is>
       </c>
-      <c r="C88" s="9" t="n">
+      <c r="C88" s="24" t="n">
         <v>0.036</v>
       </c>
     </row>
@@ -6303,18 +6317,18 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>Lens inputs</t>
         </is>
       </c>
-      <c r="B92" s="15" t="n"/>
-      <c r="C92" s="15" t="n"/>
-      <c r="D92" s="15" t="n"/>
-      <c r="E92" s="15" t="n"/>
-      <c r="F92" s="15" t="n"/>
-      <c r="G92" s="15" t="n"/>
-      <c r="H92" s="15" t="n"/>
+      <c r="B92" s="13" t="n"/>
+      <c r="C92" s="13" t="n"/>
+      <c r="D92" s="13" t="n"/>
+      <c r="E92" s="13" t="n"/>
+      <c r="F92" s="13" t="n"/>
+      <c r="G92" s="13" t="n"/>
+      <c r="H92" s="13" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -6332,7 +6346,7 @@
           <t>Peer benchmark dividend yield</t>
         </is>
       </c>
-      <c r="C94" s="9" t="n">
+      <c r="C94" s="24" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -6342,48 +6356,8 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C95" s="9" t="n">
+      <c r="C95" s="24" t="n">
         <v>0.27</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="n">
-        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -6449,11 +6423,11 @@
           <t>Present value of the five forecast years</t>
         </is>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>DCF!C27</f>
         <v/>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="16">
         <f>C5/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6464,11 +6438,11 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>DCF!C28</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="16">
         <f>C6/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6479,11 +6453,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6494,11 +6468,11 @@
           <t>Less lease liabilities (the only debt-like item)</t>
         </is>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>-Assumptions!$C$83</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="16">
         <f>C8/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6509,11 +6483,11 @@
           <t>Plus cash and term deposits</t>
         </is>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>Assumptions!$C$84</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="16">
         <f>C9/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6524,27 +6498,27 @@
           <t>Plus equity-accounted investees at carrying value</t>
         </is>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>Assumptions!$C$85</f>
         <v/>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="16">
         <f>C10/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="29">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="30">
         <f>C7+C8+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>C11/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6555,7 +6529,7 @@
           <t>Terminal value as a share of enterprise value</t>
         </is>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <f>DCF!C29</f>
         <v/>
       </c>
@@ -6671,30 +6645,30 @@
       <c r="B5" s="23" t="n">
         <v>7074.936</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <f>B5/$B$9</f>
         <v/>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="24" t="n">
         <v>0.6082941244980873</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>Assumptions!$C$13+(Assumptions!$C$15+Assumptions!$B$23)/2*Assumptions!$B$25*6/1000</f>
         <v/>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <f>(Assumptions!$B$23+Assumptions!$C$23)/2*Assumptions!$C$25*(1+Assumptions!$C$45)^1*12/1000</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="32">
         <f>(Assumptions!$C$23+Assumptions!$D$23)/2*Assumptions!$D$25*(1+Assumptions!$C$45)^2*12/1000</f>
         <v/>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <f>(Assumptions!$D$23+Assumptions!$E$23)/2*Assumptions!$E$25*(1+Assumptions!$C$45)^3*12/1000</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="32">
         <f>(Assumptions!$E$23+Assumptions!$F$23)/2*Assumptions!$F$25*(1+Assumptions!$C$45)^4*12/1000</f>
         <v/>
       </c>
@@ -6708,30 +6682,30 @@
       <c r="B6" s="23" t="n">
         <v>4379.705</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <f>B6/$B$9</f>
         <v/>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="24" t="n">
         <v>0.858015094623953</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>Assumptions!$C$14+(Assumptions!$C$16+Assumptions!$B$24)/2*Assumptions!$B$26*6/1000</f>
         <v/>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>(Assumptions!$B$24+Assumptions!$C$24)/2*Assumptions!$C$26*(1+Assumptions!$C$45)^1*12/1000</f>
         <v/>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="32">
         <f>(Assumptions!$C$24+Assumptions!$D$24)/2*Assumptions!$D$26*(1+Assumptions!$C$45)^2*12/1000</f>
         <v/>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <f>(Assumptions!$D$24+Assumptions!$E$24)/2*Assumptions!$E$26*(1+Assumptions!$C$45)^3*12/1000</f>
         <v/>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="32">
         <f>(Assumptions!$E$24+Assumptions!$F$24)/2*Assumptions!$F$26*(1+Assumptions!$C$45)^4*12/1000</f>
         <v/>
       </c>
@@ -6745,30 +6719,30 @@
       <c r="B7" s="23" t="n">
         <v>2568.222</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <f>B7/$B$9</f>
         <v/>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="24" t="n">
         <v>0.8642060538380248</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>Assumptions!$C$17*(1+Assumptions!$B$27)</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>E7*(1+Assumptions!$C$27)</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>F7*(1+Assumptions!$D$27)</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>G7*(1+Assumptions!$E$27)</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="32">
         <f>H7*(1+Assumptions!$F$27)</f>
         <v/>
       </c>
@@ -6782,41 +6756,41 @@
       <c r="B8" s="23" t="n">
         <v>1882.558</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>B8/$B$9</f>
         <v/>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="24" t="n">
         <v>0.1939000020185301</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>Assumptions!$C$18*(1+Assumptions!$B$28)</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>E8*(1+Assumptions!$C$28)</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>F8*(1+Assumptions!$D$28)</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>G8*(1+Assumptions!$E$28)</f>
         <v/>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="32">
         <f>H8*(1+Assumptions!$F$28)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
@@ -6824,24 +6798,24 @@
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="32">
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="33">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="33">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="33">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="33">
         <f>SUM(I5:I8)</f>
         <v/>
       </c>
@@ -6884,23 +6858,23 @@
           <t>Mobile interconnect (AED per subscriber per month)</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^0</f>
         <v/>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^1</f>
         <v/>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^2</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^3</f>
         <v/>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^4</f>
         <v/>
       </c>
@@ -6911,23 +6885,23 @@
           <t>Mobile commission (AED per subscriber per month)</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^0</f>
         <v/>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^1</f>
         <v/>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^2</f>
         <v/>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^3</f>
         <v/>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^4</f>
         <v/>
       </c>
@@ -6938,50 +6912,50 @@
           <t>Mobile devices and direct services (AED per subscriber per month)</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^0</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^1</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^2</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^3</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^4</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Mobile — total direct cost per subscriber per month</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>B12+B13+B14</f>
         <v/>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>C12+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>D12+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>F12+F13+F14</f>
         <v/>
       </c>
@@ -6992,23 +6966,23 @@
           <t>Fixed capacity and direct cost (AED per subscriber per month)</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^0</f>
         <v/>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^1</f>
         <v/>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^2</f>
         <v/>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^3</f>
         <v/>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^4</f>
         <v/>
       </c>
@@ -7019,23 +6993,23 @@
           <t>Wholesale direct cost / wholesale revenue (no disclosed unit — flagged)</t>
         </is>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
@@ -7046,23 +7020,23 @@
           <t>ICT direct cost / ICT revenue (no disclosed unit — flagged)</t>
         </is>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
@@ -7105,23 +7079,23 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="32">
         <f>Assumptions!$C$41+(Assumptions!$C$15+Assumptions!$B$23)/2*B15*6/1000</f>
         <v/>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>(Assumptions!$B$23+Assumptions!$C$23)/2*C15*12/1000</f>
         <v/>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <f>(Assumptions!$C$23+Assumptions!$D$23)/2*D15*12/1000</f>
         <v/>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <f>(Assumptions!$D$23+Assumptions!$E$23)/2*E15*12/1000</f>
         <v/>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <f>(Assumptions!$E$23+Assumptions!$F$23)/2*F15*12/1000</f>
         <v/>
       </c>
@@ -7132,23 +7106,23 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <f>Assumptions!$C$42+(Assumptions!$C$16+Assumptions!$B$24)/2*B16*6/1000</f>
         <v/>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>(Assumptions!$B$24+Assumptions!$C$24)/2*C16*12/1000</f>
         <v/>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <f>(Assumptions!$C$24+Assumptions!$D$24)/2*D16*12/1000</f>
         <v/>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <f>(Assumptions!$D$24+Assumptions!$E$24)/2*E16*12/1000</f>
         <v/>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <f>(Assumptions!$E$24+Assumptions!$F$24)/2*F16*12/1000</f>
         <v/>
       </c>
@@ -7159,23 +7133,23 @@
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="32">
         <f>Assumptions!$C$43+(E7-Assumptions!$C$19)*B17</f>
         <v/>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="32">
         <f>F7*C17</f>
         <v/>
       </c>
-      <c r="D23" s="31">
+      <c r="D23" s="32">
         <f>G7*D17</f>
         <v/>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="32">
         <f>H7*E17</f>
         <v/>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="32">
         <f>I7*F17</f>
         <v/>
       </c>
@@ -7186,50 +7160,50 @@
           <t>ICT and associated telecom services</t>
         </is>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <f>Assumptions!$C$44+(E8-Assumptions!$C$20)*B18</f>
         <v/>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <f>F8*C18</f>
         <v/>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <f>G8*D18</f>
         <v/>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <f>H8*E18</f>
         <v/>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <f>I8*F18</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Total direct cost</t>
         </is>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="33">
         <f>SUM(B21:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <f>SUM(C21:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <f>SUM(D21:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <f>SUM(E21:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <f>SUM(F21:F24)</f>
         <v/>
       </c>
@@ -7272,23 +7246,23 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <f>E5-B21</f>
         <v/>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <f>F5-C21</f>
         <v/>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <f>G5-D21</f>
         <v/>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <f>H5-E21</f>
         <v/>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <f>I5-F21</f>
         <v/>
       </c>
@@ -7299,23 +7273,23 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <f>E6-B22</f>
         <v/>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="32">
         <f>F6-C22</f>
         <v/>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="32">
         <f>G6-D22</f>
         <v/>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="32">
         <f>H6-E22</f>
         <v/>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="32">
         <f>I6-F22</f>
         <v/>
       </c>
@@ -7326,23 +7300,23 @@
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="32">
         <f>E7-B23</f>
         <v/>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="32">
         <f>F7-C23</f>
         <v/>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="32">
         <f>G7-D23</f>
         <v/>
       </c>
-      <c r="E30" s="31">
+      <c r="E30" s="32">
         <f>H7-E23</f>
         <v/>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="32">
         <f>I7-F23</f>
         <v/>
       </c>
@@ -7353,50 +7327,50 @@
           <t>ICT and associated telecom services</t>
         </is>
       </c>
-      <c r="B31" s="31">
+      <c r="B31" s="32">
         <f>E8-B24</f>
         <v/>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="32">
         <f>F8-C24</f>
         <v/>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="32">
         <f>G8-D24</f>
         <v/>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="32">
         <f>H8-E24</f>
         <v/>
       </c>
-      <c r="F31" s="31">
+      <c r="F31" s="32">
         <f>I8-F24</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Total contribution</t>
         </is>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="33">
         <f>SUM(B28:B31)</f>
         <v/>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="33">
         <f>SUM(C28:C31)</f>
         <v/>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="33">
         <f>SUM(D28:D31)</f>
         <v/>
       </c>
-      <c r="E32" s="32">
+      <c r="E32" s="33">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="32">
+      <c r="F32" s="33">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
@@ -7439,23 +7413,23 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="9">
         <f>B28/E5</f>
         <v/>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="9">
         <f>C28/F5</f>
         <v/>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="9">
         <f>D28/G5</f>
         <v/>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="9">
         <f>E28/H5</f>
         <v/>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="9">
         <f>F28/I5</f>
         <v/>
       </c>
@@ -7466,23 +7440,23 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="9">
         <f>B29/E6</f>
         <v/>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="9">
         <f>C29/F6</f>
         <v/>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="9">
         <f>D29/G6</f>
         <v/>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="9">
         <f>E29/H6</f>
         <v/>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="9">
         <f>F29/I6</f>
         <v/>
       </c>
@@ -7493,23 +7467,23 @@
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="9">
         <f>B30/E7</f>
         <v/>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="9">
         <f>C30/F7</f>
         <v/>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="9">
         <f>D30/G7</f>
         <v/>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="9">
         <f>E30/H7</f>
         <v/>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="9">
         <f>F30/I7</f>
         <v/>
       </c>
@@ -7520,29 +7494,29 @@
           <t>ICT and associated telecom services</t>
         </is>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="9">
         <f>B31/E8</f>
         <v/>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="9">
         <f>C31/F8</f>
         <v/>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="9">
         <f>D31/G8</f>
         <v/>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="9">
         <f>E31/H8</f>
         <v/>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="9">
         <f>F31/I8</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Group gross margin</t>
         </is>
@@ -7606,23 +7580,23 @@
           <t>Staff (wage escalator)</t>
         </is>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^0</f>
         <v/>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^1</f>
         <v/>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^2</f>
         <v/>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^3</f>
         <v/>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^4</f>
         <v/>
       </c>
@@ -7633,23 +7607,23 @@
           <t>Network &amp; maintenance (network-scale escalator)</t>
         </is>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^1</f>
         <v/>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^2</f>
         <v/>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^3</f>
         <v/>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^4</f>
         <v/>
       </c>
-      <c r="F43" s="31">
+      <c r="F43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^5</f>
         <v/>
       </c>
@@ -7660,23 +7634,23 @@
           <t>Marketing (% of revenue)</t>
         </is>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="32">
         <f>E9*Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <f>F9*Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <f>G9*Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <f>H9*Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <f>I9*Assumptions!$C$56</f>
         <v/>
       </c>
@@ -7687,23 +7661,23 @@
           <t>Telecom licence and related fees (% of revenue)</t>
         </is>
       </c>
-      <c r="B45" s="31">
+      <c r="B45" s="32">
         <f>E9*Assumptions!$C$57</f>
         <v/>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <f>F9*Assumptions!$C$57</f>
         <v/>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <f>G9*Assumptions!$C$57</f>
         <v/>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <f>H9*Assumptions!$C$57</f>
         <v/>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <f>I9*Assumptions!$C$57</f>
         <v/>
       </c>
@@ -7714,23 +7688,23 @@
           <t>Administrative (CPI escalator)</t>
         </is>
       </c>
-      <c r="B46" s="31">
+      <c r="B46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^1</f>
         <v/>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^2</f>
         <v/>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^3</f>
         <v/>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^4</f>
         <v/>
       </c>
-      <c r="F46" s="31">
+      <c r="F46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^5</f>
         <v/>
       </c>
@@ -7741,23 +7715,23 @@
           <t>Other operating expense (CPI escalator)</t>
         </is>
       </c>
-      <c r="B47" s="31">
+      <c r="B47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^1</f>
         <v/>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^2</f>
         <v/>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^3</f>
         <v/>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^4</f>
         <v/>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^5</f>
         <v/>
       </c>
@@ -7768,23 +7742,23 @@
           <t>Expected credit losses (% of revenue)</t>
         </is>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="32">
         <f>E9*Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <f>F9*Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="32">
         <f>G9*Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="32">
         <f>H9*Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="32">
         <f>I9*Assumptions!$C$58</f>
         <v/>
       </c>
@@ -7795,77 +7769,77 @@
           <t>Less other operating income</t>
         </is>
       </c>
-      <c r="B49" s="31">
+      <c r="B49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="D49" s="31">
+      <c r="D49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="F49" s="31">
+      <c r="F49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Total operating expenses before D&amp;A</t>
         </is>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="33">
         <f>SUM(B42:B49)</f>
         <v/>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <f>SUM(C42:C49)</f>
         <v/>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <f>SUM(D42:D49)</f>
         <v/>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <f>SUM(E42:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="33">
         <f>SUM(F42:F49)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Group EBITDA (contribution less the opex stack)</t>
         </is>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="33">
         <f>B32-B50</f>
         <v/>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="33">
         <f>C32-C50</f>
         <v/>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="33">
         <f>D32-D50</f>
         <v/>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="33">
         <f>E32-E50</f>
         <v/>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="33">
         <f>F32-F50</f>
         <v/>
       </c>
@@ -7876,23 +7850,23 @@
           <t>Group EBITDA margin</t>
         </is>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="9">
         <f>B51/E$9</f>
         <v/>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="9">
         <f>C51/F$9</f>
         <v/>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="9">
         <f>D51/G$9</f>
         <v/>
       </c>
-      <c r="E52" s="11">
+      <c r="E52" s="9">
         <f>E51/H$9</f>
         <v/>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="9">
         <f>F51/I$9</f>
         <v/>
       </c>
@@ -7935,23 +7909,23 @@
           <t>Mobile subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B55" s="31">
+      <c r="B55" s="32">
         <f>Assumptions!$B$23</f>
         <v/>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="32">
         <f>Assumptions!$C$23</f>
         <v/>
       </c>
-      <c r="D55" s="31">
+      <c r="D55" s="32">
         <f>Assumptions!$D$23</f>
         <v/>
       </c>
-      <c r="E55" s="31">
+      <c r="E55" s="32">
         <f>Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="F55" s="31">
+      <c r="F55" s="32">
         <f>Assumptions!$F$23</f>
         <v/>
       </c>
@@ -7962,23 +7936,23 @@
           <t>Average mobile base ('000) — (prior end + end)/2</t>
         </is>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="32">
         <f>(9280+Assumptions!$B$23)/2</f>
         <v/>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <f>(Assumptions!$B$23+Assumptions!$C$23)/2</f>
         <v/>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <f>(Assumptions!$C$23+Assumptions!$D$23)/2</f>
         <v/>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <f>(Assumptions!$D$23+Assumptions!$E$23)/2</f>
         <v/>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <f>(Assumptions!$E$23+Assumptions!$F$23)/2</f>
         <v/>
       </c>
@@ -7989,23 +7963,23 @@
           <t>Blended mobile ARPU (AED/month)</t>
         </is>
       </c>
-      <c r="B57" s="35">
+      <c r="B57" s="36">
         <f>Assumptions!$B$25</f>
         <v/>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="36">
         <f>Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="D57" s="35">
+      <c r="D57" s="36">
         <f>Assumptions!$D$25</f>
         <v/>
       </c>
-      <c r="E57" s="35">
+      <c r="E57" s="36">
         <f>Assumptions!$E$25</f>
         <v/>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="36">
         <f>Assumptions!$F$25</f>
         <v/>
       </c>
@@ -8016,24 +7990,24 @@
           <t>Unit-implied mobile revenue — average base x ARPU x 12 (FY2026 is H1 actual + unit-built H2, so the check applies from FY2027)</t>
         </is>
       </c>
-      <c r="B58" s="31" t="inlineStr">
+      <c r="B58" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="32">
         <f>C56*C57*12/1000</f>
         <v/>
       </c>
-      <c r="D58" s="31">
+      <c r="D58" s="32">
         <f>D56*D57*12/1000</f>
         <v/>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="32">
         <f>E56*E57*12/1000</f>
         <v/>
       </c>
-      <c r="F58" s="31">
+      <c r="F58" s="32">
         <f>F56*F57*12/1000</f>
         <v/>
       </c>
@@ -8044,23 +8018,23 @@
           <t>Pasted mobile segment revenue (the build output above)</t>
         </is>
       </c>
-      <c r="B59" s="18">
+      <c r="B59" s="19">
         <f>E5</f>
         <v/>
       </c>
-      <c r="C59" s="18">
+      <c r="C59" s="19">
         <f>F5</f>
         <v/>
       </c>
-      <c r="D59" s="18">
+      <c r="D59" s="19">
         <f>G5</f>
         <v/>
       </c>
-      <c r="E59" s="18">
+      <c r="E59" s="19">
         <f>H5</f>
         <v/>
       </c>
-      <c r="F59" s="18">
+      <c r="F59" s="19">
         <f>I5</f>
         <v/>
       </c>
@@ -8071,24 +8045,24 @@
           <t>Check — unit-implied less pasted</t>
         </is>
       </c>
-      <c r="B60" s="31" t="inlineStr">
+      <c r="B60" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="35">
+      <c r="C60" s="36">
         <f>C58-C59</f>
         <v/>
       </c>
-      <c r="D60" s="35">
+      <c r="D60" s="36">
         <f>D58-D59</f>
         <v/>
       </c>
-      <c r="E60" s="35">
+      <c r="E60" s="36">
         <f>E58-E59</f>
         <v/>
       </c>
-      <c r="F60" s="35">
+      <c r="F60" s="36">
         <f>F58-F59</f>
         <v/>
       </c>
@@ -8164,7 +8138,7 @@
           <t>Justified price / earnings (GCC peer median)</t>
         </is>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="37">
         <f>Assumptions!$C$93</f>
         <v/>
       </c>
@@ -8175,7 +8149,7 @@
           <t>Implied value at 31-Dec-2025 (AED)</t>
         </is>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="16">
         <f>C5*C6</f>
         <v/>
       </c>
@@ -8186,7 +8160,7 @@
           <t>Anchor accretion factor</t>
         </is>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="38">
         <f>DCF!C62</f>
         <v/>
       </c>
@@ -8206,13 +8180,13 @@
       <c r="A10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Implied value per share at the anchor (AED)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="30">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="31">
         <f>C7*C8-C9</f>
         <v/>
       </c>
@@ -8223,11 +8197,11 @@
           <t>Bear at 12.0x (C) / bull at 18.5x (D), same construction</t>
         </is>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="16">
         <f>C5*12*C8-C9</f>
         <v/>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="16">
         <f>C5*18.5*C8-C9</f>
         <v/>
       </c>
@@ -8238,7 +8212,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="37">
         <f>Assumptions!$C$5/'Income Statement'!D19</f>
         <v/>
       </c>
@@ -8249,7 +8223,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$83-Assumptions!$C$84)/'Income Statement'!D9</f>
         <v/>
       </c>
@@ -8271,7 +8245,7 @@
           <t>Peer benchmark dividend yield</t>
         </is>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="9">
         <f>Assumptions!$C$94</f>
         <v/>
       </c>
@@ -8282,7 +8256,7 @@
           <t>Implied value from the yield cross (AED)</t>
         </is>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="16">
         <f>C15/C16</f>
         <v/>
       </c>
@@ -8305,7 +8279,7 @@
           <t>Current-scale revenue (FY2026E, AED mn)</t>
         </is>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <f>DCF!B5</f>
         <v/>
       </c>
@@ -8316,7 +8290,7 @@
           <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="17">
         <f>DCF!D7</f>
         <v/>
       </c>
@@ -8327,7 +8301,7 @@
           <t>Normalised EBITDA (AED mn)</t>
         </is>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>C20*C21</f>
         <v/>
       </c>
@@ -8338,7 +8312,7 @@
           <t>Normalised EBIT (AED mn) — less FY2026E depreciation and amortisation</t>
         </is>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="19">
         <f>C22+'Income Statement'!E11</f>
         <v/>
       </c>
@@ -8349,7 +8323,7 @@
           <t>Net finance income (FY2026E, AED mn)</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="19">
         <f>'Income Statement'!E13+'Income Statement'!E14</f>
         <v/>
       </c>
@@ -8360,7 +8334,7 @@
           <t>Normalised net profit (AED mn)</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <f>(C23+C24)*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -8371,19 +8345,19 @@
           <t>Normalised earnings per share (AED)</t>
         </is>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="16">
         <f>C25/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Implied value per share at the anchor (AED)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="30">
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="31">
         <f>C26*Assumptions!$C$93*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
@@ -8392,11 +8366,11 @@
           <t>bear 12.0x (E) / bull 18.5x (F):</t>
         </is>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="16">
         <f>C26*12*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="16">
         <f>C26*18.5*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
@@ -8430,7 +8404,7 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="9">
         <f>Assumptions!$C$95</f>
         <v/>
       </c>
@@ -8441,7 +8415,7 @@
           <t>Trailing return on equity</t>
         </is>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="17">
         <f>'Income Statement'!D18/(('Balance Sheet'!C14+'Balance Sheet'!D14)/2)</f>
         <v/>
       </c>
@@ -8452,7 +8426,7 @@
           <t>Perpetual (terminal) cost of equity — a steady-state multiple takes a steady-state rate</t>
         </is>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="17">
         <f>DCF!C50</f>
         <v/>
       </c>
@@ -8463,19 +8437,19 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="39">
         <f>(C31-Assumptions!$C$80)/(C33-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Implied value per share at the anchor (AED)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="30">
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="31">
         <f>C30*C34*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
@@ -8484,11 +8458,11 @@
           <t>bear / bull constructions (E / F):</t>
         </is>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="16">
         <f>((Assumptions!$C$95-Assumptions!$C$80)/((DCF!C40+DCF!C50)/2+0.01-Assumptions!$C$80))*C30*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="16">
         <f>((Assumptions!$C$95+0.02-Assumptions!$C$80)/(DCF!C50-Assumptions!$C$80))*C30*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
@@ -8573,23 +8547,23 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>Segments!E9</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>Segments!F9</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>Segments!G9</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>Segments!H9</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>Segments!I9</f>
         <v/>
       </c>
@@ -8600,23 +8574,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>Segments!B51</f>
         <v/>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>Segments!C51</f>
         <v/>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <f>Segments!D51</f>
         <v/>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>Segments!E51</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="19">
         <f>Segments!F51</f>
         <v/>
       </c>
@@ -8627,23 +8601,23 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <f>B6/B5</f>
         <v/>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <f>F6/F5</f>
         <v/>
       </c>
@@ -8654,50 +8628,50 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <f>'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="19">
         <f>'Income Statement'!I11</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -8708,23 +8682,23 @@
           <t>NOPAT — EBIT x (1 - 43.6% combined royalty and tax)</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <f>B9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>C9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>D9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>E9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>F9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -8735,23 +8709,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>-F8</f>
         <v/>
       </c>
@@ -8762,23 +8736,23 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="32">
         <f>-B5*Assumptions!$B$62</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>-C5*Assumptions!$C$62</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>-D5*Assumptions!$D$62</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>-E5*Assumptions!$E$62</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>-F5*Assumptions!$F$62</f>
         <v/>
       </c>
@@ -8789,23 +8763,23 @@
           <t>Memo — lease replacement at right-of-use depreciation, NOT deducted (leases are debt)</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>Assumptions!$B$66</f>
         <v/>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>Assumptions!$C$66</f>
         <v/>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>Assumptions!$D$66</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>Assumptions!$E$66</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>Assumptions!$F$66</f>
         <v/>
       </c>
@@ -8816,50 +8790,50 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>-(B5*Assumptions!$C$67-'Balance Sheet'!D11)</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>-(C5-B5)*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>-(D5-C5)*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>-(E5-D5)*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>-(F5-E5)*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <f>B10+B11+B12+B14</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>C10+C11+C12+C14</f>
         <v/>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>D10+D11+D12+D14</f>
         <v/>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>E10+E11+E12+E14</f>
         <v/>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>F10+F11+F12+F14</f>
         <v/>
       </c>
@@ -8870,23 +8844,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B16" s="39">
+      <c r="B16" s="40">
         <f>$C$47-($C$47-$C$54)*B58</f>
         <v/>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="40">
         <f>$C$47-($C$47-$C$54)*C58</f>
         <v/>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="40">
         <f>$C$47-($C$47-$C$54)*D58</f>
         <v/>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="40">
         <f>$C$47-($C$47-$C$54)*E58</f>
         <v/>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="40">
         <f>$C$47-($C$47-$C$54)*F58</f>
         <v/>
       </c>
@@ -8897,56 +8871,56 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="41">
         <f>1/(1+B16)</f>
         <v/>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="41">
         <f>B17/(1+C16)</f>
         <v/>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="41">
         <f>C17/(1+D16)</f>
         <v/>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="41">
         <f>D17/(1+E16)</f>
         <v/>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="41">
         <f>E17/(1+F16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <f>B15*B17</f>
         <v/>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>C15*C17</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>D15*D17</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>E15*E17</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <f>F15*F17</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>TERMINAL VALUE, BRIDGE AND THE ANCHOR ROLL</t>
         </is>
@@ -8958,7 +8932,7 @@
           <t>Terminal-year NOPAT grown one year (AED mn)</t>
         </is>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>F10*(1+C24)</f>
         <v/>
       </c>
@@ -8969,7 +8943,7 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <f>F10*(1+C24)/'Summary Financials'!I13</f>
         <v/>
       </c>
@@ -8980,7 +8954,7 @@
           <t>Required reinvestment rate (g / return on capital)</t>
         </is>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="9">
         <f>C24/C22</f>
         <v/>
       </c>
@@ -8991,7 +8965,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="17">
         <f>Assumptions!$C$80</f>
         <v/>
       </c>
@@ -9002,7 +8976,7 @@
           <t>Terminal cost of capital</t>
         </is>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="9">
         <f>C54</f>
         <v/>
       </c>
@@ -9013,7 +8987,7 @@
           <t>Terminal value — terminal-year NOPAT C21 x (1−C23), capitalised (AED mn)</t>
         </is>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="32">
         <f>C21*(1-C23)/(C25-C24)</f>
         <v/>
       </c>
@@ -9024,7 +8998,7 @@
           <t>Present value of the five forecast years (AED mn)</t>
         </is>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <f>SUM(B18:F18)</f>
         <v/>
       </c>
@@ -9035,7 +9009,7 @@
           <t>Present value of the terminal value (AED mn)</t>
         </is>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <f>C26*F17</f>
         <v/>
       </c>
@@ -9046,7 +9020,7 @@
           <t>Terminal value as a share of enterprise value</t>
         </is>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="9">
         <f>C28/(C27+C28)</f>
         <v/>
       </c>
@@ -9057,7 +9031,7 @@
           <t>Enterprise value (AED mn)</t>
         </is>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="32">
         <f>C27+C28</f>
         <v/>
       </c>
@@ -9068,26 +9042,26 @@
           <t>Equity value (AED mn)</t>
         </is>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="19">
         <f>'SOTP Bridge'!C11</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Fair value per share at 31-Dec-2025 (AED)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="30">
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="31">
         <f>C31/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D32" s="15" t="n"/>
+      <c r="D32" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>COST OF CAPITAL — BUILT HERE, NOT ASSUMED</t>
         </is>
@@ -9099,7 +9073,7 @@
           <t>Risk-free rate — Jan-2031 AED T-bond (longest liquid AED tenor)</t>
         </is>
       </c>
-      <c r="C35" s="41">
+      <c r="C35" s="42">
         <f>Assumptions!$C$70</f>
         <v/>
       </c>
@@ -9110,7 +9084,7 @@
           <t>Less UAE sovereign default spread (removed to avoid double-counting)</t>
         </is>
       </c>
-      <c r="C36" s="41">
+      <c r="C36" s="42">
         <f>Assumptions!$C$71</f>
         <v/>
       </c>
@@ -9121,7 +9095,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="40">
         <f>C35-C36</f>
         <v/>
       </c>
@@ -9132,7 +9106,7 @@
           <t>Beta (DU weekly vs the FTSE ADX General, 5 years)</t>
         </is>
       </c>
-      <c r="C38" s="42">
+      <c r="C38" s="43">
         <f>Assumptions!$C$73</f>
         <v/>
       </c>
@@ -9143,7 +9117,7 @@
           <t>Equity risk premium (UAE total, rating basis)</t>
         </is>
       </c>
-      <c r="C39" s="41">
+      <c r="C39" s="42">
         <f>Assumptions!$C$72</f>
         <v/>
       </c>
@@ -9154,7 +9128,7 @@
           <t>Cost of equity, explicit window</t>
         </is>
       </c>
-      <c r="C40" s="39">
+      <c r="C40" s="40">
         <f>C37+C38*C39</f>
         <v/>
       </c>
@@ -9165,7 +9139,7 @@
           <t>Marginal cost of debt (AED sovereign + GCC telecom spread)</t>
         </is>
       </c>
-      <c r="C41" s="41">
+      <c r="C41" s="42">
         <f>Assumptions!$C$74</f>
         <v/>
       </c>
@@ -9176,7 +9150,7 @@
           <t>Cost of debt after tax (interest shields both fiscal legs)</t>
         </is>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="40">
         <f>C41*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -9187,7 +9161,7 @@
           <t>Market capitalisation (AED mn)</t>
         </is>
       </c>
-      <c r="C43" s="18">
+      <c r="C43" s="19">
         <f>Assumptions!$C$5*Assumptions!$C$6</f>
         <v/>
       </c>
@@ -9198,7 +9172,7 @@
           <t>Lease liabilities — the only debt-like item (AED mn)</t>
         </is>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="19">
         <f>Assumptions!$C$83</f>
         <v/>
       </c>
@@ -9209,7 +9183,7 @@
           <t>Debt weight (leases / (leases + market capitalisation))</t>
         </is>
       </c>
-      <c r="C45" s="39">
+      <c r="C45" s="40">
         <f>C44/(C44+C43)</f>
         <v/>
       </c>
@@ -9220,23 +9194,23 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C46" s="39">
+      <c r="C46" s="40">
         <f>1-C45</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Cost of capital, explicit window</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="43">
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="44">
         <f>C46*C40+C45*C42</f>
         <v/>
       </c>
-      <c r="D47" s="15" t="n"/>
+      <c r="D47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -9244,7 +9218,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C48" s="41">
+      <c r="C48" s="42">
         <f>Assumptions!$C$76</f>
         <v/>
       </c>
@@ -9255,7 +9229,7 @@
           <t>Terminal risk-free net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C49" s="39">
+      <c r="C49" s="40">
         <f>C48-C36</f>
         <v/>
       </c>
@@ -9266,7 +9240,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C50" s="39">
+      <c r="C50" s="40">
         <f>C49+C38*Assumptions!$C$77</f>
         <v/>
       </c>
@@ -9277,7 +9251,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C51" s="41">
+      <c r="C51" s="42">
         <f>Assumptions!$C$78</f>
         <v/>
       </c>
@@ -9288,7 +9262,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C52" s="39">
+      <c r="C52" s="40">
         <f>C51*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -9299,23 +9273,23 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C53" s="41">
+      <c r="C53" s="42">
         <f>Assumptions!$C$79</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>Terminal cost of capital</t>
         </is>
       </c>
-      <c r="B54" s="15" t="n"/>
-      <c r="C54" s="43">
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="44">
         <f>(1-C53)*C50+C53*C52</f>
         <v/>
       </c>
-      <c r="D54" s="15" t="n"/>
+      <c r="D54" s="13" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -9355,23 +9329,23 @@
           <t>AED risk-free path</t>
         </is>
       </c>
-      <c r="B57" s="41">
+      <c r="B57" s="42">
         <f>Assumptions!$B$75</f>
         <v/>
       </c>
-      <c r="C57" s="41">
+      <c r="C57" s="42">
         <f>Assumptions!$C$75</f>
         <v/>
       </c>
-      <c r="D57" s="41">
+      <c r="D57" s="42">
         <f>Assumptions!$D$75</f>
         <v/>
       </c>
-      <c r="E57" s="41">
+      <c r="E57" s="42">
         <f>Assumptions!$E$75</f>
         <v/>
       </c>
-      <c r="F57" s="41">
+      <c r="F57" s="42">
         <f>Assumptions!$F$75</f>
         <v/>
       </c>
@@ -9382,23 +9356,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B58" s="39">
+      <c r="B58" s="40">
         <f>($B$57-B57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="C58" s="39">
+      <c r="C58" s="40">
         <f>($B$57-C57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="D58" s="39">
+      <c r="D58" s="40">
         <f>($B$57-D57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="E58" s="39">
+      <c r="E58" s="40">
         <f>($B$57-E57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="F58" s="39">
+      <c r="F58" s="40">
         <f>($B$57-F57)/($B$57-$F$57)</f>
         <v/>
       </c>
@@ -9411,7 +9385,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>THE ANCHOR ROLL — one date, one price of time</t>
         </is>
@@ -9423,23 +9397,23 @@
           <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
         </is>
       </c>
-      <c r="C62" s="40">
+      <c r="C62" s="41">
         <f>(1+C40)^(Assumptions!$C$90/365)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>Fair value per share at the 07-Aug-2026 anchor (AED)</t>
         </is>
       </c>
-      <c r="B63" s="15" t="n"/>
-      <c r="C63" s="30">
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="31">
         <f>C32*C62-Assumptions!$C$89</f>
         <v/>
       </c>
-      <c r="D63" s="15" t="n"/>
+      <c r="D63" s="13" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -9544,37 +9518,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="30" t="n">
         <v>13636.34</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>14635.917</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>15905.421</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="30">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="30">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="30">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -9585,7 +9559,7 @@
           <t>Direct costs (interconnect, commissions, devices)</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9596,23 +9570,23 @@
       <c r="D6" s="23" t="n">
         <v>-5259.425</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>-(DCF!B5-Segments!B32)</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="19">
         <f>-(DCF!C5-Segments!C32)</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="19">
         <f>-(DCF!D5-Segments!D32)</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="19">
         <f>-(DCF!E5-Segments!E32)</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="19">
         <f>-(DCF!F5-Segments!F32)</f>
         <v/>
       </c>
@@ -9623,36 +9597,36 @@
           <t>Segment contribution</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>F5+F6</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>G5+G6</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>H5+H6</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="32">
         <f>I5+I6</f>
         <v/>
       </c>
@@ -9663,7 +9637,7 @@
           <t>Operating expenses before D&amp;A</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9674,61 +9648,61 @@
       <c r="D8" s="23" t="n">
         <v>-3307.608</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>-Segments!B50</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="19">
         <f>-Segments!C50</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="19">
         <f>-Segments!D50</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="19">
         <f>-Segments!E50</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="19">
         <f>-Segments!F50</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="30" t="n">
         <v>5799.601</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="30">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="30">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -9739,35 +9713,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <f>B9/B5</f>
         <v/>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <f>C9/C5</f>
         <v/>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <f>D9/D5</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <f>E9/E5</f>
         <v/>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <f>F9/F5</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <f>G9/G5</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="9">
         <f>H9/H5</f>
         <v/>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <f>I9/I5</f>
         <v/>
       </c>
@@ -9787,62 +9761,62 @@
       <c r="D11" s="23" t="n">
         <v>-2167.933</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>-('Balance Sheet'!E6+'Balance Sheet'!E9+Assumptions!$B$66)</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>-('Balance Sheet'!F6+'Balance Sheet'!F9+Assumptions!$C$66)</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="32">
         <f>-('Balance Sheet'!G6+'Balance Sheet'!G9+Assumptions!$D$66)</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>-('Balance Sheet'!H6+'Balance Sheet'!H9+Assumptions!$E$66)</f>
         <v/>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="32">
         <f>-('Balance Sheet'!I6+'Balance Sheet'!I9+Assumptions!$F$66)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <f>B9+B11</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>C9+C11</f>
         <v/>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>D9+D11</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>E9+E11</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>F9+F11</f>
         <v/>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="30">
         <f>G9+G11</f>
         <v/>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="30">
         <f>H9+H11</f>
         <v/>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="30">
         <f>I9+I11</f>
         <v/>
       </c>
@@ -9862,23 +9836,23 @@
       <c r="D13" s="23" t="n">
         <v>74.672</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!D12,0)</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!E12,0)</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!F12,0)</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!G12,0)</f>
         <v/>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!H12,0)</f>
         <v/>
       </c>
@@ -9898,23 +9872,23 @@
       <c r="D14" s="23" t="n">
         <v>-95.054</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!E13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!F13</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!G13</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!H13</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!I13</f>
         <v/>
       </c>
@@ -9936,37 +9910,37 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Profit before federal royalty and income tax</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="30" t="n">
         <v>3558.501</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="30" t="n">
         <v>4306.151</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="30" t="n">
         <v>5149.122</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <f>E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <f>F12+F13+F14</f>
         <v/>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <f>G12+G13+G14</f>
         <v/>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="30">
         <f>H12+H13+H14</f>
         <v/>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="30">
         <f>I12+I13+I14</f>
         <v/>
       </c>
@@ -9986,62 +9960,62 @@
       <c r="D17" s="23" t="n">
         <v>-2244.037</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>-E16*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>-F16*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>-G16*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>-H16*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="32">
         <f>-I16*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Net profit</t>
         </is>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <f>B16+B17</f>
         <v/>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="30">
         <f>G16+G17</f>
         <v/>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="30">
         <f>H16+H17</f>
         <v/>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="30">
         <f>I16+I17</f>
         <v/>
       </c>
@@ -10052,35 +10026,35 @@
           <t>Earnings per share (AED)</t>
         </is>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="16">
         <f>B18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="16">
         <f>C18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="16">
         <f>D18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="16">
         <f>E18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="16">
         <f>F18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="16">
         <f>G18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="16">
         <f>H18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="16">
         <f>I18/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -10100,23 +10074,23 @@
       <c r="D20" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="16">
         <f>E19*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="16">
         <f>F19*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="16">
         <f>G19*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="16">
         <f>H19*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="16">
         <f>I19*Assumptions!$C$86</f>
         <v/>
       </c>

--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -4577,17 +4577,13 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>vs spot</t>
+          <t>vs price</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5088,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Weighted central</t>
+          <t>THE CENTRAL — the cash-flow lens itself, not an average of the four</t>
         </is>
       </c>
       <c r="B12" s="13" t="n"/>

--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,23 +131,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1162,23 +1163,23 @@
       <c r="D5" s="23" t="n">
         <v>10288.767</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>D5-DCF!B12*Assumptions!$C$63-E6</f>
         <v/>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <f>E5-DCF!C12*Assumptions!$C$63-F6</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="32">
         <f>F5-DCF!D12*Assumptions!$C$63-G6</f>
         <v/>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <f>G5-DCF!E12*Assumptions!$C$63-H6</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="32">
         <f>H5-DCF!F12*Assumptions!$C$63-I6</f>
         <v/>
       </c>
@@ -1198,23 +1199,23 @@
       <c r="D6" s="23" t="n">
         <v>1557.989</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>Assumptions!$C$64*D5</f>
         <v/>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>Assumptions!$C$64*E5</f>
         <v/>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="32">
         <f>Assumptions!$C$64*F5</f>
         <v/>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <f>Assumptions!$C$64*G5</f>
         <v/>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="32">
         <f>Assumptions!$C$64*H5</f>
         <v/>
       </c>
@@ -1234,23 +1235,23 @@
       <c r="D7" s="23" t="n">
         <v>1515.395</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="32">
         <f>$D$7</f>
         <v/>
       </c>
@@ -1270,23 +1271,23 @@
       <c r="D8" s="23" t="n">
         <v>869.6</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>D8-DCF!B12*(1-Assumptions!$C$63)-E9</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>E8-DCF!C12*(1-Assumptions!$C$63)-F9</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>F8-DCF!D12*(1-Assumptions!$C$63)-G9</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>G8-DCF!E12*(1-Assumptions!$C$63)-H9</f>
         <v/>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="32">
         <f>H8-DCF!F12*(1-Assumptions!$C$63)-I9</f>
         <v/>
       </c>
@@ -1306,23 +1307,23 @@
       <c r="D9" s="23" t="n">
         <v>245.881</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>Assumptions!$C$65*D8</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>Assumptions!$C$65*E8</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="32">
         <f>Assumptions!$C$65*F8</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <f>Assumptions!$C$65*G8</f>
         <v/>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="32">
         <f>Assumptions!$C$65*H8</f>
         <v/>
       </c>
@@ -1333,7 +1334,7 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1344,23 +1345,23 @@
       <c r="D10" s="23" t="n">
         <v>413.22</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="32">
         <f>$D$10</f>
         <v/>
       </c>
@@ -1380,23 +1381,23 @@
       <c r="D11" s="23" t="n">
         <v>-1062.442</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>'Income Statement'!E5*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>'Income Statement'!F5*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="32">
         <f>'Income Statement'!G5*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>'Income Statement'!H5*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="32">
         <f>'Income Statement'!I5*Assumptions!$C$67</f>
         <v/>
       </c>
@@ -1416,23 +1417,23 @@
       <c r="D12" s="23" t="n">
         <v>2249.719</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>D12+'Income Statement'!E18-'Income Statement'!E11+DCF!B12+DCF!B14-'Income Statement'!E18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>E12+'Income Statement'!F18-'Income Statement'!F11+DCF!C12+DCF!C14-'Income Statement'!F18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="32">
         <f>F12+'Income Statement'!G18-'Income Statement'!G11+DCF!D12+DCF!D14-'Income Statement'!G18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="32">
         <f>G12+'Income Statement'!H18-'Income Statement'!H11+DCF!E12+DCF!E14-'Income Statement'!H18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="32">
         <f>H12+'Income Statement'!I18-'Income Statement'!I11+DCF!F12+DCF!F14-'Income Statement'!I18*Assumptions!$C$86</f>
         <v/>
       </c>
@@ -1452,59 +1453,59 @@
       <c r="D13" s="23" t="n">
         <v>1938.819</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="32">
         <f>$D$13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="30" t="n">
         <v>9243.213</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="30" t="n">
         <v>9878.445</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="30" t="n">
         <v>10148.291</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>D14+'Income Statement'!E18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>E14+'Income Statement'!F18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <f>F14+'Income Statement'!G18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <f>G14+'Income Statement'!H18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="30">
         <f>H14+'Income Statement'!I18*(1-Assumptions!$C$86)</f>
         <v/>
       </c>
@@ -1515,35 +1516,35 @@
           <t>Net cash after lease liabilities</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <f>B12-B13</f>
         <v/>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>D12-D13</f>
         <v/>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>E12-E13</f>
         <v/>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>F12-F13</f>
         <v/>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>G12-G13</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="32">
         <f>H12-H13</f>
         <v/>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="32">
         <f>I12-I13</f>
         <v/>
       </c>
@@ -1554,35 +1555,35 @@
           <t>Lease liabilities / EBITDA</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="39">
         <f>B13/'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <f>C13/'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="39">
         <f>D13/'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="39">
         <f>E13/'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="39">
         <f>F13/'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G16" s="38">
+      <c r="G16" s="39">
         <f>G13/'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="39">
         <f>H13/'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I16" s="38">
+      <c r="I16" s="39">
         <f>I13/'Income Statement'!I9</f>
         <v/>
       </c>
@@ -1690,31 +1691,31 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="19">
         <f>'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="19">
         <f>'Income Statement'!I9</f>
         <v/>
       </c>
@@ -1764,33 +1765,33 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>DCF!B10</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>DCF!C10</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>DCF!D10</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="19">
         <f>DCF!E10</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="19">
         <f>DCF!F10</f>
         <v/>
       </c>
@@ -1801,33 +1802,33 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>DCF!B11</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>DCF!C11</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>DCF!D11</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <f>DCF!E11</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="19">
         <f>DCF!F11</f>
         <v/>
       </c>
@@ -1838,33 +1839,33 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f>DCF!B12</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>DCF!C12</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <f>DCF!D12</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="19">
         <f>DCF!E12</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="19">
         <f>DCF!F12</f>
         <v/>
       </c>
@@ -1875,33 +1876,33 @@
           <t>Memo — lease replacement, NOT deducted (leases are debt)</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f>DCF!B13</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>DCF!C13</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <f>DCF!D13</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <f>DCF!E13</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="19">
         <f>DCF!F13</f>
         <v/>
       </c>
@@ -1912,73 +1913,73 @@
           <t>Change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>-('Balance Sheet'!D11-'Balance Sheet'!C11)</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>DCF!B14</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>DCF!C14</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>DCF!D14</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="19">
         <f>DCF!E14</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="19">
         <f>DCF!F14</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>D9+D10+D11+D13</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>E9+E10+E11+E13</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>F9+F10+F11+F13</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <f>G9+G10+G11+G13</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <f>H9+H10+H11+H13</f>
         <v/>
       </c>
-      <c r="I14" s="15" t="n"/>
+      <c r="I14" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1992,23 +1993,23 @@
       <c r="C16" s="23" t="n">
         <v>-2629.085</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>-'Income Statement'!E18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>-'Income Statement'!F18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>-'Income Statement'!G18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>-'Income Statement'!H18*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>-'Income Statement'!I18*Assumptions!$C$86</f>
         <v/>
       </c>
@@ -2019,7 +2020,7 @@
           <t>Cash conversion — operating cash flow as a share of EBITDA, FY2025</t>
         </is>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="9">
         <f>C7/C5</f>
         <v/>
       </c>
@@ -2132,35 +2133,35 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="19">
         <f>'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="19">
         <f>'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="19">
         <f>'Income Statement'!I5</f>
         <v/>
       </c>
@@ -2171,36 +2172,36 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="9">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="9">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9">
         <f>I5/H5-1</f>
         <v/>
       </c>
@@ -2211,35 +2212,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="19">
         <f>'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="19">
         <f>'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="19">
         <f>'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="19">
         <f>'Income Statement'!I9</f>
         <v/>
       </c>
@@ -2250,35 +2251,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <f>I7/I5</f>
         <v/>
       </c>
@@ -2289,35 +2290,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>'Income Statement'!B12</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>'Income Statement'!C12</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>'Income Statement'!D12</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>'Income Statement'!E12</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>'Income Statement'!F12</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="19">
         <f>'Income Statement'!G12</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="19">
         <f>'Income Statement'!H12</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="19">
         <f>'Income Statement'!I12</f>
         <v/>
       </c>
@@ -2328,35 +2329,35 @@
           <t>Net profit</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>'Income Statement'!B18</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>'Income Statement'!C18</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>'Income Statement'!D18</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>'Income Statement'!E18</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>'Income Statement'!F18</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <f>'Income Statement'!G18</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="19">
         <f>'Income Statement'!H18</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="19">
         <f>'Income Statement'!I18</f>
         <v/>
       </c>
@@ -2367,38 +2368,38 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>'Cash Flow'!D14</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <f>'Cash Flow'!E14</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="19">
         <f>'Cash Flow'!F14</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="19">
         <f>'Cash Flow'!G14</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="19">
         <f>'Cash Flow'!H14</f>
         <v/>
       </c>
@@ -2409,35 +2410,35 @@
           <t>Net cash after lease liabilities</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <f>'Balance Sheet'!B15</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <f>'Balance Sheet'!C15</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f>'Balance Sheet'!D15</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>'Balance Sheet'!E15</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <f>'Balance Sheet'!F15</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <f>'Balance Sheet'!G15</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="19">
         <f>'Balance Sheet'!H15</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="19">
         <f>'Balance Sheet'!I15</f>
         <v/>
       </c>
@@ -2448,36 +2449,36 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <f>'Balance Sheet'!C5+'Balance Sheet'!C7+'Balance Sheet'!C8+'Balance Sheet'!C10+'Balance Sheet'!C11</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>'Balance Sheet'!D5+'Balance Sheet'!D7+'Balance Sheet'!D8+'Balance Sheet'!D10+'Balance Sheet'!D11</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>'Balance Sheet'!E5+'Balance Sheet'!E7+'Balance Sheet'!E8+'Balance Sheet'!E10+'Balance Sheet'!E11</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>'Balance Sheet'!F5+'Balance Sheet'!F7+'Balance Sheet'!F8+'Balance Sheet'!F10+'Balance Sheet'!F11</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="19">
         <f>'Balance Sheet'!G5+'Balance Sheet'!G7+'Balance Sheet'!G8+'Balance Sheet'!G10+'Balance Sheet'!G11</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="19">
         <f>'Balance Sheet'!H5+'Balance Sheet'!H7+'Balance Sheet'!H8+'Balance Sheet'!H10+'Balance Sheet'!H11</f>
         <v/>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="19">
         <f>'Balance Sheet'!I5+'Balance Sheet'!I7+'Balance Sheet'!I8+'Balance Sheet'!I10+'Balance Sheet'!I11</f>
         <v/>
       </c>
@@ -2488,38 +2489,38 @@
           <t>Return on invested capital (average capital)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="17">
         <f>DCF!B10/((D13+E13)/2)</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="17">
         <f>DCF!C10/((E13+F13)/2)</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>DCF!D10/((F13+G13)/2)</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="17">
         <f>DCF!E10/((G13+H13)/2)</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="17">
         <f>DCF!F10/((H13+I13)/2)</f>
         <v/>
       </c>
@@ -2635,7 +2636,7 @@
       <c r="F5" s="7" t="n">
         <v>13.87837142039896</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="24" t="n">
         <v>0.49186</v>
       </c>
     </row>
@@ -2660,7 +2661,7 @@
       <c r="F6" s="7" t="n">
         <v>15.32471824257266</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="24" t="n">
         <v>0.48962</v>
       </c>
     </row>
@@ -2687,10 +2688,10 @@
           <t>Finishes 10% or more above spot</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="24" t="n">
         <v>0.09089999999999999</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="24" t="n">
         <v>0.21854</v>
       </c>
     </row>
@@ -2700,10 +2701,10 @@
           <t>Finishes 10% or more below spot</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="24" t="n">
         <v>0.07883999999999999</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="24" t="n">
         <v>0.21026</v>
       </c>
     </row>
@@ -2713,10 +2714,10 @@
           <t>Touches 10% above spot at any point</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="24" t="n">
         <v>0.1523</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="24" t="n">
         <v>0.40526</v>
       </c>
     </row>
@@ -2726,10 +2727,10 @@
           <t>Touches 10% below spot at any point</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="24" t="n">
         <v>0.128</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="24" t="n">
         <v>0.37854</v>
       </c>
     </row>
@@ -2761,7 +2762,7 @@
           <t>Annualised volatility (3-month anchor)</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="24" t="n">
         <v>0.2808947610903803</v>
       </c>
     </row>
@@ -2772,7 +2773,7 @@
         </is>
       </c>
       <c r="C17" s="8">
-        <f>Summary!C14</f>
+        <f>Summary!C15</f>
         <v/>
       </c>
     </row>
@@ -2782,7 +2783,7 @@
           <t>Anchor date</t>
         </is>
       </c>
-      <c r="C18" s="44" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -2835,7 +2836,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Terminal cost of capital (rows) x terminal growth (columns)</t>
         </is>
@@ -2980,7 +2981,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Explicit-window cost of capital (columns) x terminal cost of capital (rows)</t>
         </is>
@@ -3125,7 +3126,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Single-driver sensitivities — five engine re-runs per row; the parameter grid for each row is shown beside its name</t>
         </is>
@@ -3170,7 +3171,7 @@
       <c r="F22" s="7" t="n">
         <v>13.8943248227103</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
         <v/>
       </c>
@@ -3196,7 +3197,7 @@
       <c r="F23" s="7" t="n">
         <v>15.30952628288052</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
         <v/>
       </c>
@@ -3222,7 +3223,7 @@
       <c r="F24" s="7" t="n">
         <v>21.77719264552191</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
         <v/>
       </c>
@@ -3248,7 +3249,7 @@
       <c r="F25" s="7" t="n">
         <v>19.83109343891408</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
         <v/>
       </c>
@@ -3274,7 +3275,7 @@
       <c r="F26" s="7" t="n">
         <v>17.70370701195685</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
         <v/>
       </c>
@@ -3300,7 +3301,7 @@
       <c r="F27" s="7" t="n">
         <v>20.3331339912772</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
         <v/>
       </c>
@@ -3326,7 +3327,7 @@
       <c r="F28" s="7" t="n">
         <v>17.52507215192293</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
         <v/>
       </c>
@@ -3352,7 +3353,7 @@
       <c r="F29" s="7" t="n">
         <v>18.6580060074063</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="16">
         <f>MAX(B29:F29)-MIN(B29:F29)</f>
         <v/>
       </c>
@@ -3378,7 +3379,7 @@
       <c r="F30" s="7" t="n">
         <v>19.20646518163991</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="16">
         <f>MAX(B30:F30)-MIN(B30:F30)</f>
         <v/>
       </c>
@@ -3404,7 +3405,7 @@
       <c r="F31" s="7" t="n">
         <v>24.28194674822564</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="16">
         <f>MAX(B31:F31)-MIN(B31:F31)</f>
         <v/>
       </c>
@@ -3510,35 +3511,35 @@
           <t>Earnings per share (AED)</t>
         </is>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="16">
         <f>'Income Statement'!B19</f>
         <v/>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="16">
         <f>'Income Statement'!C19</f>
         <v/>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="16">
         <f>'Income Statement'!D19</f>
         <v/>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="16">
         <f>'Income Statement'!E19</f>
         <v/>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="16">
         <f>'Income Statement'!F19</f>
         <v/>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="16">
         <f>'Income Statement'!G19</f>
         <v/>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="16">
         <f>'Income Statement'!H19</f>
         <v/>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="16">
         <f>'Income Statement'!I19</f>
         <v/>
       </c>
@@ -3549,35 +3550,35 @@
           <t>Dividend per share (AED)</t>
         </is>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="16">
         <f>'Income Statement'!B20</f>
         <v/>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="16">
         <f>'Income Statement'!C20</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="16">
         <f>'Income Statement'!D20</f>
         <v/>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="16">
         <f>'Income Statement'!E20</f>
         <v/>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="16">
         <f>'Income Statement'!F20</f>
         <v/>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="16">
         <f>'Income Statement'!G20</f>
         <v/>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="16">
         <f>'Income Statement'!H20</f>
         <v/>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="16">
         <f>'Income Statement'!I20</f>
         <v/>
       </c>
@@ -3588,35 +3589,35 @@
           <t>Payout ratio</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <f>'Income Statement'!B20/'Income Statement'!B19</f>
         <v/>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <f>'Income Statement'!C20/'Income Statement'!C19</f>
         <v/>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <f>'Income Statement'!D20/'Income Statement'!D19</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <f>'Income Statement'!E20/'Income Statement'!E19</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <f>'Income Statement'!F20/'Income Statement'!F19</f>
         <v/>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="9">
         <f>'Income Statement'!G20/'Income Statement'!G19</f>
         <v/>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="9">
         <f>'Income Statement'!H20/'Income Statement'!H19</f>
         <v/>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="9">
         <f>'Income Statement'!I20/'Income Statement'!I19</f>
         <v/>
       </c>
@@ -3627,35 +3628,35 @@
           <t>Dividend yield at the anchor spot</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <f>'Income Statement'!B20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>'Income Statement'!C20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <f>'Income Statement'!D20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>'Income Statement'!E20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>'Income Statement'!F20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <f>'Income Statement'!G20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <f>'Income Statement'!H20/Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <f>'Income Statement'!I20/Assumptions!$C$5</f>
         <v/>
       </c>
@@ -3666,35 +3667,35 @@
           <t>Book value per share (AED)</t>
         </is>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="16">
         <f>'Balance Sheet'!B14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="16">
         <f>'Balance Sheet'!C14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="16">
         <f>'Balance Sheet'!D14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="16">
         <f>'Balance Sheet'!E14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="16">
         <f>'Balance Sheet'!F14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="16">
         <f>'Balance Sheet'!G14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="16">
         <f>'Balance Sheet'!H14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="16">
         <f>'Balance Sheet'!I14/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -3705,38 +3706,38 @@
           <t>Free cash flow to the firm per share (AED)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="16">
         <f>'Summary Financials'!E11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="16">
         <f>'Summary Financials'!F11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="16">
         <f>'Summary Financials'!G11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="16">
         <f>'Summary Financials'!H11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="16">
         <f>'Summary Financials'!I11/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -3747,35 +3748,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <f>'Summary Financials'!B8</f>
         <v/>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <f>'Summary Financials'!C8</f>
         <v/>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <f>'Summary Financials'!D8</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <f>'Summary Financials'!E8</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="9">
         <f>'Summary Financials'!F8</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="9">
         <f>'Summary Financials'!G8</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="9">
         <f>'Summary Financials'!H8</f>
         <v/>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="9">
         <f>'Summary Financials'!I8</f>
         <v/>
       </c>
@@ -3786,35 +3787,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <f>'Income Statement'!B12/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="9">
         <f>'Income Statement'!C12/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="9">
         <f>'Income Statement'!D12/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <f>'Income Statement'!E12/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="9">
         <f>'Income Statement'!F12/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="9">
         <f>'Income Statement'!G12/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="9">
         <f>'Income Statement'!H12/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="9">
         <f>'Income Statement'!I12/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3825,35 +3826,35 @@
           <t>Net margin</t>
         </is>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="9">
         <f>'Income Statement'!B18/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="9">
         <f>'Income Statement'!C18/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="9">
         <f>'Income Statement'!D18/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <f>'Income Statement'!E18/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="9">
         <f>'Income Statement'!F18/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="9">
         <f>'Income Statement'!G18/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="9">
         <f>'Income Statement'!H18/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <f>'Income Statement'!I18/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3864,36 +3865,36 @@
           <t>Return on equity</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="9">
         <f>'Income Statement'!C18/(('Balance Sheet'!B14+'Balance Sheet'!C14)/2)</f>
         <v/>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="9">
         <f>'Income Statement'!D18/(('Balance Sheet'!C14+'Balance Sheet'!D14)/2)</f>
         <v/>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <f>'Income Statement'!E18/(('Balance Sheet'!D14+'Balance Sheet'!E14)/2)</f>
         <v/>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="9">
         <f>'Income Statement'!F18/(('Balance Sheet'!E14+'Balance Sheet'!F14)/2)</f>
         <v/>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="9">
         <f>'Income Statement'!G18/(('Balance Sheet'!F14+'Balance Sheet'!G14)/2)</f>
         <v/>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="9">
         <f>'Income Statement'!H18/(('Balance Sheet'!G14+'Balance Sheet'!H14)/2)</f>
         <v/>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <f>'Income Statement'!I18/(('Balance Sheet'!H14+'Balance Sheet'!I14)/2)</f>
         <v/>
       </c>
@@ -3904,38 +3905,38 @@
           <t>Return on invested capital</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="9">
         <f>'Summary Financials'!E14</f>
         <v/>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="9">
         <f>'Summary Financials'!F14</f>
         <v/>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="9">
         <f>'Summary Financials'!G14</f>
         <v/>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="9">
         <f>'Summary Financials'!H14</f>
         <v/>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="9">
         <f>'Summary Financials'!I14</f>
         <v/>
       </c>
@@ -3946,38 +3947,38 @@
           <t>Capital expenditure / revenue (capital intensity)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <f>-'Cash Flow'!D11/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="9">
         <f>-'Cash Flow'!E11/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="9">
         <f>-'Cash Flow'!F11/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="9">
         <f>-'Cash Flow'!G11/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="9">
         <f>-'Cash Flow'!H11/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3988,35 +3989,35 @@
           <t>Lease liabilities / EBITDA</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="39">
         <f>'Balance Sheet'!B16</f>
         <v/>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="39">
         <f>'Balance Sheet'!C16</f>
         <v/>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="39">
         <f>'Balance Sheet'!D16</f>
         <v/>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="39">
         <f>'Balance Sheet'!E16</f>
         <v/>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="39">
         <f>'Balance Sheet'!F16</f>
         <v/>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="39">
         <f>'Balance Sheet'!G16</f>
         <v/>
       </c>
-      <c r="H17" s="38">
+      <c r="H17" s="39">
         <f>'Balance Sheet'!H16</f>
         <v/>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="39">
         <f>'Balance Sheet'!I16</f>
         <v/>
       </c>
@@ -4027,41 +4028,41 @@
           <t>Working capital / revenue</t>
         </is>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <f>'Balance Sheet'!B11/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="9">
         <f>'Balance Sheet'!C11/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="9">
         <f>'Balance Sheet'!D11/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="9">
         <f>'Balance Sheet'!E11/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="9">
         <f>'Balance Sheet'!F11/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="9">
         <f>'Balance Sheet'!G11/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="9">
         <f>'Balance Sheet'!H11/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="9">
         <f>'Balance Sheet'!I11/'Income Statement'!I5</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Operating KPIs (company-disclosed history, house forecast)</t>
         </is>
@@ -4073,7 +4074,7 @@
           <t>Mobile subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4084,23 +4085,23 @@
       <c r="D21" s="23" t="n">
         <v>9704</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="19">
         <f>Assumptions!$B$23</f>
         <v/>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="19">
         <f>Assumptions!$C$23</f>
         <v/>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="19">
         <f>Assumptions!$D$23</f>
         <v/>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="19">
         <f>Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="19">
         <f>Assumptions!$F$23</f>
         <v/>
       </c>
@@ -4111,7 +4112,7 @@
           <t>Fixed subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4122,23 +4123,23 @@
       <c r="D22" s="23" t="n">
         <v>735</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="19">
         <f>Assumptions!$B$24</f>
         <v/>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="19">
         <f>Assumptions!$C$24</f>
         <v/>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="19">
         <f>Assumptions!$D$24</f>
         <v/>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="19">
         <f>Assumptions!$E$24</f>
         <v/>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="19">
         <f>Assumptions!$F$24</f>
         <v/>
       </c>
@@ -4149,34 +4150,34 @@
           <t>Blended mobile ARPU (AED/month)</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="24" t="n">
+      <c r="C23" s="25" t="n">
         <v>65.8</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="25" t="n">
         <v>63.3</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="46">
         <f>Assumptions!$B$25</f>
         <v/>
       </c>
-      <c r="F23" s="45">
+      <c r="F23" s="46">
         <f>Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="G23" s="45">
+      <c r="G23" s="46">
         <f>Assumptions!$D$25</f>
         <v/>
       </c>
-      <c r="H23" s="45">
+      <c r="H23" s="46">
         <f>Assumptions!$E$25</f>
         <v/>
       </c>
-      <c r="I23" s="45">
+      <c r="I23" s="46">
         <f>Assumptions!$F$25</f>
         <v/>
       </c>
@@ -4268,12 +4269,12 @@
           <t>UAE (ADX)</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="45" t="inlineStr">
         <is>
           <t>~20.7x</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="45" t="inlineStr">
         <is>
           <t>~4.8%</t>
         </is>
@@ -4295,12 +4296,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>~18.9x</t>
         </is>
       </c>
-      <c r="D6" s="44" t="inlineStr">
+      <c r="D6" s="45" t="inlineStr">
         <is>
           <t>~5.2%</t>
         </is>
@@ -4322,12 +4323,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="45" t="inlineStr">
         <is>
           <t>~15.5x</t>
         </is>
       </c>
-      <c r="D7" s="44" t="inlineStr">
+      <c r="D7" s="45" t="inlineStr">
         <is>
           <t>~2.9%</t>
         </is>
@@ -4349,12 +4350,12 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>~12.5x</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>~4.6%</t>
         </is>
@@ -4376,12 +4377,12 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C9" s="45" t="inlineStr">
         <is>
           <t>~9x</t>
         </is>
       </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="D9" s="45" t="inlineStr">
         <is>
           <t>~6-7%</t>
         </is>
@@ -4403,12 +4404,12 @@
           <t>Oman</t>
         </is>
       </c>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>~11.4x</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>~6.7%</t>
         </is>
@@ -4430,12 +4431,12 @@
           <t>Developed markets</t>
         </is>
       </c>
-      <c r="C11" s="44" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
         <is>
           <t>n/m</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D11" s="45" t="inlineStr">
         <is>
           <t>3.4% / n/m</t>
         </is>
@@ -4464,7 +4465,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="37">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -4475,7 +4476,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="37">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -4486,7 +4487,7 @@
           <t>Trailing dividend yield (FY2025 DPS / spot)</t>
         </is>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="17">
         <f>'Income Statement'!D20/Assumptions!$C$5</f>
         <v/>
       </c>
@@ -4497,7 +4498,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B17" s="36">
+      <c r="B17" s="37">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -4521,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4576,17 +4577,13 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>vs spot</t>
+          <t>vs price</t>
         </is>
       </c>
     </row>
@@ -4606,15 +4603,13 @@
       <c r="D5" s="7" t="n">
         <v>28.6533036884854</v>
       </c>
-      <c r="E5" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F5" s="10">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>C5/$C$14-1</f>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the class primary</t>
+        </is>
+      </c>
+      <c r="G5" s="9">
+        <f>C5/$C$15-1</f>
         <v/>
       </c>
     </row>
@@ -4636,15 +4631,13 @@
         <f>'Relative &amp; Normalized'!D12</f>
         <v/>
       </c>
-      <c r="E6" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F6" s="10">
-        <f>C6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
-        <f>C6/$C$14-1</f>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="G6" s="9">
+        <f>C6/$C$15-1</f>
         <v/>
       </c>
     </row>
@@ -4666,15 +4659,13 @@
         <f>'Relative &amp; Normalized'!F27</f>
         <v/>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F7" s="10">
-        <f>C7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
-        <f>C7/$C$14-1</f>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED — not a lens this class publishes</t>
+        </is>
+      </c>
+      <c r="G7" s="9">
+        <f>C7/$C$15-1</f>
         <v/>
       </c>
     </row>
@@ -4696,235 +4687,254 @@
         <f>'Relative &amp; Normalized'!F35</f>
         <v/>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F8" s="10">
-        <f>C8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
-        <f>C8/$C$14-1</f>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>a disclosed floor, never weighted</t>
+        </is>
+      </c>
+      <c r="G8" s="9">
+        <f>C8/$C$15-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B9" s="13">
-        <f>B5*E5+B6*E6+B7*E7+B8*E8</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>SUM(F5:F8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>D5*E5+D6*E6+D7*E7+D8*E8</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>SUM(E5:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="15" t="n"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the cash-flow lens, not an average</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>the class primary</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n"/>
       <c r="G9" s="14">
-        <f>C9/$C$14-1</f>
+        <f>C9/$C$15-1</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Span across lenses (min/max — NOT weighted)</t>
-        </is>
-      </c>
-      <c r="B10" s="10">
-        <f>MIN(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="D10" s="10">
-        <f>MAX(D5:D8)</f>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>NOT AVERAGED — the retired blend, published unused</t>
+        </is>
+      </c>
+      <c r="C10" s="16">
+        <f>C5*0.45+C6*0.25+C7*0.2+C8*0.1</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>retired 02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="G10" s="9">
+        <f>C10/$C$15-1</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Contested judgement, other way — no terminal re-rating (Framing 2)</t>
-        </is>
-      </c>
-      <c r="C11" s="8">
-        <f>'Fundamental Valuation'!C18</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>C11/$C$14-1</f>
+          <t>Span across the lenses (min/max) — a spread between METHODS, not a range around the answer</t>
+        </is>
+      </c>
+      <c r="B11" s="16">
+        <f>MIN(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f>MAX(D5:D8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Terminal value share of DCF enterprise value</t>
-        </is>
-      </c>
-      <c r="C12" s="16">
-        <f>DCF!C29</f>
+          <t>Contested judgement, other way — no terminal re-rating (Framing 2)</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
+        <f>'Fundamental Valuation'!C18</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>C12/$C$15-1</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>Terminal value share of DCF enterprise value</t>
+        </is>
+      </c>
+      <c r="C13" s="17">
+        <f>DCF!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>Expert panel median</t>
         </is>
       </c>
-      <c r="C13" s="8">
+      <c r="C14" s="8">
         <f>'Fundamental Valuation'!C27</f>
         <v/>
       </c>
-      <c r="G13" s="11">
-        <f>C13/$C$14-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="G14" s="9">
+        <f>C14/$C$15-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Market price (anchor)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="17" t="n">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="18" t="n">
         <v>12.3</v>
       </c>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Key figure</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="C17" s="18">
-        <f>Assumptions!$C$6</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Market capitalisation (AED mn)</t>
-        </is>
-      </c>
-      <c r="C18" s="18">
-        <f>$C$14*C17</f>
+          <t>Shares outstanding (mn)</t>
+        </is>
+      </c>
+      <c r="C18" s="19">
+        <f>Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities, FY2025 (AED mn) — the only debt-like item</t>
-        </is>
-      </c>
-      <c r="C19" s="18">
-        <f>Assumptions!$C$83</f>
+          <t>Market capitalisation (AED mn)</t>
+        </is>
+      </c>
+      <c r="C19" s="19">
+        <f>$C$15*C18</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Cash and term deposits, FY2025 (AED mn)</t>
-        </is>
-      </c>
-      <c r="C20" s="18">
-        <f>Assumptions!$C$84</f>
+          <t>Lease liabilities, FY2025 (AED mn) — the only debt-like item</t>
+        </is>
+      </c>
+      <c r="C20" s="19">
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>FY2025 revenue (AED mn)</t>
-        </is>
-      </c>
-      <c r="C21" s="18">
-        <f>'Income Statement'!D5</f>
+          <t>Cash and term deposits, FY2025 (AED mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="19">
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>FY2025 EBITDA (AED mn)</t>
-        </is>
-      </c>
-      <c r="C22" s="18">
-        <f>'Income Statement'!D9</f>
+          <t>FY2025 revenue (AED mn)</t>
+        </is>
+      </c>
+      <c r="C22" s="19">
+        <f>'Income Statement'!D5</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net profit (AED mn)</t>
-        </is>
-      </c>
-      <c r="C23" s="18">
-        <f>'Income Statement'!D18</f>
+          <t>FY2025 EBITDA (AED mn)</t>
+        </is>
+      </c>
+      <c r="C23" s="19">
+        <f>'Income Statement'!D9</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — explicit window</t>
-        </is>
-      </c>
-      <c r="C24" s="16">
-        <f>DCF!C47</f>
+          <t>FY2025 net profit (AED mn)</t>
+        </is>
+      </c>
+      <c r="C24" s="19">
+        <f>'Income Statement'!D18</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — terminal</t>
-        </is>
-      </c>
-      <c r="C25" s="16">
-        <f>DCF!C54</f>
+          <t>Cost of capital — explicit window</t>
+        </is>
+      </c>
+      <c r="C25" s="17">
+        <f>DCF!C47</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t>Cost of capital — terminal</t>
+        </is>
+      </c>
+      <c r="C26" s="17">
+        <f>DCF!C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C26" s="16">
+      <c r="C27" s="17">
         <f>DCF!C24</f>
         <v/>
       </c>
@@ -5076,19 +5086,19 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="19">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the cash-flow lens itself, not an average of the four</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="20">
         <f>Summary!C9</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>THE CONTESTED JUDGEMENT — THE REQUIRED RETURN, BOTH WAYS</t>
         </is>
@@ -5141,7 +5151,7 @@
           <t>The judgement is worth (Framing 1 less Framing 2, per share)</t>
         </is>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="16">
         <f>C15-C18</f>
         <v/>
       </c>
@@ -5157,7 +5167,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>EXPERT PANEL</t>
         </is>
@@ -5254,18 +5264,18 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Panel median</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="13">
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="11">
         <f>MEDIAN(C24:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5296,7 +5306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5363,18 +5373,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Anchors</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5402,7 +5412,7 @@
           <t>Combined federal royalty + income tax rate (Framing A, audited FY2025)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="24" t="n">
         <v>0.4357</v>
       </c>
     </row>
@@ -5412,7 +5422,7 @@
           <t>Regulated revenue share (Framing B base, audited FY2023)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="24" t="n">
         <v>0.6899999999999999</v>
       </c>
     </row>
@@ -5422,7 +5432,7 @@
           <t>Framing B — royalty rate on regulated revenue</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="24" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5432,23 +5442,23 @@
           <t>Framing B — royalty rate on regulated profit</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="24" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>H1-2026 reviewed segment actuals — the base the FY2026 build chains off</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5531,18 +5541,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Unit build — mobile and fixed (subscribers x ARPU)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5594,19 +5604,19 @@
           <t>Blended mobile ARPU (AED/month)</t>
         </is>
       </c>
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="25" t="n">
         <v>63.4</v>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="25" t="n">
         <v>63.6</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="25" t="n">
         <v>63.8</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="25" t="n">
         <v>64</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="25" t="n">
         <v>64.2</v>
       </c>
     </row>
@@ -5638,19 +5648,19 @@
           <t>Wholesale revenue growth</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="24" t="n">
         <v>-0.008</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="24" t="n">
         <v>0.015</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="24" t="n">
         <v>0.02</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="24" t="n">
         <v>0.02</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="24" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -5660,35 +5670,35 @@
           <t>ICT and associated telecom revenue growth</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="24" t="n">
         <v>0.079</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="24" t="n">
         <v>0.11</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="24" t="n">
         <v>0.09</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="24" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Direct-cost stack — cost per unit, one escalator per driver class. CONTRIBUTION MARGIN IS NOT AN INPUT HERE: it is computed on the Segments sheet as what is left after each cost line is grown on its own physical driver.</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5696,7 +5706,7 @@
           <t>Mobile interconnect cost, H1-2026 actual (AED/subscriber/month)</t>
         </is>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="26" t="n">
         <v>16.81380811911785</v>
       </c>
     </row>
@@ -5706,7 +5716,7 @@
           <t>Mobile interconnect escalator (termination rates, OTT substitution)</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="24" t="n">
         <v>-0.015</v>
       </c>
     </row>
@@ -5716,7 +5726,7 @@
           <t>Mobile commission cost, H1-2026 actual (AED/subscriber/month)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="n">
+      <c r="C33" s="26" t="n">
         <v>6.306854895350471</v>
       </c>
     </row>
@@ -5726,7 +5736,7 @@
           <t>Mobile commission escalator (acquisition/retention cost)</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="24" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -5736,7 +5746,7 @@
           <t>Mobile devices and direct services, H1-2026 actual (AED/subscriber/month)</t>
         </is>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C35" s="26" t="n">
         <v>0.9565423514538555</v>
       </c>
     </row>
@@ -5746,7 +5756,7 @@
           <t>Mobile devices escalator (held flat — lumpy, no trend read into it)</t>
         </is>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5756,7 +5766,7 @@
           <t>Fixed capacity and direct cost, H1-2026 actual (AED/subscriber/month)</t>
         </is>
       </c>
-      <c r="C37" s="25" t="n">
+      <c r="C37" s="26" t="n">
         <v>68.35316655397791</v>
       </c>
     </row>
@@ -5766,7 +5776,7 @@
           <t>Fixed capacity escalator (held flat against an observed decline)</t>
         </is>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5776,7 +5786,7 @@
           <t>Wholesale direct cost / wholesale revenue (H1-2026 rate, held flat)</t>
         </is>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="24" t="n">
         <v>0.1558</v>
       </c>
     </row>
@@ -5786,7 +5796,7 @@
           <t>ICT direct cost / ICT revenue (H1-2026 rate, held flat)</t>
         </is>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="24" t="n">
         <v>0.7848000000000001</v>
       </c>
     </row>
@@ -5836,23 +5846,23 @@
           <t>Blended ARPU drift (mix-exhaustion sensitivity; zero in the base case)</t>
         </is>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Operating expense stack — one escalator per cost class</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="15" t="n"/>
-      <c r="D47" s="15" t="n"/>
-      <c r="E47" s="15" t="n"/>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
-      <c r="H47" s="15" t="n"/>
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="13" t="n"/>
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -5870,7 +5880,7 @@
           <t>Staff escalator (UAE wage inflation)</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" s="24" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -5890,7 +5900,7 @@
           <t>Network escalator (network scale)</t>
         </is>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="24" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -5910,7 +5920,7 @@
           <t>Administrative escalator (CPI)</t>
         </is>
       </c>
-      <c r="C53" s="9" t="n">
+      <c r="C53" s="24" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -5930,7 +5940,7 @@
           <t>Other-expense escalator (CPI)</t>
         </is>
       </c>
-      <c r="C55" s="9" t="n">
+      <c r="C55" s="24" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -5940,7 +5950,7 @@
           <t>Marketing / revenue</t>
         </is>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="C56" s="24" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -5950,7 +5960,7 @@
           <t>Telecom licence and related fees / revenue (regulatory revenue share)</t>
         </is>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C57" s="24" t="n">
         <v>0.027</v>
       </c>
     </row>
@@ -5960,7 +5970,7 @@
           <t>Expected credit losses / revenue</t>
         </is>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C58" s="24" t="n">
         <v>0.0145</v>
       </c>
     </row>
@@ -5975,18 +5985,18 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>Capital intensity and working capital</t>
         </is>
       </c>
-      <c r="B61" s="15" t="n"/>
-      <c r="C61" s="15" t="n"/>
-      <c r="D61" s="15" t="n"/>
-      <c r="E61" s="15" t="n"/>
-      <c r="F61" s="15" t="n"/>
-      <c r="G61" s="15" t="n"/>
-      <c r="H61" s="15" t="n"/>
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="13" t="n"/>
+      <c r="E61" s="13" t="n"/>
+      <c r="F61" s="13" t="n"/>
+      <c r="G61" s="13" t="n"/>
+      <c r="H61" s="13" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -5994,19 +6004,19 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="B62" s="9" t="n">
+      <c r="B62" s="24" t="n">
         <v>0.155</v>
       </c>
-      <c r="C62" s="9" t="n">
+      <c r="C62" s="24" t="n">
         <v>0.15</v>
       </c>
-      <c r="D62" s="9" t="n">
+      <c r="D62" s="24" t="n">
         <v>0.145</v>
       </c>
-      <c r="E62" s="9" t="n">
+      <c r="E62" s="24" t="n">
         <v>0.135</v>
       </c>
-      <c r="F62" s="9" t="n">
+      <c r="F62" s="24" t="n">
         <v>0.13</v>
       </c>
     </row>
@@ -6016,7 +6026,7 @@
           <t>Tangible share of capex (audited FY2025)</t>
         </is>
       </c>
-      <c r="C63" s="9" t="n">
+      <c r="C63" s="24" t="n">
         <v>0.866</v>
       </c>
     </row>
@@ -6026,7 +6036,7 @@
           <t>PP&amp;E depreciation rate on opening balance (audited FY2025)</t>
         </is>
       </c>
-      <c r="C64" s="9" t="n">
+      <c r="C64" s="24" t="n">
         <v>0.1583</v>
       </c>
     </row>
@@ -6036,7 +6046,7 @@
           <t>Intangibles amortisation rate on opening balance (audited FY2025)</t>
         </is>
       </c>
-      <c r="C65" s="9" t="n">
+      <c r="C65" s="24" t="n">
         <v>0.289</v>
       </c>
     </row>
@@ -6068,23 +6078,23 @@
           <t>Net working capital / revenue (audited FY2025 component days)</t>
         </is>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="C67" s="24" t="n">
         <v>-0.0667974774135183</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>Cost of capital</t>
         </is>
       </c>
-      <c r="B69" s="15" t="n"/>
-      <c r="C69" s="15" t="n"/>
-      <c r="D69" s="15" t="n"/>
-      <c r="E69" s="15" t="n"/>
-      <c r="F69" s="15" t="n"/>
-      <c r="G69" s="15" t="n"/>
-      <c r="H69" s="15" t="n"/>
+      <c r="B69" s="13" t="n"/>
+      <c r="C69" s="13" t="n"/>
+      <c r="D69" s="13" t="n"/>
+      <c r="E69" s="13" t="n"/>
+      <c r="F69" s="13" t="n"/>
+      <c r="G69" s="13" t="n"/>
+      <c r="H69" s="13" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -6092,7 +6102,7 @@
           <t>Risk-free rate — Jan-2031 AED T-bond (longest liquid AED tenor)</t>
         </is>
       </c>
-      <c r="C70" s="9" t="n">
+      <c r="C70" s="24" t="n">
         <v>0.0448</v>
       </c>
     </row>
@@ -6102,7 +6112,7 @@
           <t>UAE sovereign default spread (netted out; Aa2 rating basis)</t>
         </is>
       </c>
-      <c r="C71" s="9" t="n">
+      <c r="C71" s="24" t="n">
         <v>0.0004</v>
       </c>
     </row>
@@ -6112,7 +6122,7 @@
           <t>Equity risk premium (UAE total, rating basis)</t>
         </is>
       </c>
-      <c r="C72" s="9" t="n">
+      <c r="C72" s="24" t="n">
         <v>0.0429</v>
       </c>
     </row>
@@ -6122,7 +6132,7 @@
           <t>Beta (DU weekly vs FTSE ADX General, 5y)</t>
         </is>
       </c>
-      <c r="C73" s="26" t="n">
+      <c r="C73" s="27" t="n">
         <v>0.488</v>
       </c>
     </row>
@@ -6132,7 +6142,7 @@
           <t>Marginal cost of debt (AED sovereign + GCC telecom spread)</t>
         </is>
       </c>
-      <c r="C74" s="9" t="n">
+      <c r="C74" s="24" t="n">
         <v>0.051</v>
       </c>
     </row>
@@ -6142,19 +6152,19 @@
           <t>AED risk-free path (defines the glide)</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n">
+      <c r="B75" s="24" t="n">
         <v>0.0448</v>
       </c>
-      <c r="C75" s="9" t="n">
+      <c r="C75" s="24" t="n">
         <v>0.0444</v>
       </c>
-      <c r="D75" s="9" t="n">
+      <c r="D75" s="24" t="n">
         <v>0.0439</v>
       </c>
-      <c r="E75" s="9" t="n">
+      <c r="E75" s="24" t="n">
         <v>0.0435</v>
       </c>
-      <c r="F75" s="9" t="n">
+      <c r="F75" s="24" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -6164,7 +6174,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C76" s="9" t="n">
+      <c r="C76" s="24" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -6174,7 +6184,7 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C77" s="9" t="n">
+      <c r="C77" s="24" t="n">
         <v>0.0429</v>
       </c>
     </row>
@@ -6184,7 +6194,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C78" s="9" t="n">
+      <c r="C78" s="24" t="n">
         <v>0.049</v>
       </c>
     </row>
@@ -6194,7 +6204,7 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C79" s="9" t="n">
+      <c r="C79" s="24" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -6204,23 +6214,23 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C80" s="9" t="n">
+      <c r="C80" s="24" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="12" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>Balance-sheet and bridge anchors</t>
         </is>
       </c>
-      <c r="B82" s="15" t="n"/>
-      <c r="C82" s="15" t="n"/>
-      <c r="D82" s="15" t="n"/>
-      <c r="E82" s="15" t="n"/>
-      <c r="F82" s="15" t="n"/>
-      <c r="G82" s="15" t="n"/>
-      <c r="H82" s="15" t="n"/>
+      <c r="B82" s="13" t="n"/>
+      <c r="C82" s="13" t="n"/>
+      <c r="D82" s="13" t="n"/>
+      <c r="E82" s="13" t="n"/>
+      <c r="F82" s="13" t="n"/>
+      <c r="G82" s="13" t="n"/>
+      <c r="H82" s="13" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -6248,7 +6258,7 @@
           <t>Equity-accounted investees at carrying value (AED mn)</t>
         </is>
       </c>
-      <c r="C85" s="24" t="n">
+      <c r="C85" s="25" t="n">
         <v>0.511</v>
       </c>
     </row>
@@ -6258,7 +6268,7 @@
           <t>Forecast dividend payout ratio (FY2024 actual 98%, FY2025 ~100%)</t>
         </is>
       </c>
-      <c r="C86" s="9" t="n">
+      <c r="C86" s="24" t="n">
         <v>0.98</v>
       </c>
     </row>
@@ -6268,7 +6278,7 @@
           <t>Yield on cash and term deposits (audited FY2025 effective)</t>
         </is>
       </c>
-      <c r="C87" s="9" t="n">
+      <c r="C87" s="24" t="n">
         <v>0.033</v>
       </c>
     </row>
@@ -6278,7 +6288,7 @@
           <t>Lease interest rate (audited FY2025 effective)</t>
         </is>
       </c>
-      <c r="C88" s="9" t="n">
+      <c r="C88" s="24" t="n">
         <v>0.036</v>
       </c>
     </row>
@@ -6303,18 +6313,18 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>Lens inputs</t>
         </is>
       </c>
-      <c r="B92" s="15" t="n"/>
-      <c r="C92" s="15" t="n"/>
-      <c r="D92" s="15" t="n"/>
-      <c r="E92" s="15" t="n"/>
-      <c r="F92" s="15" t="n"/>
-      <c r="G92" s="15" t="n"/>
-      <c r="H92" s="15" t="n"/>
+      <c r="B92" s="13" t="n"/>
+      <c r="C92" s="13" t="n"/>
+      <c r="D92" s="13" t="n"/>
+      <c r="E92" s="13" t="n"/>
+      <c r="F92" s="13" t="n"/>
+      <c r="G92" s="13" t="n"/>
+      <c r="H92" s="13" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -6332,7 +6342,7 @@
           <t>Peer benchmark dividend yield</t>
         </is>
       </c>
-      <c r="C94" s="9" t="n">
+      <c r="C94" s="24" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -6342,48 +6352,8 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C95" s="9" t="n">
+      <c r="C95" s="24" t="n">
         <v>0.27</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="n">
-        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -6449,11 +6419,11 @@
           <t>Present value of the five forecast years</t>
         </is>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>DCF!C27</f>
         <v/>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="16">
         <f>C5/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6464,11 +6434,11 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>DCF!C28</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="16">
         <f>C6/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6479,11 +6449,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6494,11 +6464,11 @@
           <t>Less lease liabilities (the only debt-like item)</t>
         </is>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>-Assumptions!$C$83</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="16">
         <f>C8/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6509,11 +6479,11 @@
           <t>Plus cash and term deposits</t>
         </is>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>Assumptions!$C$84</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="16">
         <f>C9/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6524,27 +6494,27 @@
           <t>Plus equity-accounted investees at carrying value</t>
         </is>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>Assumptions!$C$85</f>
         <v/>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="16">
         <f>C10/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="29">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="30">
         <f>C7+C8+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>C11/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6555,7 +6525,7 @@
           <t>Terminal value as a share of enterprise value</t>
         </is>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <f>DCF!C29</f>
         <v/>
       </c>
@@ -6671,30 +6641,30 @@
       <c r="B5" s="23" t="n">
         <v>7074.936</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <f>B5/$B$9</f>
         <v/>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="24" t="n">
         <v>0.6082941244980873</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>Assumptions!$C$13+(Assumptions!$C$15+Assumptions!$B$23)/2*Assumptions!$B$25*6/1000</f>
         <v/>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <f>(Assumptions!$B$23+Assumptions!$C$23)/2*Assumptions!$C$25*(1+Assumptions!$C$45)^1*12/1000</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="32">
         <f>(Assumptions!$C$23+Assumptions!$D$23)/2*Assumptions!$D$25*(1+Assumptions!$C$45)^2*12/1000</f>
         <v/>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <f>(Assumptions!$D$23+Assumptions!$E$23)/2*Assumptions!$E$25*(1+Assumptions!$C$45)^3*12/1000</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="32">
         <f>(Assumptions!$E$23+Assumptions!$F$23)/2*Assumptions!$F$25*(1+Assumptions!$C$45)^4*12/1000</f>
         <v/>
       </c>
@@ -6708,30 +6678,30 @@
       <c r="B6" s="23" t="n">
         <v>4379.705</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <f>B6/$B$9</f>
         <v/>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="24" t="n">
         <v>0.858015094623953</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>Assumptions!$C$14+(Assumptions!$C$16+Assumptions!$B$24)/2*Assumptions!$B$26*6/1000</f>
         <v/>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>(Assumptions!$B$24+Assumptions!$C$24)/2*Assumptions!$C$26*(1+Assumptions!$C$45)^1*12/1000</f>
         <v/>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="32">
         <f>(Assumptions!$C$24+Assumptions!$D$24)/2*Assumptions!$D$26*(1+Assumptions!$C$45)^2*12/1000</f>
         <v/>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <f>(Assumptions!$D$24+Assumptions!$E$24)/2*Assumptions!$E$26*(1+Assumptions!$C$45)^3*12/1000</f>
         <v/>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="32">
         <f>(Assumptions!$E$24+Assumptions!$F$24)/2*Assumptions!$F$26*(1+Assumptions!$C$45)^4*12/1000</f>
         <v/>
       </c>
@@ -6745,30 +6715,30 @@
       <c r="B7" s="23" t="n">
         <v>2568.222</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <f>B7/$B$9</f>
         <v/>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="24" t="n">
         <v>0.8642060538380248</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>Assumptions!$C$17*(1+Assumptions!$B$27)</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>E7*(1+Assumptions!$C$27)</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>F7*(1+Assumptions!$D$27)</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>G7*(1+Assumptions!$E$27)</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="32">
         <f>H7*(1+Assumptions!$F$27)</f>
         <v/>
       </c>
@@ -6782,41 +6752,41 @@
       <c r="B8" s="23" t="n">
         <v>1882.558</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>B8/$B$9</f>
         <v/>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="24" t="n">
         <v>0.1939000020185301</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>Assumptions!$C$18*(1+Assumptions!$B$28)</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>E8*(1+Assumptions!$C$28)</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>F8*(1+Assumptions!$D$28)</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>G8*(1+Assumptions!$E$28)</f>
         <v/>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="32">
         <f>H8*(1+Assumptions!$F$28)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
@@ -6824,24 +6794,24 @@
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="32">
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="33">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="33">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="33">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="33">
         <f>SUM(I5:I8)</f>
         <v/>
       </c>
@@ -6884,23 +6854,23 @@
           <t>Mobile interconnect (AED per subscriber per month)</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^0</f>
         <v/>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^1</f>
         <v/>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^2</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^3</f>
         <v/>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>Assumptions!$C$31*(1+Assumptions!$C$32)^4</f>
         <v/>
       </c>
@@ -6911,23 +6881,23 @@
           <t>Mobile commission (AED per subscriber per month)</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^0</f>
         <v/>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^1</f>
         <v/>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^2</f>
         <v/>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^3</f>
         <v/>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="34">
         <f>Assumptions!$C$33*(1+Assumptions!$C$34)^4</f>
         <v/>
       </c>
@@ -6938,50 +6908,50 @@
           <t>Mobile devices and direct services (AED per subscriber per month)</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^0</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^1</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^2</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^3</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="34">
         <f>Assumptions!$C$35*(1+Assumptions!$C$36)^4</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Mobile — total direct cost per subscriber per month</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>B12+B13+B14</f>
         <v/>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>C12+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>D12+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>F12+F13+F14</f>
         <v/>
       </c>
@@ -6992,23 +6962,23 @@
           <t>Fixed capacity and direct cost (AED per subscriber per month)</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^0</f>
         <v/>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^1</f>
         <v/>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^2</f>
         <v/>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^3</f>
         <v/>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="34">
         <f>Assumptions!$C$37*(1+Assumptions!$C$38)^4</f>
         <v/>
       </c>
@@ -7019,23 +6989,23 @@
           <t>Wholesale direct cost / wholesale revenue (no disclosed unit — flagged)</t>
         </is>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="9">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
@@ -7046,23 +7016,23 @@
           <t>ICT direct cost / ICT revenue (no disclosed unit — flagged)</t>
         </is>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="9">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
@@ -7105,23 +7075,23 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="32">
         <f>Assumptions!$C$41+(Assumptions!$C$15+Assumptions!$B$23)/2*B15*6/1000</f>
         <v/>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>(Assumptions!$B$23+Assumptions!$C$23)/2*C15*12/1000</f>
         <v/>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <f>(Assumptions!$C$23+Assumptions!$D$23)/2*D15*12/1000</f>
         <v/>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <f>(Assumptions!$D$23+Assumptions!$E$23)/2*E15*12/1000</f>
         <v/>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <f>(Assumptions!$E$23+Assumptions!$F$23)/2*F15*12/1000</f>
         <v/>
       </c>
@@ -7132,23 +7102,23 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <f>Assumptions!$C$42+(Assumptions!$C$16+Assumptions!$B$24)/2*B16*6/1000</f>
         <v/>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>(Assumptions!$B$24+Assumptions!$C$24)/2*C16*12/1000</f>
         <v/>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <f>(Assumptions!$C$24+Assumptions!$D$24)/2*D16*12/1000</f>
         <v/>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <f>(Assumptions!$D$24+Assumptions!$E$24)/2*E16*12/1000</f>
         <v/>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <f>(Assumptions!$E$24+Assumptions!$F$24)/2*F16*12/1000</f>
         <v/>
       </c>
@@ -7159,23 +7129,23 @@
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="32">
         <f>Assumptions!$C$43+(E7-Assumptions!$C$19)*B17</f>
         <v/>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="32">
         <f>F7*C17</f>
         <v/>
       </c>
-      <c r="D23" s="31">
+      <c r="D23" s="32">
         <f>G7*D17</f>
         <v/>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="32">
         <f>H7*E17</f>
         <v/>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="32">
         <f>I7*F17</f>
         <v/>
       </c>
@@ -7186,50 +7156,50 @@
           <t>ICT and associated telecom services</t>
         </is>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <f>Assumptions!$C$44+(E8-Assumptions!$C$20)*B18</f>
         <v/>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <f>F8*C18</f>
         <v/>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <f>G8*D18</f>
         <v/>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <f>H8*E18</f>
         <v/>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <f>I8*F18</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Total direct cost</t>
         </is>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="33">
         <f>SUM(B21:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <f>SUM(C21:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <f>SUM(D21:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <f>SUM(E21:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <f>SUM(F21:F24)</f>
         <v/>
       </c>
@@ -7272,23 +7242,23 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <f>E5-B21</f>
         <v/>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <f>F5-C21</f>
         <v/>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <f>G5-D21</f>
         <v/>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <f>H5-E21</f>
         <v/>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <f>I5-F21</f>
         <v/>
       </c>
@@ -7299,23 +7269,23 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <f>E6-B22</f>
         <v/>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="32">
         <f>F6-C22</f>
         <v/>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="32">
         <f>G6-D22</f>
         <v/>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="32">
         <f>H6-E22</f>
         <v/>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="32">
         <f>I6-F22</f>
         <v/>
       </c>
@@ -7326,23 +7296,23 @@
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="32">
         <f>E7-B23</f>
         <v/>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="32">
         <f>F7-C23</f>
         <v/>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="32">
         <f>G7-D23</f>
         <v/>
       </c>
-      <c r="E30" s="31">
+      <c r="E30" s="32">
         <f>H7-E23</f>
         <v/>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="32">
         <f>I7-F23</f>
         <v/>
       </c>
@@ -7353,50 +7323,50 @@
           <t>ICT and associated telecom services</t>
         </is>
       </c>
-      <c r="B31" s="31">
+      <c r="B31" s="32">
         <f>E8-B24</f>
         <v/>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="32">
         <f>F8-C24</f>
         <v/>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="32">
         <f>G8-D24</f>
         <v/>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="32">
         <f>H8-E24</f>
         <v/>
       </c>
-      <c r="F31" s="31">
+      <c r="F31" s="32">
         <f>I8-F24</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Total contribution</t>
         </is>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="33">
         <f>SUM(B28:B31)</f>
         <v/>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="33">
         <f>SUM(C28:C31)</f>
         <v/>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="33">
         <f>SUM(D28:D31)</f>
         <v/>
       </c>
-      <c r="E32" s="32">
+      <c r="E32" s="33">
         <f>SUM(E28:E31)</f>
         <v/>
       </c>
-      <c r="F32" s="32">
+      <c r="F32" s="33">
         <f>SUM(F28:F31)</f>
         <v/>
       </c>
@@ -7439,23 +7409,23 @@
           <t>Mobile</t>
         </is>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="9">
         <f>B28/E5</f>
         <v/>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="9">
         <f>C28/F5</f>
         <v/>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="9">
         <f>D28/G5</f>
         <v/>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="9">
         <f>E28/H5</f>
         <v/>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="9">
         <f>F28/I5</f>
         <v/>
       </c>
@@ -7466,23 +7436,23 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="9">
         <f>B29/E6</f>
         <v/>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="9">
         <f>C29/F6</f>
         <v/>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="9">
         <f>D29/G6</f>
         <v/>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="9">
         <f>E29/H6</f>
         <v/>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="9">
         <f>F29/I6</f>
         <v/>
       </c>
@@ -7493,23 +7463,23 @@
           <t>Wholesale</t>
         </is>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="9">
         <f>B30/E7</f>
         <v/>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="9">
         <f>C30/F7</f>
         <v/>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="9">
         <f>D30/G7</f>
         <v/>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="9">
         <f>E30/H7</f>
         <v/>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="9">
         <f>F30/I7</f>
         <v/>
       </c>
@@ -7520,29 +7490,29 @@
           <t>ICT and associated telecom services</t>
         </is>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="9">
         <f>B31/E8</f>
         <v/>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="9">
         <f>C31/F8</f>
         <v/>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="9">
         <f>D31/G8</f>
         <v/>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="9">
         <f>E31/H8</f>
         <v/>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="9">
         <f>F31/I8</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Group gross margin</t>
         </is>
@@ -7606,23 +7576,23 @@
           <t>Staff (wage escalator)</t>
         </is>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^0</f>
         <v/>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^1</f>
         <v/>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^2</f>
         <v/>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^3</f>
         <v/>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <f>Assumptions!$C$48*(1+Assumptions!$C$49)^4</f>
         <v/>
       </c>
@@ -7633,23 +7603,23 @@
           <t>Network &amp; maintenance (network-scale escalator)</t>
         </is>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^1</f>
         <v/>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^2</f>
         <v/>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^3</f>
         <v/>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^4</f>
         <v/>
       </c>
-      <c r="F43" s="31">
+      <c r="F43" s="32">
         <f>Assumptions!$C$50*(1+Assumptions!$C$51)^5</f>
         <v/>
       </c>
@@ -7660,23 +7630,23 @@
           <t>Marketing (% of revenue)</t>
         </is>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="32">
         <f>E9*Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <f>F9*Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <f>G9*Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <f>H9*Assumptions!$C$56</f>
         <v/>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <f>I9*Assumptions!$C$56</f>
         <v/>
       </c>
@@ -7687,23 +7657,23 @@
           <t>Telecom licence and related fees (% of revenue)</t>
         </is>
       </c>
-      <c r="B45" s="31">
+      <c r="B45" s="32">
         <f>E9*Assumptions!$C$57</f>
         <v/>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <f>F9*Assumptions!$C$57</f>
         <v/>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <f>G9*Assumptions!$C$57</f>
         <v/>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <f>H9*Assumptions!$C$57</f>
         <v/>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <f>I9*Assumptions!$C$57</f>
         <v/>
       </c>
@@ -7714,23 +7684,23 @@
           <t>Administrative (CPI escalator)</t>
         </is>
       </c>
-      <c r="B46" s="31">
+      <c r="B46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^1</f>
         <v/>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^2</f>
         <v/>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^3</f>
         <v/>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^4</f>
         <v/>
       </c>
-      <c r="F46" s="31">
+      <c r="F46" s="32">
         <f>Assumptions!$C$52*(1+Assumptions!$C$53)^5</f>
         <v/>
       </c>
@@ -7741,23 +7711,23 @@
           <t>Other operating expense (CPI escalator)</t>
         </is>
       </c>
-      <c r="B47" s="31">
+      <c r="B47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^1</f>
         <v/>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^2</f>
         <v/>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^3</f>
         <v/>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^4</f>
         <v/>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <f>Assumptions!$C$54*(1+Assumptions!$C$55)^5</f>
         <v/>
       </c>
@@ -7768,23 +7738,23 @@
           <t>Expected credit losses (% of revenue)</t>
         </is>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="32">
         <f>E9*Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <f>F9*Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="32">
         <f>G9*Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="32">
         <f>H9*Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="32">
         <f>I9*Assumptions!$C$58</f>
         <v/>
       </c>
@@ -7795,77 +7765,77 @@
           <t>Less other operating income</t>
         </is>
       </c>
-      <c r="B49" s="31">
+      <c r="B49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="D49" s="31">
+      <c r="D49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="F49" s="31">
+      <c r="F49" s="32">
         <f>-Assumptions!$C$59</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Total operating expenses before D&amp;A</t>
         </is>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="33">
         <f>SUM(B42:B49)</f>
         <v/>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <f>SUM(C42:C49)</f>
         <v/>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <f>SUM(D42:D49)</f>
         <v/>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <f>SUM(E42:E49)</f>
         <v/>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="33">
         <f>SUM(F42:F49)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Group EBITDA (contribution less the opex stack)</t>
         </is>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="33">
         <f>B32-B50</f>
         <v/>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="33">
         <f>C32-C50</f>
         <v/>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="33">
         <f>D32-D50</f>
         <v/>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="33">
         <f>E32-E50</f>
         <v/>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="33">
         <f>F32-F50</f>
         <v/>
       </c>
@@ -7876,23 +7846,23 @@
           <t>Group EBITDA margin</t>
         </is>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="9">
         <f>B51/E$9</f>
         <v/>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="9">
         <f>C51/F$9</f>
         <v/>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="9">
         <f>D51/G$9</f>
         <v/>
       </c>
-      <c r="E52" s="11">
+      <c r="E52" s="9">
         <f>E51/H$9</f>
         <v/>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="9">
         <f>F51/I$9</f>
         <v/>
       </c>
@@ -7935,23 +7905,23 @@
           <t>Mobile subscribers, end of year ('000)</t>
         </is>
       </c>
-      <c r="B55" s="31">
+      <c r="B55" s="32">
         <f>Assumptions!$B$23</f>
         <v/>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="32">
         <f>Assumptions!$C$23</f>
         <v/>
       </c>
-      <c r="D55" s="31">
+      <c r="D55" s="32">
         <f>Assumptions!$D$23</f>
         <v/>
       </c>
-      <c r="E55" s="31">
+      <c r="E55" s="32">
         <f>Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="F55" s="31">
+      <c r="F55" s="32">
         <f>Assumptions!$F$23</f>
         <v/>
       </c>
@@ -7962,23 +7932,23 @@
           <t>Average mobile base ('000) — (prior end + end)/2</t>
         </is>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="32">
         <f>(9280+Assumptions!$B$23)/2</f>
         <v/>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <f>(Assumptions!$B$23+Assumptions!$C$23)/2</f>
         <v/>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <f>(Assumptions!$C$23+Assumptions!$D$23)/2</f>
         <v/>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <f>(Assumptions!$D$23+Assumptions!$E$23)/2</f>
         <v/>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <f>(Assumptions!$E$23+Assumptions!$F$23)/2</f>
         <v/>
       </c>
@@ -7989,23 +7959,23 @@
           <t>Blended mobile ARPU (AED/month)</t>
         </is>
       </c>
-      <c r="B57" s="35">
+      <c r="B57" s="36">
         <f>Assumptions!$B$25</f>
         <v/>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="36">
         <f>Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="D57" s="35">
+      <c r="D57" s="36">
         <f>Assumptions!$D$25</f>
         <v/>
       </c>
-      <c r="E57" s="35">
+      <c r="E57" s="36">
         <f>Assumptions!$E$25</f>
         <v/>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="36">
         <f>Assumptions!$F$25</f>
         <v/>
       </c>
@@ -8016,24 +7986,24 @@
           <t>Unit-implied mobile revenue — average base x ARPU x 12 (FY2026 is H1 actual + unit-built H2, so the check applies from FY2027)</t>
         </is>
       </c>
-      <c r="B58" s="31" t="inlineStr">
+      <c r="B58" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="32">
         <f>C56*C57*12/1000</f>
         <v/>
       </c>
-      <c r="D58" s="31">
+      <c r="D58" s="32">
         <f>D56*D57*12/1000</f>
         <v/>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="32">
         <f>E56*E57*12/1000</f>
         <v/>
       </c>
-      <c r="F58" s="31">
+      <c r="F58" s="32">
         <f>F56*F57*12/1000</f>
         <v/>
       </c>
@@ -8044,23 +8014,23 @@
           <t>Pasted mobile segment revenue (the build output above)</t>
         </is>
       </c>
-      <c r="B59" s="18">
+      <c r="B59" s="19">
         <f>E5</f>
         <v/>
       </c>
-      <c r="C59" s="18">
+      <c r="C59" s="19">
         <f>F5</f>
         <v/>
       </c>
-      <c r="D59" s="18">
+      <c r="D59" s="19">
         <f>G5</f>
         <v/>
       </c>
-      <c r="E59" s="18">
+      <c r="E59" s="19">
         <f>H5</f>
         <v/>
       </c>
-      <c r="F59" s="18">
+      <c r="F59" s="19">
         <f>I5</f>
         <v/>
       </c>
@@ -8071,24 +8041,24 @@
           <t>Check — unit-implied less pasted</t>
         </is>
       </c>
-      <c r="B60" s="31" t="inlineStr">
+      <c r="B60" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="35">
+      <c r="C60" s="36">
         <f>C58-C59</f>
         <v/>
       </c>
-      <c r="D60" s="35">
+      <c r="D60" s="36">
         <f>D58-D59</f>
         <v/>
       </c>
-      <c r="E60" s="35">
+      <c r="E60" s="36">
         <f>E58-E59</f>
         <v/>
       </c>
-      <c r="F60" s="35">
+      <c r="F60" s="36">
         <f>F58-F59</f>
         <v/>
       </c>
@@ -8164,7 +8134,7 @@
           <t>Justified price / earnings (GCC peer median)</t>
         </is>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="37">
         <f>Assumptions!$C$93</f>
         <v/>
       </c>
@@ -8175,7 +8145,7 @@
           <t>Implied value at 31-Dec-2025 (AED)</t>
         </is>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="16">
         <f>C5*C6</f>
         <v/>
       </c>
@@ -8186,7 +8156,7 @@
           <t>Anchor accretion factor</t>
         </is>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="38">
         <f>DCF!C62</f>
         <v/>
       </c>
@@ -8206,13 +8176,13 @@
       <c r="A10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Implied value per share at the anchor (AED)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="30">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="31">
         <f>C7*C8-C9</f>
         <v/>
       </c>
@@ -8223,11 +8193,11 @@
           <t>Bear at 12.0x (C) / bull at 18.5x (D), same construction</t>
         </is>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="16">
         <f>C5*12*C8-C9</f>
         <v/>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="16">
         <f>C5*18.5*C8-C9</f>
         <v/>
       </c>
@@ -8238,7 +8208,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="37">
         <f>Assumptions!$C$5/'Income Statement'!D19</f>
         <v/>
       </c>
@@ -8249,7 +8219,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$83-Assumptions!$C$84)/'Income Statement'!D9</f>
         <v/>
       </c>
@@ -8271,7 +8241,7 @@
           <t>Peer benchmark dividend yield</t>
         </is>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="9">
         <f>Assumptions!$C$94</f>
         <v/>
       </c>
@@ -8282,7 +8252,7 @@
           <t>Implied value from the yield cross (AED)</t>
         </is>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="16">
         <f>C15/C16</f>
         <v/>
       </c>
@@ -8305,7 +8275,7 @@
           <t>Current-scale revenue (FY2026E, AED mn)</t>
         </is>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <f>DCF!B5</f>
         <v/>
       </c>
@@ -8316,7 +8286,7 @@
           <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="17">
         <f>DCF!D7</f>
         <v/>
       </c>
@@ -8327,7 +8297,7 @@
           <t>Normalised EBITDA (AED mn)</t>
         </is>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>C20*C21</f>
         <v/>
       </c>
@@ -8338,7 +8308,7 @@
           <t>Normalised EBIT (AED mn) — less FY2026E depreciation and amortisation</t>
         </is>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="19">
         <f>C22+'Income Statement'!E11</f>
         <v/>
       </c>
@@ -8349,7 +8319,7 @@
           <t>Net finance income (FY2026E, AED mn)</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="19">
         <f>'Income Statement'!E13+'Income Statement'!E14</f>
         <v/>
       </c>
@@ -8360,7 +8330,7 @@
           <t>Normalised net profit (AED mn)</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <f>(C23+C24)*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -8371,19 +8341,19 @@
           <t>Normalised earnings per share (AED)</t>
         </is>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="16">
         <f>C25/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Implied value per share at the anchor (AED)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="30">
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="31">
         <f>C26*Assumptions!$C$93*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
@@ -8392,11 +8362,11 @@
           <t>bear 12.0x (E) / bull 18.5x (F):</t>
         </is>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="16">
         <f>C26*12*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="16">
         <f>C26*18.5*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
@@ -8430,7 +8400,7 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="9">
         <f>Assumptions!$C$95</f>
         <v/>
       </c>
@@ -8441,7 +8411,7 @@
           <t>Trailing return on equity</t>
         </is>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="17">
         <f>'Income Statement'!D18/(('Balance Sheet'!C14+'Balance Sheet'!D14)/2)</f>
         <v/>
       </c>
@@ -8452,7 +8422,7 @@
           <t>Perpetual (terminal) cost of equity — a steady-state multiple takes a steady-state rate</t>
         </is>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="17">
         <f>DCF!C50</f>
         <v/>
       </c>
@@ -8463,19 +8433,19 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="39">
         <f>(C31-Assumptions!$C$80)/(C33-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Implied value per share at the anchor (AED)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="30">
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="31">
         <f>C30*C34*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
@@ -8484,11 +8454,11 @@
           <t>bear / bull constructions (E / F):</t>
         </is>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="16">
         <f>((Assumptions!$C$95-Assumptions!$C$80)/((DCF!C40+DCF!C50)/2+0.01-Assumptions!$C$80))*C30*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="16">
         <f>((Assumptions!$C$95+0.02-Assumptions!$C$80)/(DCF!C50-Assumptions!$C$80))*C30*DCF!$C$62-Assumptions!$C$89</f>
         <v/>
       </c>
@@ -8573,23 +8543,23 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>Segments!E9</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>Segments!F9</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>Segments!G9</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>Segments!H9</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>Segments!I9</f>
         <v/>
       </c>
@@ -8600,23 +8570,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>Segments!B51</f>
         <v/>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>Segments!C51</f>
         <v/>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <f>Segments!D51</f>
         <v/>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>Segments!E51</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="19">
         <f>Segments!F51</f>
         <v/>
       </c>
@@ -8627,23 +8597,23 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <f>B6/B5</f>
         <v/>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <f>F6/F5</f>
         <v/>
       </c>
@@ -8654,50 +8624,50 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <f>'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="19">
         <f>'Income Statement'!I11</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -8708,23 +8678,23 @@
           <t>NOPAT — EBIT x (1 - 43.6% combined royalty and tax)</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <f>B9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>C9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>D9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>E9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>F9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -8735,23 +8705,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>-F8</f>
         <v/>
       </c>
@@ -8762,23 +8732,23 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="32">
         <f>-B5*Assumptions!$B$62</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>-C5*Assumptions!$C$62</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>-D5*Assumptions!$D$62</f>
         <v/>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>-E5*Assumptions!$E$62</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>-F5*Assumptions!$F$62</f>
         <v/>
       </c>
@@ -8789,23 +8759,23 @@
           <t>Memo — lease replacement at right-of-use depreciation, NOT deducted (leases are debt)</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>Assumptions!$B$66</f>
         <v/>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>Assumptions!$C$66</f>
         <v/>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>Assumptions!$D$66</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>Assumptions!$E$66</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>Assumptions!$F$66</f>
         <v/>
       </c>
@@ -8816,50 +8786,50 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>-(B5*Assumptions!$C$67-'Balance Sheet'!D11)</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>-(C5-B5)*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>-(D5-C5)*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>-(E5-D5)*Assumptions!$C$67</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>-(F5-E5)*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <f>B10+B11+B12+B14</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>C10+C11+C12+C14</f>
         <v/>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>D10+D11+D12+D14</f>
         <v/>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>E10+E11+E12+E14</f>
         <v/>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>F10+F11+F12+F14</f>
         <v/>
       </c>
@@ -8870,23 +8840,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B16" s="39">
+      <c r="B16" s="40">
         <f>$C$47-($C$47-$C$54)*B58</f>
         <v/>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="40">
         <f>$C$47-($C$47-$C$54)*C58</f>
         <v/>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="40">
         <f>$C$47-($C$47-$C$54)*D58</f>
         <v/>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="40">
         <f>$C$47-($C$47-$C$54)*E58</f>
         <v/>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="40">
         <f>$C$47-($C$47-$C$54)*F58</f>
         <v/>
       </c>
@@ -8897,56 +8867,56 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="41">
         <f>1/(1+B16)</f>
         <v/>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="41">
         <f>B17/(1+C16)</f>
         <v/>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="41">
         <f>C17/(1+D16)</f>
         <v/>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="41">
         <f>D17/(1+E16)</f>
         <v/>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="41">
         <f>E17/(1+F16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <f>B15*B17</f>
         <v/>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>C15*C17</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>D15*D17</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>E15*E17</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <f>F15*F17</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>TERMINAL VALUE, BRIDGE AND THE ANCHOR ROLL</t>
         </is>
@@ -8958,7 +8928,7 @@
           <t>Terminal-year NOPAT grown one year (AED mn)</t>
         </is>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>F10*(1+C24)</f>
         <v/>
       </c>
@@ -8969,7 +8939,7 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <f>F10*(1+C24)/'Summary Financials'!I13</f>
         <v/>
       </c>
@@ -8980,7 +8950,7 @@
           <t>Required reinvestment rate (g / return on capital)</t>
         </is>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="9">
         <f>C24/C22</f>
         <v/>
       </c>
@@ -8991,7 +8961,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="17">
         <f>Assumptions!$C$80</f>
         <v/>
       </c>
@@ -9002,7 +8972,7 @@
           <t>Terminal cost of capital</t>
         </is>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="9">
         <f>C54</f>
         <v/>
       </c>
@@ -9013,7 +8983,7 @@
           <t>Terminal value — terminal-year NOPAT C21 x (1−C23), capitalised (AED mn)</t>
         </is>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="32">
         <f>C21*(1-C23)/(C25-C24)</f>
         <v/>
       </c>
@@ -9024,7 +8994,7 @@
           <t>Present value of the five forecast years (AED mn)</t>
         </is>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <f>SUM(B18:F18)</f>
         <v/>
       </c>
@@ -9035,7 +9005,7 @@
           <t>Present value of the terminal value (AED mn)</t>
         </is>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <f>C26*F17</f>
         <v/>
       </c>
@@ -9046,7 +9016,7 @@
           <t>Terminal value as a share of enterprise value</t>
         </is>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="9">
         <f>C28/(C27+C28)</f>
         <v/>
       </c>
@@ -9057,7 +9027,7 @@
           <t>Enterprise value (AED mn)</t>
         </is>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="32">
         <f>C27+C28</f>
         <v/>
       </c>
@@ -9068,26 +9038,26 @@
           <t>Equity value (AED mn)</t>
         </is>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="19">
         <f>'SOTP Bridge'!C11</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Fair value per share at 31-Dec-2025 (AED)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="30">
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="31">
         <f>C31/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D32" s="15" t="n"/>
+      <c r="D32" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>COST OF CAPITAL — BUILT HERE, NOT ASSUMED</t>
         </is>
@@ -9099,7 +9069,7 @@
           <t>Risk-free rate — Jan-2031 AED T-bond (longest liquid AED tenor)</t>
         </is>
       </c>
-      <c r="C35" s="41">
+      <c r="C35" s="42">
         <f>Assumptions!$C$70</f>
         <v/>
       </c>
@@ -9110,7 +9080,7 @@
           <t>Less UAE sovereign default spread (removed to avoid double-counting)</t>
         </is>
       </c>
-      <c r="C36" s="41">
+      <c r="C36" s="42">
         <f>Assumptions!$C$71</f>
         <v/>
       </c>
@@ -9121,7 +9091,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="40">
         <f>C35-C36</f>
         <v/>
       </c>
@@ -9132,7 +9102,7 @@
           <t>Beta (DU weekly vs the FTSE ADX General, 5 years)</t>
         </is>
       </c>
-      <c r="C38" s="42">
+      <c r="C38" s="43">
         <f>Assumptions!$C$73</f>
         <v/>
       </c>
@@ -9143,7 +9113,7 @@
           <t>Equity risk premium (UAE total, rating basis)</t>
         </is>
       </c>
-      <c r="C39" s="41">
+      <c r="C39" s="42">
         <f>Assumptions!$C$72</f>
         <v/>
       </c>
@@ -9154,7 +9124,7 @@
           <t>Cost of equity, explicit window</t>
         </is>
       </c>
-      <c r="C40" s="39">
+      <c r="C40" s="40">
         <f>C37+C38*C39</f>
         <v/>
       </c>
@@ -9165,7 +9135,7 @@
           <t>Marginal cost of debt (AED sovereign + GCC telecom spread)</t>
         </is>
       </c>
-      <c r="C41" s="41">
+      <c r="C41" s="42">
         <f>Assumptions!$C$74</f>
         <v/>
       </c>
@@ -9176,7 +9146,7 @@
           <t>Cost of debt after tax (interest shields both fiscal legs)</t>
         </is>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="40">
         <f>C41*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -9187,7 +9157,7 @@
           <t>Market capitalisation (AED mn)</t>
         </is>
       </c>
-      <c r="C43" s="18">
+      <c r="C43" s="19">
         <f>Assumptions!$C$5*Assumptions!$C$6</f>
         <v/>
       </c>
@@ -9198,7 +9168,7 @@
           <t>Lease liabilities — the only debt-like item (AED mn)</t>
         </is>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="19">
         <f>Assumptions!$C$83</f>
         <v/>
       </c>
@@ -9209,7 +9179,7 @@
           <t>Debt weight (leases / (leases + market capitalisation))</t>
         </is>
       </c>
-      <c r="C45" s="39">
+      <c r="C45" s="40">
         <f>C44/(C44+C43)</f>
         <v/>
       </c>
@@ -9220,23 +9190,23 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C46" s="39">
+      <c r="C46" s="40">
         <f>1-C45</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Cost of capital, explicit window</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="43">
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="44">
         <f>C46*C40+C45*C42</f>
         <v/>
       </c>
-      <c r="D47" s="15" t="n"/>
+      <c r="D47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -9244,7 +9214,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C48" s="41">
+      <c r="C48" s="42">
         <f>Assumptions!$C$76</f>
         <v/>
       </c>
@@ -9255,7 +9225,7 @@
           <t>Terminal risk-free net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C49" s="39">
+      <c r="C49" s="40">
         <f>C48-C36</f>
         <v/>
       </c>
@@ -9266,7 +9236,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C50" s="39">
+      <c r="C50" s="40">
         <f>C49+C38*Assumptions!$C$77</f>
         <v/>
       </c>
@@ -9277,7 +9247,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C51" s="41">
+      <c r="C51" s="42">
         <f>Assumptions!$C$78</f>
         <v/>
       </c>
@@ -9288,7 +9258,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C52" s="39">
+      <c r="C52" s="40">
         <f>C51*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -9299,23 +9269,23 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C53" s="41">
+      <c r="C53" s="42">
         <f>Assumptions!$C$79</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>Terminal cost of capital</t>
         </is>
       </c>
-      <c r="B54" s="15" t="n"/>
-      <c r="C54" s="43">
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="44">
         <f>(1-C53)*C50+C53*C52</f>
         <v/>
       </c>
-      <c r="D54" s="15" t="n"/>
+      <c r="D54" s="13" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -9355,23 +9325,23 @@
           <t>AED risk-free path</t>
         </is>
       </c>
-      <c r="B57" s="41">
+      <c r="B57" s="42">
         <f>Assumptions!$B$75</f>
         <v/>
       </c>
-      <c r="C57" s="41">
+      <c r="C57" s="42">
         <f>Assumptions!$C$75</f>
         <v/>
       </c>
-      <c r="D57" s="41">
+      <c r="D57" s="42">
         <f>Assumptions!$D$75</f>
         <v/>
       </c>
-      <c r="E57" s="41">
+      <c r="E57" s="42">
         <f>Assumptions!$E$75</f>
         <v/>
       </c>
-      <c r="F57" s="41">
+      <c r="F57" s="42">
         <f>Assumptions!$F$75</f>
         <v/>
       </c>
@@ -9382,23 +9352,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B58" s="39">
+      <c r="B58" s="40">
         <f>($B$57-B57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="C58" s="39">
+      <c r="C58" s="40">
         <f>($B$57-C57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="D58" s="39">
+      <c r="D58" s="40">
         <f>($B$57-D57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="E58" s="39">
+      <c r="E58" s="40">
         <f>($B$57-E57)/($B$57-$F$57)</f>
         <v/>
       </c>
-      <c r="F58" s="39">
+      <c r="F58" s="40">
         <f>($B$57-F57)/($B$57-$F$57)</f>
         <v/>
       </c>
@@ -9411,7 +9381,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>THE ANCHOR ROLL — one date, one price of time</t>
         </is>
@@ -9423,23 +9393,23 @@
           <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
         </is>
       </c>
-      <c r="C62" s="40">
+      <c r="C62" s="41">
         <f>(1+C40)^(Assumptions!$C$90/365)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>Fair value per share at the 07-Aug-2026 anchor (AED)</t>
         </is>
       </c>
-      <c r="B63" s="15" t="n"/>
-      <c r="C63" s="30">
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="31">
         <f>C32*C62-Assumptions!$C$89</f>
         <v/>
       </c>
-      <c r="D63" s="15" t="n"/>
+      <c r="D63" s="13" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -9544,37 +9514,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="30" t="n">
         <v>13636.34</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>14635.917</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>15905.421</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="30">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="30">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="30">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -9585,7 +9555,7 @@
           <t>Direct costs (interconnect, commissions, devices)</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9596,23 +9566,23 @@
       <c r="D6" s="23" t="n">
         <v>-5259.425</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>-(DCF!B5-Segments!B32)</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="19">
         <f>-(DCF!C5-Segments!C32)</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="19">
         <f>-(DCF!D5-Segments!D32)</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="19">
         <f>-(DCF!E5-Segments!E32)</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="19">
         <f>-(DCF!F5-Segments!F32)</f>
         <v/>
       </c>
@@ -9623,36 +9593,36 @@
           <t>Segment contribution</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>F5+F6</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>G5+G6</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>H5+H6</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="32">
         <f>I5+I6</f>
         <v/>
       </c>
@@ -9663,7 +9633,7 @@
           <t>Operating expenses before D&amp;A</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9674,61 +9644,61 @@
       <c r="D8" s="23" t="n">
         <v>-3307.608</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>-Segments!B50</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="19">
         <f>-Segments!C50</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="19">
         <f>-Segments!D50</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="19">
         <f>-Segments!E50</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="19">
         <f>-Segments!F50</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="30" t="n">
         <v>5799.601</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="30">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="30">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -9739,35 +9709,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <f>B9/B5</f>
         <v/>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <f>C9/C5</f>
         <v/>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <f>D9/D5</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <f>E9/E5</f>
         <v/>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <f>F9/F5</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <f>G9/G5</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="9">
         <f>H9/H5</f>
         <v/>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <f>I9/I5</f>
         <v/>
       </c>
@@ -9787,62 +9757,62 @@
       <c r="D11" s="23" t="n">
         <v>-2167.933</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>-('Balance Sheet'!E6+'Balance Sheet'!E9+Assumptions!$B$66)</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>-('Balance Sheet'!F6+'Balance Sheet'!F9+Assumptions!$C$66)</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="32">
         <f>-('Balance Sheet'!G6+'Balance Sheet'!G9+Assumptions!$D$66)</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>-('Balance Sheet'!H6+'Balance Sheet'!H9+Assumptions!$E$66)</f>
         <v/>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="32">
         <f>-('Balance Sheet'!I6+'Balance Sheet'!I9+Assumptions!$F$66)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <f>B9+B11</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>C9+C11</f>
         <v/>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>D9+D11</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>E9+E11</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>F9+F11</f>
         <v/>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="30">
         <f>G9+G11</f>
         <v/>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="30">
         <f>H9+H11</f>
         <v/>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="30">
         <f>I9+I11</f>
         <v/>
       </c>
@@ -9862,23 +9832,23 @@
       <c r="D13" s="23" t="n">
         <v>74.672</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!D12,0)</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!E12,0)</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!F12,0)</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!G12,0)</f>
         <v/>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="32">
         <f>Assumptions!$C$87*MAX('Balance Sheet'!H12,0)</f>
         <v/>
       </c>
@@ -9898,23 +9868,23 @@
       <c r="D14" s="23" t="n">
         <v>-95.054</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!E13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!F13</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!G13</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!H13</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>-Assumptions!$C$88*'Balance Sheet'!I13</f>
         <v/>
       </c>
@@ -9936,37 +9906,37 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Profit before federal royalty and income tax</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="30" t="n">
         <v>3558.501</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="30" t="n">
         <v>4306.151</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="30" t="n">
         <v>5149.122</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <f>E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <f>F12+F13+F14</f>
         <v/>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <f>G12+G13+G14</f>
         <v/>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="30">
         <f>H12+H13+H14</f>
         <v/>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="30">
         <f>I12+I13+I14</f>
         <v/>
       </c>
@@ -9986,62 +9956,62 @@
       <c r="D17" s="23" t="n">
         <v>-2244.037</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>-E16*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>-F16*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>-G16*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>-H16*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="32">
         <f>-I16*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Net profit</t>
         </is>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <f>B16+B17</f>
         <v/>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="30">
         <f>G16+G17</f>
         <v/>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="30">
         <f>H16+H17</f>
         <v/>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="30">
         <f>I16+I17</f>
         <v/>
       </c>
@@ -10052,35 +10022,35 @@
           <t>Earnings per share (AED)</t>
         </is>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="16">
         <f>B18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="16">
         <f>C18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="16">
         <f>D18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="16">
         <f>E18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="16">
         <f>F18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="16">
         <f>G18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="16">
         <f>H18/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="16">
         <f>I18/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -10100,23 +10070,23 @@
       <c r="D20" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="16">
         <f>E19*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="16">
         <f>F19*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="16">
         <f>G19*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="16">
         <f>H19*Assumptions!$C$86</f>
         <v/>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="16">
         <f>I19*Assumptions!$C$86</f>
         <v/>
       </c>

--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -169,8 +169,8 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -983,7 +983,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>at full-year END-of-period factors, gliding 6.41% -&gt; 6.17% on the AED risk-free path (du has no debt whose cost could</t>
+          <t>at full-year END-of-period factors, gliding 6.40% -&gt; 6.17% on the AED risk-free path (du has no debt whose cost could</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Currency. AED million unless stated. Spot AED 12.30 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
+          <t>Currency. AED million unless stated. Spot AED 11.36 (2026-08-07 close). Sheets: READ FIRST · Summary ·</t>
         </is>
       </c>
     </row>
@@ -1418,23 +1418,23 @@
         <v>2249.719</v>
       </c>
       <c r="E12" s="32">
-        <f>D12+'Income Statement'!E18-'Income Statement'!E11+DCF!B12+DCF!B14-'Income Statement'!E18*Assumptions!$C$86</f>
+        <f>D12+'Income Statement'!E18-'Income Statement'!E11+DCF!B12+DCF!B14-'Income Statement'!E18*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="F12" s="32">
-        <f>E12+'Income Statement'!F18-'Income Statement'!F11+DCF!C12+DCF!C14-'Income Statement'!F18*Assumptions!$C$86</f>
+        <f>E12+'Income Statement'!F18-'Income Statement'!F11+DCF!C12+DCF!C14-'Income Statement'!F18*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="G12" s="32">
-        <f>F12+'Income Statement'!G18-'Income Statement'!G11+DCF!D12+DCF!D14-'Income Statement'!G18*Assumptions!$C$86</f>
+        <f>F12+'Income Statement'!G18-'Income Statement'!G11+DCF!D12+DCF!D14-'Income Statement'!G18*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="H12" s="32">
-        <f>G12+'Income Statement'!H18-'Income Statement'!H11+DCF!E12+DCF!E14-'Income Statement'!H18*Assumptions!$C$86</f>
+        <f>G12+'Income Statement'!H18-'Income Statement'!H11+DCF!E12+DCF!E14-'Income Statement'!H18*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="I12" s="32">
-        <f>H12+'Income Statement'!I18-'Income Statement'!I11+DCF!F12+DCF!F14-'Income Statement'!I18*Assumptions!$C$86</f>
+        <f>H12+'Income Statement'!I18-'Income Statement'!I11+DCF!F12+DCF!F14-'Income Statement'!I18*Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -1490,23 +1490,23 @@
         <v>10148.291</v>
       </c>
       <c r="E14" s="30">
-        <f>D14+'Income Statement'!E18*(1-Assumptions!$C$86)</f>
+        <f>D14+'Income Statement'!E18*(1-Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="F14" s="30">
-        <f>E14+'Income Statement'!F18*(1-Assumptions!$C$86)</f>
+        <f>E14+'Income Statement'!F18*(1-Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>F14+'Income Statement'!G18*(1-Assumptions!$C$86)</f>
+        <f>F14+'Income Statement'!G18*(1-Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="H14" s="30">
-        <f>G14+'Income Statement'!H18*(1-Assumptions!$C$86)</f>
+        <f>G14+'Income Statement'!H18*(1-Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="I14" s="30">
-        <f>H14+'Income Statement'!I18*(1-Assumptions!$C$86)</f>
+        <f>H14+'Income Statement'!I18*(1-Assumptions!$C$89)</f>
         <v/>
       </c>
     </row>
@@ -1994,23 +1994,23 @@
         <v>-2629.085</v>
       </c>
       <c r="D16" s="32">
-        <f>-'Income Statement'!E18*Assumptions!$C$86</f>
+        <f>-'Income Statement'!E18*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>-'Income Statement'!F18*Assumptions!$C$86</f>
+        <f>-'Income Statement'!F18*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="F16" s="32">
-        <f>-'Income Statement'!G18*Assumptions!$C$86</f>
+        <f>-'Income Statement'!G18*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="G16" s="32">
-        <f>-'Income Statement'!H18*Assumptions!$C$86</f>
+        <f>-'Income Statement'!H18*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="H16" s="32">
-        <f>-'Income Statement'!I18*Assumptions!$C$86</f>
+        <f>-'Income Statement'!I18*Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
           <t>Anchor date</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
+      <c r="C18" s="46" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -2877,19 +2877,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>19.79941369811398</v>
+        <v>19.89521878509298</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>22.21134817207639</v>
+        <v>22.31635263346431</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>25.52077124203224</v>
+        <v>25.63837116711629</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>30.346897498859</v>
+        <v>30.48283207972232</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>38.04870082568256</v>
+        <v>38.21385160013466</v>
       </c>
     </row>
     <row r="7">
@@ -2899,19 +2899,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>17.55870311681214</v>
+        <v>17.64409201442004</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>19.34238216802864</v>
+        <v>19.4343444346818</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>21.68428419355597</v>
+        <v>21.78485405395134</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>24.89753706605635</v>
+        <v>25.00988981661522</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>29.58332185972701</v>
+        <v>29.71282356551465</v>
       </c>
     </row>
     <row r="8">
@@ -2921,19 +2921,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>15.79662376636993</v>
+        <v>15.87382058959345</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>17.15983565739926</v>
+        <v>17.24187484176169</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>18.9790672692687</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>21.16365166408015</v>
+        <v>21.2598434469616</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>24.28194674822564</v>
+        <v>24.38911956629517</v>
       </c>
     </row>
     <row r="9">
@@ -2943,19 +2943,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>14.37442603137347</v>
+        <v>14.44501016379528</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>15.44343464289715</v>
+        <v>15.51766894581018</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>16.76578009962793</v>
+        <v>16.84451177084813</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>18.44489059524078</v>
+        <v>18.52931271255159</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>20.649364466215</v>
+        <v>20.74123392646188</v>
       </c>
     </row>
     <row r="10">
@@ -2965,19 +2965,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>13.20226648770423</v>
+        <v>13.26739983488979</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>14.05804986372445</v>
+        <v>14.12598346651176</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>15.09447965499236</v>
+        <v>15.16578852715548</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>16.37647279813237</v>
+        <v>16.45193858988862</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>18.00428385302159</v>
+        <v>18.08500733386205</v>
       </c>
     </row>
     <row r="12">
@@ -2991,27 +2991,27 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>5.40%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>5.90%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>6.41%</t>
+          <t>6.40%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>7.41%</t>
+          <t>7.40%</t>
         </is>
       </c>
     </row>
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>26.14357352570003</v>
+        <v>22.86071252254099</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>25.82975570066811</v>
+        <v>22.58642287182825</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>25.52077124203224</v>
+        <v>22.31635263346432</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>25.21652784942216</v>
+        <v>22.05042127703677</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>24.916935334247</v>
+        <v>21.78855011408429</v>
       </c>
     </row>
     <row r="15">
@@ -3044,19 +3044,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>22.21263784305483</v>
+        <v>19.90766657933445</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>21.94641594959031</v>
+        <v>19.66917559223161</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>21.68428419355597</v>
+        <v>19.4343444346818</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>21.42616459016411</v>
+        <v>19.20310336399791</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>21.17198093686849</v>
+        <v>18.97538423093015</v>
       </c>
     </row>
     <row r="16">
@@ -3066,19 +3066,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>19.35048571765527</v>
+        <v>17.66115751553052</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>19.11891790217087</v>
+        <v>17.44989909580002</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>17.24187484176169</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>18.66636176730568</v>
+        <v>17.03702321635302</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>18.44523986519273</v>
+        <v>16.8352840869271</v>
       </c>
     </row>
     <row r="17">
@@ -3088,19 +3088,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>17.17305269319061</v>
+        <v>15.89445565418189</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>16.96784770384932</v>
+        <v>15.70461257694443</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>16.76578009962793</v>
+        <v>15.51766894581018</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>16.56679024596512</v>
+        <v>15.33356967583791</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>16.37081986815219</v>
+        <v>15.15226093788137</v>
       </c>
     </row>
     <row r="18">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>15.46061148513528</v>
+        <v>14.46847143263363</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>15.27613872850689</v>
+        <v>14.29591279580231</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>15.09447965499236</v>
+        <v>14.12598346651176</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>14.91558086413144</v>
+        <v>13.95863356675025</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>14.73939017182985</v>
+        <v>13.79381435436996</v>
       </c>
     </row>
     <row r="20">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>22.40198251354033</v>
+        <v>20.02326655981615</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>17.24187484176169</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>16.40920067045051</v>
+        <v>15.20238643027447</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>15.93101093635009</v>
+        <v>14.80213040813605</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>13.8943248227103</v>
+        <v>13.07025919514067</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -3183,19 +3183,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>20.23250466545218</v>
+        <v>18.08333122101619</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>16.85628211698551</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>17.60190552972687</v>
+        <v>15.6773525856619</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>16.4745059001303</v>
+        <v>14.64621888479577</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>15.30952628288052</v>
+        <v>13.58071406056744</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -3209,19 +3209,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>16.00460556694265</v>
+        <v>14.23093082186519</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>17.44775233658746</v>
+        <v>15.54360646942535</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>16.85628211698551</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>20.33404587587708</v>
+        <v>18.16895776454566</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>21.77719264552191</v>
+        <v>19.48163341210584</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -3235,19 +3235,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>17.95070477355046</v>
+        <v>16.0030123794334</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>18.42080193989137</v>
+        <v>16.42964724820946</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>16.85628211698551</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>19.36099627257317</v>
+        <v>17.28291698576156</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>19.83109343891408</v>
+        <v>17.70955185453761</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -3261,19 +3261,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>20.07809120050769</v>
+        <v>17.94035354897293</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>19.48449515336998</v>
+        <v>17.39831783297922</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>16.85628211698551</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>18.29730305909456</v>
+        <v>16.31424640099178</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>17.70370701195685</v>
+        <v>15.77221068499807</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -3287,19 +3287,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>15.4693092551696</v>
+        <v>13.75255603699058</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>16.80692954187711</v>
+        <v>14.96593768913588</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>16.85628211698551</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>19.60665360020088</v>
+        <v>17.50551741515849</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>20.3331339912772</v>
+        <v>18.16447323631922</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -3313,19 +3313,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>19.91526932196428</v>
+        <v>17.82633212951094</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>19.40308421409827</v>
+        <v>17.34130712324822</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>16.85628211698551</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>18.2079856290776</v>
+        <v>16.20958210863521</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>17.52507215192293</v>
+        <v>15.56288210028492</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>19.10103955382623</v>
+        <v>17.04752904637536</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>19.0061037938791</v>
+        <v>16.96112886598618</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>16.85628211698551</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>18.78458702066914</v>
+        <v>16.75952844507809</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>18.6580060074063</v>
+        <v>16.64432820455918</v>
       </c>
       <c r="H29" s="16">
         <f>MAX(B29:F29)-MIN(B29:F29)</f>
@@ -3361,23 +3361,23 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital  (18.0% / 22.0% / 27.4% / 30.0% / 34.0%)</t>
+          <t>Asset life, years — derived from the depreciation notes  (10.7 / 13.7 / 16.7 / 19.7 / 22.7)</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>18.03758600609211</v>
+        <v>17.59954905673535</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>18.48919841482648</v>
+        <v>17.23341326119689</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>16.85623865313141</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>19.03113330530774</v>
+        <v>16.46769241781963</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>19.20646518163991</v>
+        <v>16.06743170634368</v>
       </c>
       <c r="H30" s="16">
         <f>MAX(B30:F30)-MIN(B30:F30)</f>
@@ -3391,19 +3391,19 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>15.79662376636993</v>
+        <v>15.87382058959345</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>17.15983565739926</v>
+        <v>17.24187484176169</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>18.89089910623227</v>
+        <v>18.9790672692687</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>21.16365166408015</v>
+        <v>21.2598434469616</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>24.28194674822564</v>
+        <v>24.38911956629517</v>
       </c>
       <c r="H31" s="16">
         <f>MAX(B31:F31)-MIN(B31:F31)</f>
@@ -4161,23 +4161,23 @@
       <c r="D23" s="25" t="n">
         <v>63.3</v>
       </c>
-      <c r="E23" s="46">
+      <c r="E23" s="45">
         <f>Assumptions!$B$25</f>
         <v/>
       </c>
-      <c r="F23" s="46">
+      <c r="F23" s="45">
         <f>Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="G23" s="46">
+      <c r="G23" s="45">
         <f>Assumptions!$D$25</f>
         <v/>
       </c>
-      <c r="H23" s="46">
+      <c r="H23" s="45">
         <f>Assumptions!$E$25</f>
         <v/>
       </c>
-      <c r="I23" s="46">
+      <c r="I23" s="45">
         <f>Assumptions!$F$25</f>
         <v/>
       </c>
@@ -4269,12 +4269,12 @@
           <t>UAE (ADX)</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>~20.7x</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>~4.8%</t>
         </is>
@@ -4296,12 +4296,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C6" s="45" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>~18.9x</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>~5.2%</t>
         </is>
@@ -4323,12 +4323,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C7" s="45" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>~15.5x</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>~2.9%</t>
         </is>
@@ -4350,12 +4350,12 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>~12.5x</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>~4.6%</t>
         </is>
@@ -4377,12 +4377,12 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="C9" s="45" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>~9x</t>
         </is>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>~6-7%</t>
         </is>
@@ -4404,12 +4404,12 @@
           <t>Oman</t>
         </is>
       </c>
-      <c r="C10" s="45" t="inlineStr">
+      <c r="C10" s="46" t="inlineStr">
         <is>
           <t>~11.4x</t>
         </is>
       </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>~6.7%</t>
         </is>
@@ -4431,12 +4431,12 @@
           <t>Developed markets</t>
         </is>
       </c>
-      <c r="C11" s="45" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>n/m</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>3.4% / n/m</t>
         </is>
@@ -4594,14 +4594,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>11.02686991091756</v>
+        <v>10.73766295146378</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C63</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>28.6533036884854</v>
+        <v>28.4368006184044</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="B15" s="13" t="n"/>
       <c r="C15" s="18" t="n">
-        <v>12.3</v>
+        <v>11.36</v>
       </c>
       <c r="D15" s="13" t="n"/>
       <c r="E15" s="13" t="n"/>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="C20" s="19">
-        <f>Assumptions!$C$83</f>
+        <f>Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="C21" s="19">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$87</f>
         <v/>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>11.02686991091756</v>
+        <v>10.73766295146378</v>
       </c>
     </row>
     <row r="7">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>28.6533036884854</v>
+        <v>28.4368006184044</v>
       </c>
     </row>
     <row r="8">
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>10.08649012975652</v>
+        <v>8.813624287539183</v>
       </c>
     </row>
     <row r="17">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="C17" s="21" t="n">
-        <v>7.555316462511931</v>
+        <v>6.974680547695217</v>
       </c>
     </row>
     <row r="18">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>14.81218441814286</v>
+        <v>13.89294132763612</v>
       </c>
     </row>
     <row r="19">
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>16.11429287425042</v>
+        <v>14.74258105617417</v>
       </c>
     </row>
     <row r="22">
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>18.57393404235861</v>
+        <v>16.36137867684112</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>9.836466254461905</v>
+        <v>9.885722650418625</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>21.54947017920073</v>
+        <v>21.65369177441337</v>
       </c>
     </row>
     <row r="26">
@@ -5254,13 +5254,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>18.45966756100478</v>
+        <v>16.83846400340635</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>12.19616318319305</v>
+        <v>11.23004905689838</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>20.67482766832535</v>
+        <v>18.85907968381511</v>
       </c>
     </row>
     <row r="27">
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>17.89729092471108</v>
+        <v>16.43966144595204</v>
       </c>
     </row>
   </sheetData>
@@ -5306,7 +5306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>12.3</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="6">
@@ -6211,148 +6211,179 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal REAL growth (stated, not derived)</t>
         </is>
       </c>
       <c r="C80" s="24" t="n">
-        <v>0.025</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Terminal inflation — UAE house macro path</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>Balance-sheet and bridge anchors</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="n"/>
-      <c r="C82" s="13" t="n"/>
-      <c r="D82" s="13" t="n"/>
-      <c r="E82" s="13" t="n"/>
-      <c r="F82" s="13" t="n"/>
-      <c r="G82" s="13" t="n"/>
-      <c r="H82" s="13" t="n"/>
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Weighted asset life, DERIVED from notes 6 and 8 (gross cost of the depreciable owned base over the year's own charge)</t>
+        </is>
+      </c>
+      <c r="C82" s="25" t="n">
+        <v>16.69965937728147</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities at FY2025 (AED mn, audited — the only debt-like item)</t>
-        </is>
-      </c>
-      <c r="C83" s="23" t="n">
-        <v>1938.819</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>Cash and term deposits at FY2025 (AED mn, audited)</t>
-        </is>
-      </c>
-      <c r="C84" s="23" t="n">
-        <v>2249.719</v>
+          <t>Terminal growth = (1+inflation)(1+real growth) − 1</t>
+        </is>
+      </c>
+      <c r="C83" s="9">
+        <f>(1+$C$81)*(1+$C$80)-1</f>
+        <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>Equity-accounted investees at carrying value (AED mn)</t>
-        </is>
-      </c>
-      <c r="C85" s="25" t="n">
-        <v>0.511</v>
-      </c>
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Balance-sheet and bridge anchors</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="n"/>
+      <c r="C85" s="13" t="n"/>
+      <c r="D85" s="13" t="n"/>
+      <c r="E85" s="13" t="n"/>
+      <c r="F85" s="13" t="n"/>
+      <c r="G85" s="13" t="n"/>
+      <c r="H85" s="13" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio (FY2024 actual 98%, FY2025 ~100%)</t>
-        </is>
-      </c>
-      <c r="C86" s="24" t="n">
-        <v>0.98</v>
+          <t>Lease liabilities at FY2025 (AED mn, audited — the only debt-like item)</t>
+        </is>
+      </c>
+      <c r="C86" s="23" t="n">
+        <v>1938.819</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Yield on cash and term deposits (audited FY2025 effective)</t>
-        </is>
-      </c>
-      <c r="C87" s="24" t="n">
-        <v>0.033</v>
+          <t>Cash and term deposits at FY2025 (AED mn, audited)</t>
+        </is>
+      </c>
+      <c r="C87" s="23" t="n">
+        <v>2249.719</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Lease interest rate (audited FY2025 effective)</t>
-        </is>
-      </c>
-      <c r="C88" s="24" t="n">
-        <v>0.036</v>
+          <t>Equity-accounted investees at carrying value (AED mn)</t>
+        </is>
+      </c>
+      <c r="C88" s="25" t="n">
+        <v>0.511</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Dividends gone ex between 31-Dec-2025 and the anchor (AED/share)</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="n">
-        <v>0.66</v>
+          <t>Forecast dividend payout ratio (FY2024 actual 98%, FY2025 ~100%)</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Days from the 31-Dec-2025 valuation date to the 07-Aug-2026 anchor</t>
-        </is>
-      </c>
-      <c r="C90" s="23" t="n">
-        <v>219</v>
+          <t>Yield on cash and term deposits (audited FY2025 effective)</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="n">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Lease interest rate (audited FY2025 effective)</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="n">
+        <v>0.036</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="n"/>
-      <c r="C92" s="13" t="n"/>
-      <c r="D92" s="13" t="n"/>
-      <c r="E92" s="13" t="n"/>
-      <c r="F92" s="13" t="n"/>
-      <c r="G92" s="13" t="n"/>
-      <c r="H92" s="13" t="n"/>
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Dividends gone ex between 31-Dec-2025 and the anchor (AED/share)</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
+          <t>Days from the 31-Dec-2025 valuation date to the 07-Aug-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C93" s="23" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="n"/>
+      <c r="C95" s="13" t="n"/>
+      <c r="D95" s="13" t="n"/>
+      <c r="E95" s="13" t="n"/>
+      <c r="F95" s="13" t="n"/>
+      <c r="G95" s="13" t="n"/>
+      <c r="H95" s="13" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
           <t>Justified price/earnings (GCC telecom peer median)</t>
         </is>
       </c>
-      <c r="C93" s="21" t="n">
+      <c r="C96" s="21" t="n">
         <v>12.9</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>Peer benchmark dividend yield</t>
         </is>
       </c>
-      <c r="C94" s="24" t="n">
+      <c r="C97" s="24" t="n">
         <v>0.0489</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C95" s="24" t="n">
+      <c r="C98" s="24" t="n">
         <v>0.27</v>
       </c>
     </row>
@@ -6465,7 +6496,7 @@
         </is>
       </c>
       <c r="C8" s="19">
-        <f>-Assumptions!$C$83</f>
+        <f>-Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="D8" s="16">
@@ -6480,7 +6511,7 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="D9" s="16">
@@ -6495,7 +6526,7 @@
         </is>
       </c>
       <c r="C10" s="19">
-        <f>Assumptions!$C$85</f>
+        <f>Assumptions!$C$88</f>
         <v/>
       </c>
       <c r="D10" s="16">
@@ -8135,7 +8166,7 @@
         </is>
       </c>
       <c r="C6" s="37">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -8168,7 +8199,7 @@
         </is>
       </c>
       <c r="C9" s="8">
-        <f>Assumptions!$C$89</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -8220,7 +8251,7 @@
         </is>
       </c>
       <c r="C14" s="37">
-        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$83-Assumptions!$C$84)/'Income Statement'!D9</f>
+        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$86-Assumptions!$C$87)/'Income Statement'!D9</f>
         <v/>
       </c>
     </row>
@@ -8242,7 +8273,7 @@
         </is>
       </c>
       <c r="C16" s="9">
-        <f>Assumptions!$C$94</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -8354,7 +8385,7 @@
       </c>
       <c r="B27" s="13" t="n"/>
       <c r="C27" s="31">
-        <f>C26*Assumptions!$C$93*DCF!$C$62-Assumptions!$C$89</f>
+        <f>C26*Assumptions!$C$96*DCF!$C$62-Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -8363,11 +8394,11 @@
         </is>
       </c>
       <c r="E27" s="16">
-        <f>C26*12*DCF!$C$62-Assumptions!$C$89</f>
+        <f>C26*12*DCF!$C$62-Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>C26*18.5*DCF!$C$62-Assumptions!$C$89</f>
+        <f>C26*18.5*DCF!$C$62-Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -8401,7 +8432,7 @@
         </is>
       </c>
       <c r="C31" s="9">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
     </row>
@@ -8434,7 +8465,7 @@
         </is>
       </c>
       <c r="C34" s="39">
-        <f>(C31-Assumptions!$C$80)/(C33-Assumptions!$C$80)</f>
+        <f>(C31-Assumptions!$C$83)/(C33-Assumptions!$C$83)</f>
         <v/>
       </c>
     </row>
@@ -8446,7 +8477,7 @@
       </c>
       <c r="B35" s="13" t="n"/>
       <c r="C35" s="31">
-        <f>C30*C34*DCF!$C$62-Assumptions!$C$89</f>
+        <f>C30*C34*DCF!$C$62-Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -8455,11 +8486,11 @@
         </is>
       </c>
       <c r="E35" s="16">
-        <f>((Assumptions!$C$95-Assumptions!$C$80)/((DCF!C40+DCF!C50)/2+0.01-Assumptions!$C$80))*C30*DCF!$C$62-Assumptions!$C$89</f>
+        <f>((Assumptions!$C$98-Assumptions!$C$83)/((DCF!C40+DCF!C50)/2+0.01-Assumptions!$C$83))*C30*DCF!$C$62-Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>((Assumptions!$C$95+0.02-Assumptions!$C$80)/(DCF!C50-Assumptions!$C$80))*C30*DCF!$C$62-Assumptions!$C$89</f>
+        <f>((Assumptions!$C$98+0.02-Assumptions!$C$83)/(DCF!C50-Assumptions!$C$83))*C30*DCF!$C$62-Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -8475,7 +8506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -8925,7 +8956,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Terminal-year NOPAT grown one year (AED mn)</t>
+          <t>Terminal-year operating profit after tax, grown one year (AED mn)</t>
         </is>
       </c>
       <c r="C21" s="32">
@@ -8936,33 +8967,33 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
-        </is>
-      </c>
-      <c r="C22" s="17">
-        <f>F10*(1+C24)/'Summary Financials'!I13</f>
+          <t>Terminal free cash flow — built line by line at rows 70-77 (AED mn)</t>
+        </is>
+      </c>
+      <c r="C22" s="32">
+        <f>C77</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Required reinvestment rate (g / return on capital)</t>
+          <t>Terminal free cash flow as a share of terminal profit</t>
         </is>
       </c>
       <c r="C23" s="9">
-        <f>C24/C22</f>
+        <f>C22/C21</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C24" s="17">
-        <f>Assumptions!$C$80</f>
+          <t>Terminal growth — (1+inflation)(1+real growth)−1, both at rows 70-71</t>
+        </is>
+      </c>
+      <c r="C24" s="9">
+        <f>(1+C70)*(1+C71)-1</f>
         <v/>
       </c>
     </row>
@@ -8980,11 +9011,11 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Terminal value — terminal-year NOPAT C21 x (1−C23), capitalised (AED mn)</t>
+          <t>Terminal value — terminal free cash flow C22 grown one year, capitalised (AED mn)</t>
         </is>
       </c>
       <c r="C26" s="32">
-        <f>C21*(1-C23)/(C25-C24)</f>
+        <f>C22*(1+C24)/(C25-C24)</f>
         <v/>
       </c>
     </row>
@@ -9169,7 +9200,7 @@
         </is>
       </c>
       <c r="C44" s="19">
-        <f>Assumptions!$C$83</f>
+        <f>Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -9394,7 +9425,7 @@
         </is>
       </c>
       <c r="C62" s="41">
-        <f>(1+C40)^(Assumptions!$C$90/365)</f>
+        <f>(1+C40)^(Assumptions!$C$93/365)</f>
         <v/>
       </c>
     </row>
@@ -9406,7 +9437,7 @@
       </c>
       <c r="B63" s="13" t="n"/>
       <c r="C63" s="31">
-        <f>C32*C62-Assumptions!$C$89</f>
+        <f>C32*C62-Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="D63" s="13" t="n"/>
@@ -9416,6 +9447,119 @@
         <is>
           <t>The bridge on row 32 is dated 31-Dec-2025 (the audited balance-sheet date it nets leases and cash at). Row 63 rolls it to the anchor at the cost of equity, net of the AED 0.40 final FY2025 dividend paid 28-Apr-2026. Every lens on every sheet is rolled the same way. The H1-2026 interim dividend of AED 0.26 (declared 23-Jul-2026, unpaid at the anchor) stays in the share.</t>
         </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>THE TERMINAL, LINE BY LINE — capital maintained at replacement cost over the asset life the depreciation notes themselves imply</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>The retired construction grew terminal profit and deducted a reinvestment rate set by the growth rate over the return on capital, which is arithmetically the same as rebuilding the whole capital base every 1/g years — a fact about the dirham's peg to the dollar rather than about a mobile network. The asset life below is DERIVED from notes 6 and 8: the gross cost of the depreciable owned base over the year's own charge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Terminal inflation — UAE house macro path</t>
+        </is>
+      </c>
+      <c r="C70" s="17">
+        <f>Assumptions!$C$81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Terminal REAL growth (stated)</t>
+        </is>
+      </c>
+      <c r="C71" s="17">
+        <f>Assumptions!$C$80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Weighted asset life, derived from notes 6 and 8 (years)</t>
+        </is>
+      </c>
+      <c r="C72" s="45">
+        <f>Assumptions!$C$82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Terminal operating profit after tax (from row 21)</t>
+        </is>
+      </c>
+      <c r="C73" s="32">
+        <f>C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Plus owned depreciation and amortisation, grown one year — the right-of-use charge is neither added back nor charged, which is a lease renewed at its own current cost</t>
+        </is>
+      </c>
+      <c r="C74" s="32">
+        <f>2582.418423*(1+C24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Less capital maintenance at replacement cost — that charge escalated over half the derived life</t>
+        </is>
+      </c>
+      <c r="C75" s="32">
+        <f>-C74*(1+C70)^(C72/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Less capital for real growth, and less inflation on working capital (a CREDIT here: this company collects before it pays)</t>
+        </is>
+      </c>
+      <c r="C76" s="32">
+        <f>-C71*10429.868530-C70*-1323.408954</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Terminal free cash flow</t>
+        </is>
+      </c>
+      <c r="C77" s="28">
+        <f>SUM(C73:C76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Memo — the no-growth perpetuity at book depreciation, a diagnostic and not a bound</t>
+        </is>
+      </c>
+      <c r="C78" s="32">
+        <f>C21/C25</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -9833,23 +9977,23 @@
         <v>74.672</v>
       </c>
       <c r="E13" s="32">
-        <f>Assumptions!$C$87*MAX('Balance Sheet'!D12,0)</f>
+        <f>Assumptions!$C$90*MAX('Balance Sheet'!D12,0)</f>
         <v/>
       </c>
       <c r="F13" s="32">
-        <f>Assumptions!$C$87*MAX('Balance Sheet'!E12,0)</f>
+        <f>Assumptions!$C$90*MAX('Balance Sheet'!E12,0)</f>
         <v/>
       </c>
       <c r="G13" s="32">
-        <f>Assumptions!$C$87*MAX('Balance Sheet'!F12,0)</f>
+        <f>Assumptions!$C$90*MAX('Balance Sheet'!F12,0)</f>
         <v/>
       </c>
       <c r="H13" s="32">
-        <f>Assumptions!$C$87*MAX('Balance Sheet'!G12,0)</f>
+        <f>Assumptions!$C$90*MAX('Balance Sheet'!G12,0)</f>
         <v/>
       </c>
       <c r="I13" s="32">
-        <f>Assumptions!$C$87*MAX('Balance Sheet'!H12,0)</f>
+        <f>Assumptions!$C$90*MAX('Balance Sheet'!H12,0)</f>
         <v/>
       </c>
     </row>
@@ -9869,23 +10013,23 @@
         <v>-95.054</v>
       </c>
       <c r="E14" s="32">
-        <f>-Assumptions!$C$88*'Balance Sheet'!E13</f>
+        <f>-Assumptions!$C$91*'Balance Sheet'!E13</f>
         <v/>
       </c>
       <c r="F14" s="32">
-        <f>-Assumptions!$C$88*'Balance Sheet'!F13</f>
+        <f>-Assumptions!$C$91*'Balance Sheet'!F13</f>
         <v/>
       </c>
       <c r="G14" s="32">
-        <f>-Assumptions!$C$88*'Balance Sheet'!G13</f>
+        <f>-Assumptions!$C$91*'Balance Sheet'!G13</f>
         <v/>
       </c>
       <c r="H14" s="32">
-        <f>-Assumptions!$C$88*'Balance Sheet'!H13</f>
+        <f>-Assumptions!$C$91*'Balance Sheet'!H13</f>
         <v/>
       </c>
       <c r="I14" s="32">
-        <f>-Assumptions!$C$88*'Balance Sheet'!I13</f>
+        <f>-Assumptions!$C$91*'Balance Sheet'!I13</f>
         <v/>
       </c>
     </row>
@@ -10071,23 +10215,23 @@
         <v>0.64</v>
       </c>
       <c r="E20" s="16">
-        <f>E19*Assumptions!$C$86</f>
+        <f>E19*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>F19*Assumptions!$C$86</f>
+        <f>F19*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>G19*Assumptions!$C$86</f>
+        <f>G19*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>H19*Assumptions!$C$86</f>
+        <f>H19*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>I19*Assumptions!$C$86</f>
+        <f>I19*Assumptions!$C$89</f>
         <v/>
       </c>
     </row>

--- a/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
+++ b/engine/du_study/DU_Valuation_Model_09082026_public.xlsx
@@ -3183,19 +3183,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>18.08333122101619</v>
+        <v>17.78493082128233</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>16.85628211698551</v>
+        <v>16.57779987073647</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>15.6773525856619</v>
+        <v>15.41800738883945</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>14.64621888479577</v>
+        <v>14.40361163207821</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>13.58071406056744</v>
+        <v>13.35540268342493</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -3209,19 +3209,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>14.23093082186519</v>
+        <v>13.99663235400643</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>15.54360646942535</v>
+        <v>15.28721611237145</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>16.85628211698551</v>
+        <v>16.57779987073647</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>18.16895776454566</v>
+        <v>17.86838362910148</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>19.48163341210584</v>
+        <v>19.15896738746652</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -3235,19 +3235,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>16.0030123794334</v>
+        <v>15.7390753752909</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>16.42964724820946</v>
+        <v>16.15843762301369</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>16.85628211698551</v>
+        <v>16.57779987073647</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>17.28291698576156</v>
+        <v>16.99716211845924</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>17.70955185453761</v>
+        <v>17.41652436618203</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -3261,19 +3261,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>17.94035354897293</v>
+        <v>17.64395765095027</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>17.39831783297922</v>
+        <v>17.11087876084336</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>16.85628211698551</v>
+        <v>16.57779987073647</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>16.31424640099178</v>
+        <v>16.04472098062956</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>15.77221068499807</v>
+        <v>15.51164209052265</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -3287,19 +3287,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>13.75255603699058</v>
+        <v>13.52997619908564</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>14.96593768913588</v>
+        <v>14.72151775672866</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>16.85628211698551</v>
+        <v>16.57779987073647</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>17.50551741515849</v>
+        <v>17.21532665438986</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>18.16447323631922</v>
+        <v>17.8623937445068</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -3313,19 +3313,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>17.82633212951094</v>
+        <v>17.53520713489131</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>17.34130712324822</v>
+        <v>17.05650350281389</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>16.85628211698551</v>
+        <v>16.57779987073647</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>16.20958210863521</v>
+        <v>15.9395283612999</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>15.56288210028492</v>
+        <v>15.30125685186333</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>17.04752904637536</v>
+        <v>16.76797703305044</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>16.96112886598618</v>
+        <v>16.68206014443815</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>16.85628211698551</v>
+        <v>16.57779987073647</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>16.75952844507809</v>
+        <v>16.48158740434283</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>16.64432820455918</v>
+        <v>16.36703155285978</v>
       </c>
       <c r="H29" s="16">
         <f>MAX(B29:F29)-MIN(B29:F29)</f>
@@ -3365,19 +3365,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>17.59954905673535</v>
+        <v>17.30649294892259</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>17.23341326119689</v>
+        <v>16.94753628662998</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>16.85623865313141</v>
+        <v>16.5777572591148</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>16.46769241781963</v>
+        <v>16.19682957743659</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>16.06743170634368</v>
+        <v>15.80441711520527</v>
       </c>
       <c r="H30" s="16">
         <f>MAX(B30:F30)-MIN(B30:F30)</f>
@@ -4594,14 +4594,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>10.73766295146378</v>
+        <v>10.56609178209415</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C63</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>28.4368006184044</v>
+        <v>27.67129453178129</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>10.73766295146378</v>
+        <v>10.56609178209415</v>
       </c>
     </row>
     <row r="7">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>28.4368006184044</v>
+        <v>27.67129453178129</v>
       </c>
     </row>
     <row r="8">
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>8.813624287539183</v>
+        <v>8.640808125038413</v>
       </c>
     </row>
     <row r="17">
@@ -8956,11 +8956,11 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Terminal-year operating profit after tax, grown one year (AED mn)</t>
+          <t>FY2030E operating profit after tax — the perpetuity grows this once (AED mn)</t>
         </is>
       </c>
       <c r="C21" s="32">
-        <f>F10*(1+C24)</f>
+        <f>F10</f>
         <v/>
       </c>
     </row>
@@ -9510,11 +9510,11 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Plus owned depreciation and amortisation, grown one year — the right-of-use charge is neither added back nor charged, which is a lease renewed at its own current cost</t>
+          <t>Plus owned depreciation and amortisation — the right-of-use charge is neither added back nor charged, which is a lease renewed at its own current cost</t>
         </is>
       </c>
       <c r="C74" s="32">
-        <f>2582.418423*(1+C24)</f>
+        <f>2582.418423</f>
         <v/>
       </c>
     </row>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="C76" s="32">
-        <f>-C71*10429.868530-C70*-1323.408954</f>
+        <f>-C71*10429.868530-C70*-1297.459758</f>
         <v/>
       </c>
     </row>
